--- a/Angebotsdaten.xlsx
+++ b/Angebotsdaten.xlsx
@@ -28573,7 +28573,7 @@
         </is>
       </c>
       <c r="F628" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H628" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         </is>
       </c>
       <c r="F673" t="n">
-        <v>0</v>
+        <v>3560</v>
       </c>
       <c r="H673" t="inlineStr">
         <is>
@@ -32655,7 +32655,7 @@
         </is>
       </c>
       <c r="F720" t="n">
-        <v>0</v>
+        <v>3560</v>
       </c>
       <c r="H720" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         </is>
       </c>
       <c r="F767" t="n">
-        <v>0</v>
+        <v>3560</v>
       </c>
       <c r="H767" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         </is>
       </c>
       <c r="F815" t="n">
-        <v>0</v>
+        <v>3560</v>
       </c>
       <c r="H815" t="inlineStr">
         <is>
@@ -40517,7 +40517,7 @@
         </is>
       </c>
       <c r="F897" t="n">
-        <v>0</v>
+        <v>4730</v>
       </c>
       <c r="H897" t="inlineStr">
         <is>
@@ -42430,7 +42430,7 @@
         </is>
       </c>
       <c r="F940" t="n">
-        <v>0</v>
+        <v>4330</v>
       </c>
       <c r="H940" t="inlineStr">
         <is>
@@ -43272,7 +43272,7 @@
         </is>
       </c>
       <c r="C960" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -43318,7 +43318,7 @@
         </is>
       </c>
       <c r="C961" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
         </is>
       </c>
       <c r="C962" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -43410,7 +43410,7 @@
         </is>
       </c>
       <c r="C963" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         </is>
       </c>
       <c r="C964" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -43502,7 +43502,7 @@
         </is>
       </c>
       <c r="C965" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -43548,7 +43548,7 @@
         </is>
       </c>
       <c r="C966" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -43594,7 +43594,7 @@
         </is>
       </c>
       <c r="C967" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -43640,7 +43640,7 @@
         </is>
       </c>
       <c r="C968" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -43686,7 +43686,7 @@
         </is>
       </c>
       <c r="C969" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -43732,7 +43732,7 @@
         </is>
       </c>
       <c r="C970" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         </is>
       </c>
       <c r="C971" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -43819,7 +43819,7 @@
         </is>
       </c>
       <c r="C972" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         </is>
       </c>
       <c r="C973" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         </is>
       </c>
       <c r="C974" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -43942,7 +43942,7 @@
         </is>
       </c>
       <c r="C975" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -43983,7 +43983,7 @@
         </is>
       </c>
       <c r="C976" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -44029,7 +44029,7 @@
         </is>
       </c>
       <c r="C977" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
         </is>
       </c>
       <c r="C978" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -44111,7 +44111,7 @@
         </is>
       </c>
       <c r="C979" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -44152,7 +44152,7 @@
         </is>
       </c>
       <c r="C980" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -44198,7 +44198,7 @@
         </is>
       </c>
       <c r="C981" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -44244,7 +44244,7 @@
         </is>
       </c>
       <c r="C982" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         </is>
       </c>
       <c r="C983" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
         </is>
       </c>
       <c r="C984" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -44382,7 +44382,7 @@
         </is>
       </c>
       <c r="C985" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         </is>
       </c>
       <c r="C986" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -44474,7 +44474,7 @@
         </is>
       </c>
       <c r="C987" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -44520,7 +44520,7 @@
         </is>
       </c>
       <c r="C988" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -44566,7 +44566,7 @@
         </is>
       </c>
       <c r="C989" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         </is>
       </c>
       <c r="C990" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -44658,7 +44658,7 @@
         </is>
       </c>
       <c r="C991" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -44704,7 +44704,7 @@
         </is>
       </c>
       <c r="C992" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         </is>
       </c>
       <c r="C993" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         </is>
       </c>
       <c r="C994" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         </is>
       </c>
       <c r="C995" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         </is>
       </c>
       <c r="C996" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -44934,7 +44934,7 @@
         </is>
       </c>
       <c r="C997" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -44980,7 +44980,7 @@
         </is>
       </c>
       <c r="C998" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -45026,7 +45026,7 @@
         </is>
       </c>
       <c r="C999" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -45072,7 +45072,7 @@
         </is>
       </c>
       <c r="C1000" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         </is>
       </c>
       <c r="C1001" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         </is>
       </c>
       <c r="C1002" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -45210,7 +45210,7 @@
         </is>
       </c>
       <c r="C1003" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -45256,7 +45256,7 @@
         </is>
       </c>
       <c r="C1004" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -45302,7 +45302,7 @@
         </is>
       </c>
       <c r="C1005" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -45348,7 +45348,7 @@
         </is>
       </c>
       <c r="C1006" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         </is>
       </c>
       <c r="C1007" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         </is>
       </c>
       <c r="C1008" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -45486,7 +45486,7 @@
         </is>
       </c>
       <c r="C1009" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -45532,7 +45532,7 @@
         </is>
       </c>
       <c r="C1010" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -45578,7 +45578,7 @@
         </is>
       </c>
       <c r="C1011" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         </is>
       </c>
       <c r="C1012" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -45670,7 +45670,7 @@
         </is>
       </c>
       <c r="C1013" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -45679,7 +45679,7 @@
       </c>
       <c r="E1013" t="inlineStr">
         <is>
-          <t>Ausgklappbare 2.US</t>
+          <t>Ausklappbare 2.US</t>
         </is>
       </c>
       <c r="F1013" t="n">
@@ -45716,7 +45716,7 @@
         </is>
       </c>
       <c r="C1014" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         </is>
       </c>
       <c r="C1015" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         </is>
       </c>
       <c r="C1016" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -45854,7 +45854,7 @@
         </is>
       </c>
       <c r="C1017" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         </is>
       </c>
       <c r="C1018" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         </is>
       </c>
       <c r="C1019" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -45992,7 +45992,7 @@
         </is>
       </c>
       <c r="C1020" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -46038,7 +46038,7 @@
         </is>
       </c>
       <c r="C1021" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -46084,7 +46084,7 @@
         </is>
       </c>
       <c r="C1022" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         </is>
       </c>
       <c r="C1023" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -46176,7 +46176,7 @@
         </is>
       </c>
       <c r="C1024" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -46222,7 +46222,7 @@
         </is>
       </c>
       <c r="C1025" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -46268,7 +46268,7 @@
         </is>
       </c>
       <c r="C1026" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         </is>
       </c>
       <c r="C1027" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -46360,7 +46360,7 @@
         </is>
       </c>
       <c r="C1028" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -46866,7 +46866,7 @@
         </is>
       </c>
       <c r="C1039" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
       </c>
       <c r="E1039" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
+          <t>1/1 Seite 4c</t>
         </is>
       </c>
       <c r="F1039" t="n">
@@ -46912,7 +46912,7 @@
         </is>
       </c>
       <c r="C1040" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
       </c>
       <c r="E1040" t="inlineStr">
         <is>
-          <t>1/2 Seite</t>
+          <t>1/2 Seite 4c</t>
         </is>
       </c>
       <c r="F1040" t="n">
@@ -46958,7 +46958,7 @@
         </is>
       </c>
       <c r="C1041" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -46967,7 +46967,7 @@
       </c>
       <c r="E1041" t="inlineStr">
         <is>
-          <t>1/3 Seite</t>
+          <t>1/3 Seite 4c</t>
         </is>
       </c>
       <c r="F1041" t="n">
@@ -47004,7 +47004,7 @@
         </is>
       </c>
       <c r="C1042" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -47013,7 +47013,7 @@
       </c>
       <c r="E1042" t="inlineStr">
         <is>
-          <t>1/4 Seite</t>
+          <t>1/4 Seite 4c</t>
         </is>
       </c>
       <c r="F1042" t="n">
@@ -47050,7 +47050,7 @@
         </is>
       </c>
       <c r="C1043" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         </is>
       </c>
       <c r="C1044" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         </is>
       </c>
       <c r="C1045" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -47151,7 +47151,7 @@
       </c>
       <c r="E1045" t="inlineStr">
         <is>
-          <t>gegenüber Textanfang</t>
+          <t>Seite ggü. Textanfang</t>
         </is>
       </c>
       <c r="F1045" t="n">
@@ -47188,7 +47188,7 @@
         </is>
       </c>
       <c r="C1046" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -47234,7 +47234,7 @@
         </is>
       </c>
       <c r="C1047" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -47280,7 +47280,7 @@
         </is>
       </c>
       <c r="C1048" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -47326,7 +47326,7 @@
         </is>
       </c>
       <c r="C1049" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -47372,7 +47372,7 @@
         </is>
       </c>
       <c r="C1050" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -47418,7 +47418,7 @@
         </is>
       </c>
       <c r="C1051" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -47459,7 +47459,7 @@
         </is>
       </c>
       <c r="C1052" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         </is>
       </c>
       <c r="C1053" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         </is>
       </c>
       <c r="C1054" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -47582,7 +47582,7 @@
         </is>
       </c>
       <c r="C1055" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         </is>
       </c>
       <c r="C1056" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -47669,7 +47669,7 @@
         </is>
       </c>
       <c r="C1057" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -47710,7 +47710,7 @@
         </is>
       </c>
       <c r="C1058" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         </is>
       </c>
       <c r="C1059" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -47760,7 +47760,7 @@
       </c>
       <c r="E1059" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
+          <t>1/1 Seite 4c</t>
         </is>
       </c>
       <c r="F1059" t="n">
@@ -47797,7 +47797,7 @@
         </is>
       </c>
       <c r="C1060" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -47806,7 +47806,7 @@
       </c>
       <c r="E1060" t="inlineStr">
         <is>
-          <t>1/2 Seite</t>
+          <t>1/2 Seite 4c</t>
         </is>
       </c>
       <c r="F1060" t="n">
@@ -47843,7 +47843,7 @@
         </is>
       </c>
       <c r="C1061" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -47852,7 +47852,7 @@
       </c>
       <c r="E1061" t="inlineStr">
         <is>
-          <t>1/3 Seite</t>
+          <t>1/3 Seite 4c</t>
         </is>
       </c>
       <c r="F1061" t="n">
@@ -47889,7 +47889,7 @@
         </is>
       </c>
       <c r="C1062" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -47898,7 +47898,7 @@
       </c>
       <c r="E1062" t="inlineStr">
         <is>
-          <t>1/4 Seite</t>
+          <t>1/4 Seite 4c</t>
         </is>
       </c>
       <c r="F1062" t="n">
@@ -47935,7 +47935,7 @@
         </is>
       </c>
       <c r="C1063" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -47981,7 +47981,7 @@
         </is>
       </c>
       <c r="C1064" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         </is>
       </c>
       <c r="C1065" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -48036,7 +48036,7 @@
       </c>
       <c r="E1065" t="inlineStr">
         <is>
-          <t>Gegenüber Inhalt</t>
+          <t>Seite ggü. Inhalt</t>
         </is>
       </c>
       <c r="F1065" t="n">
@@ -48073,7 +48073,7 @@
         </is>
       </c>
       <c r="C1066" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -48119,7 +48119,7 @@
         </is>
       </c>
       <c r="C1067" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         </is>
       </c>
       <c r="C1068" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -48211,7 +48211,7 @@
         </is>
       </c>
       <c r="C1069" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         </is>
       </c>
       <c r="C1070" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -48298,7 +48298,7 @@
         </is>
       </c>
       <c r="C1071" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -48339,7 +48339,7 @@
         </is>
       </c>
       <c r="C1072" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -48380,7 +48380,7 @@
         </is>
       </c>
       <c r="C1073" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         </is>
       </c>
       <c r="C1074" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -48462,7 +48462,7 @@
         </is>
       </c>
       <c r="C1075" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -48508,7 +48508,7 @@
         </is>
       </c>
       <c r="C1076" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -48549,7 +48549,7 @@
         </is>
       </c>
       <c r="C1077" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -48590,7 +48590,7 @@
         </is>
       </c>
       <c r="C1078" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -48631,7 +48631,7 @@
         </is>
       </c>
       <c r="C1079" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
       </c>
       <c r="E1079" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
+          <t>1/1 Seite 4c</t>
         </is>
       </c>
       <c r="F1079" t="n">
@@ -48677,7 +48677,7 @@
         </is>
       </c>
       <c r="C1080" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -48686,7 +48686,7 @@
       </c>
       <c r="E1080" t="inlineStr">
         <is>
-          <t>1/2 Seite</t>
+          <t>1/2 Seite 4c</t>
         </is>
       </c>
       <c r="F1080" t="n">
@@ -48723,7 +48723,7 @@
         </is>
       </c>
       <c r="C1081" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -48732,7 +48732,7 @@
       </c>
       <c r="E1081" t="inlineStr">
         <is>
-          <t>1/3 seite</t>
+          <t>1/3 Seite 4c</t>
         </is>
       </c>
       <c r="F1081" t="n">
@@ -48769,7 +48769,7 @@
         </is>
       </c>
       <c r="C1082" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -48778,7 +48778,7 @@
       </c>
       <c r="E1082" t="inlineStr">
         <is>
-          <t>1/4 Seite</t>
+          <t>1/4 Seite 4c</t>
         </is>
       </c>
       <c r="F1082" t="n">
@@ -48815,7 +48815,7 @@
         </is>
       </c>
       <c r="C1083" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -48861,7 +48861,7 @@
         </is>
       </c>
       <c r="C1084" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -48907,7 +48907,7 @@
         </is>
       </c>
       <c r="C1085" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -48916,7 +48916,7 @@
       </c>
       <c r="E1085" t="inlineStr">
         <is>
-          <t>gegenüber Textanfang</t>
+          <t>Seite ggü. Textanfang</t>
         </is>
       </c>
       <c r="F1085" t="n">
@@ -48953,7 +48953,7 @@
         </is>
       </c>
       <c r="C1086" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         </is>
       </c>
       <c r="C1087" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         </is>
       </c>
       <c r="C1088" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -49091,7 +49091,7 @@
         </is>
       </c>
       <c r="C1089" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -49137,7 +49137,7 @@
         </is>
       </c>
       <c r="C1090" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -49183,7 +49183,7 @@
         </is>
       </c>
       <c r="C1091" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -49224,7 +49224,7 @@
         </is>
       </c>
       <c r="C1092" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -49265,7 +49265,7 @@
         </is>
       </c>
       <c r="C1093" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -49306,7 +49306,7 @@
         </is>
       </c>
       <c r="C1094" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -49347,7 +49347,7 @@
         </is>
       </c>
       <c r="C1095" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -49388,7 +49388,7 @@
         </is>
       </c>
       <c r="C1096" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -49429,7 +49429,7 @@
         </is>
       </c>
       <c r="C1097" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         </is>
       </c>
       <c r="C1098" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -49516,7 +49516,7 @@
         </is>
       </c>
       <c r="C1099" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -49557,7 +49557,7 @@
         </is>
       </c>
       <c r="C1100" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
       </c>
       <c r="E1100" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
+          <t>1/1 Seite 4c</t>
         </is>
       </c>
       <c r="F1100" t="n">
@@ -49603,7 +49603,7 @@
         </is>
       </c>
       <c r="C1101" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
@@ -49612,7 +49612,7 @@
       </c>
       <c r="E1101" t="inlineStr">
         <is>
-          <t>1/2 Seite</t>
+          <t>1/2 Seite 4c</t>
         </is>
       </c>
       <c r="F1101" t="n">
@@ -49649,7 +49649,7 @@
         </is>
       </c>
       <c r="C1102" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1102" t="inlineStr">
         <is>
@@ -49658,7 +49658,7 @@
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t>1/3 Seite</t>
+          <t>1/3 Seite 4c</t>
         </is>
       </c>
       <c r="F1102" t="n">
@@ -49695,7 +49695,7 @@
         </is>
       </c>
       <c r="C1103" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1103" t="inlineStr">
         <is>
@@ -49704,7 +49704,7 @@
       </c>
       <c r="E1103" t="inlineStr">
         <is>
-          <t>1/4 Seite</t>
+          <t>1/4 Seite 4c</t>
         </is>
       </c>
       <c r="F1103" t="n">
@@ -49741,7 +49741,7 @@
         </is>
       </c>
       <c r="C1104" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1104" t="inlineStr">
         <is>
@@ -49787,7 +49787,7 @@
         </is>
       </c>
       <c r="C1105" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1105" t="inlineStr">
         <is>
@@ -49833,7 +49833,7 @@
         </is>
       </c>
       <c r="C1106" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1106" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
       </c>
       <c r="E1106" t="inlineStr">
         <is>
-          <t>Gegenüber Inhalt</t>
+          <t>Seite ggü. Inhalt</t>
         </is>
       </c>
       <c r="F1106" t="n">
@@ -49879,7 +49879,7 @@
         </is>
       </c>
       <c r="C1107" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1107" t="inlineStr">
         <is>
@@ -49925,7 +49925,7 @@
         </is>
       </c>
       <c r="C1108" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1108" t="inlineStr">
         <is>
@@ -49971,7 +49971,7 @@
         </is>
       </c>
       <c r="C1109" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1109" t="inlineStr">
         <is>
@@ -50017,7 +50017,7 @@
         </is>
       </c>
       <c r="C1110" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1110" t="inlineStr">
         <is>
@@ -50063,7 +50063,7 @@
         </is>
       </c>
       <c r="C1111" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1111" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         </is>
       </c>
       <c r="C1112" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1112" t="inlineStr">
         <is>
@@ -50145,7 +50145,7 @@
         </is>
       </c>
       <c r="C1113" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1113" t="inlineStr">
         <is>
@@ -50186,7 +50186,7 @@
         </is>
       </c>
       <c r="C1114" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1114" t="inlineStr">
         <is>
@@ -50227,7 +50227,7 @@
         </is>
       </c>
       <c r="C1115" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1115" t="inlineStr">
         <is>
@@ -50273,7 +50273,7 @@
         </is>
       </c>
       <c r="C1116" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1116" t="inlineStr">
         <is>
@@ -50314,7 +50314,7 @@
         </is>
       </c>
       <c r="C1117" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1117" t="inlineStr">
         <is>
@@ -50355,7 +50355,7 @@
         </is>
       </c>
       <c r="C1118" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1118" t="inlineStr">
         <is>
@@ -50396,7 +50396,7 @@
         </is>
       </c>
       <c r="C1119" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1119" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         </is>
       </c>
       <c r="C1138" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D1138" t="inlineStr">
         <is>
@@ -51306,7 +51306,7 @@
         </is>
       </c>
       <c r="C1139" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D1139" t="inlineStr">
         <is>
@@ -51352,7 +51352,7 @@
         </is>
       </c>
       <c r="C1140" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D1140" t="inlineStr">
         <is>
@@ -51398,7 +51398,7 @@
         </is>
       </c>
       <c r="C1141" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D1141" t="inlineStr">
         <is>
@@ -51444,7 +51444,7 @@
         </is>
       </c>
       <c r="C1142" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D1142" t="inlineStr">
         <is>
@@ -51490,7 +51490,7 @@
         </is>
       </c>
       <c r="C1143" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D1143" t="inlineStr">
         <is>
@@ -51536,7 +51536,7 @@
         </is>
       </c>
       <c r="C1144" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D1144" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         </is>
       </c>
       <c r="C1145" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D1145" t="inlineStr">
         <is>
@@ -51628,7 +51628,7 @@
         </is>
       </c>
       <c r="C1146" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D1146" t="inlineStr">
         <is>
@@ -51674,7 +51674,7 @@
         </is>
       </c>
       <c r="C1147" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D1147" t="inlineStr">
         <is>
@@ -51720,7 +51720,7 @@
         </is>
       </c>
       <c r="C1148" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D1148" t="inlineStr">
         <is>
@@ -51766,7 +51766,7 @@
         </is>
       </c>
       <c r="C1149" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D1149" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         </is>
       </c>
       <c r="C1150" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D1150" t="inlineStr">
         <is>
@@ -51858,7 +51858,7 @@
         </is>
       </c>
       <c r="C1151" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D1151" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         </is>
       </c>
       <c r="C1152" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D1152" t="inlineStr">
         <is>
@@ -51950,7 +51950,7 @@
         </is>
       </c>
       <c r="C1153" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D1153" t="inlineStr">
         <is>
@@ -51996,7 +51996,7 @@
         </is>
       </c>
       <c r="C1154" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D1154" t="inlineStr">
         <is>
@@ -72494,6 +72494,26 @@
           <t>Februar</t>
         </is>
       </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>12.02.</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>15.01.</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>19.01.</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>29.01.</t>
+        </is>
+      </c>
       <c r="I210" t="inlineStr">
         <is>
           <t>Hypertonie</t>
@@ -72519,6 +72539,26 @@
           <t>März</t>
         </is>
       </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>16.03.</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>17.02.</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>19.02.</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>02.03.</t>
+        </is>
+      </c>
       <c r="I211" t="inlineStr">
         <is>
           <t>Kardiologie</t>
@@ -72544,6 +72584,26 @@
           <t>Juni</t>
         </is>
       </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>10.06.</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>14.05.</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>18.05.</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>28.05.</t>
+        </is>
+      </c>
       <c r="I212" t="inlineStr">
         <is>
           <t>Adipositas / Diabetes</t>
@@ -72569,6 +72629,26 @@
           <t>September</t>
         </is>
       </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>17.09.</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>24.08.</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>26.08.</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>06.09.</t>
+        </is>
+      </c>
       <c r="I213" t="inlineStr">
         <is>
           <t>Kardiologie</t>
@@ -72594,6 +72674,26 @@
           <t>Oktober</t>
         </is>
       </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>22.10.</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>28.09.</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>30.09.</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>11.10.</t>
+        </is>
+      </c>
       <c r="I214" t="inlineStr">
         <is>
           <t>Neurologie</t>
@@ -72619,6 +72719,26 @@
           <t>Dezember</t>
         </is>
       </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>10.12.</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>16.11.</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>18.11.</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>29.11.</t>
+        </is>
+      </c>
       <c r="I215" t="inlineStr">
         <is>
           <t>Angiologie / Lipidologie</t>
@@ -74641,6 +74761,26 @@
           <t>Februar</t>
         </is>
       </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>26.02.</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>02.02.</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>04.02.</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>16.02.</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -74661,6 +74801,26 @@
           <t>April</t>
         </is>
       </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>23.04.</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>30.03.</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>01.04.</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>13.04.</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -74681,6 +74841,26 @@
           <t>Juni</t>
         </is>
       </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>25.06.</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>02.06.</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>04.06.</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>15.06.</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -74701,6 +74881,26 @@
           <t>September</t>
         </is>
       </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>03.09.</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>11.08.</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>13.08.</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>24.08.</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -74721,6 +74921,26 @@
           <t>Oktober</t>
         </is>
       </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>28.10.</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>05.10.</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>07.10.</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>18.10.</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -74741,6 +74961,26 @@
           <t>Dezember</t>
         </is>
       </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>10.12.</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>17.11.</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>19.11.</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>30.11.</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -74761,6 +75001,21 @@
           <t>Februar</t>
         </is>
       </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>12.02.</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>25.01.</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>29.01.</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -74781,6 +75036,21 @@
           <t>März</t>
         </is>
       </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>12.03.</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>22.02.</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>26.02.</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -74801,6 +75071,21 @@
           <t>April</t>
         </is>
       </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>23.04.</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>05.04.</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>09.04.</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -74821,6 +75106,21 @@
           <t>Mai</t>
         </is>
       </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>21.05.</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>29.04.</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>05.05.</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -74841,6 +75141,21 @@
           <t>Juni</t>
         </is>
       </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>25.06.</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>04.06.</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>10.06.</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -74861,6 +75176,21 @@
           <t>August</t>
         </is>
       </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>13.08.</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>26.07.</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>30.07.</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -74881,6 +75211,21 @@
           <t>September</t>
         </is>
       </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>24.09.</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>06.09.</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>10.09.</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -74901,6 +75246,21 @@
           <t>Oktober</t>
         </is>
       </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>29.10.</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>11.10.</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>15.10.</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -74919,6 +75279,21 @@
       <c r="D280" t="inlineStr">
         <is>
           <t>Dezember</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>10.12.</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>22.11.</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>26.11.</t>
         </is>
       </c>
     </row>

--- a/Angebotsdaten.xlsx
+++ b/Angebotsdaten.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Termine" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Preise'!$A$1:$L$1428</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Preise'!$A$1:$L$1430</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Termine'!$A$1:$J$335</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -591,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1428"/>
+  <dimension ref="A1:L1430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12973,11 +12973,11 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>1/1 Seite 4c</t>
+          <t>2/1 Doppelseite 4c</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>6025</v>
+        <v>11060</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -13019,11 +13019,11 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>1/2 Seite 4c</t>
+          <t>1/1 Seite 4c</t>
         </is>
       </c>
       <c r="F272" t="n">
-        <v>3295</v>
+        <v>6025</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -13065,11 +13065,11 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>1/3 Seite 4c</t>
+          <t>1/2 Seite 4c</t>
         </is>
       </c>
       <c r="F273" t="n">
-        <v>2350</v>
+        <v>3295</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -13111,11 +13111,11 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>1/4 Seite 4c</t>
+          <t>1/3 Seite 4c</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>1885</v>
+        <v>2350</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -13157,11 +13157,11 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2/1 Doppelseite</t>
+          <t>1/4 Seite 4c</t>
         </is>
       </c>
       <c r="F275" t="n">
-        <v>11060</v>
+        <v>1885</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -14854,14 +14854,14 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
+          <t>2/1 Doppelseite</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>3995</v>
+        <v>7990</v>
       </c>
       <c r="G312" t="n">
-        <v>1500</v>
+        <v>2250</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
@@ -14903,14 +14903,14 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>1/2 Seite</t>
+          <t>1/1 Seite</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>2505</v>
+        <v>3995</v>
       </c>
       <c r="G313" t="n">
-        <v>1120</v>
+        <v>1500</v>
       </c>
       <c r="H313" t="inlineStr">
         <is>
@@ -14952,14 +14952,14 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>1/3 Seite</t>
+          <t>1/2 Seite</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>1805</v>
+        <v>2505</v>
       </c>
       <c r="G314" t="n">
-        <v>760</v>
+        <v>1120</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
@@ -15001,11 +15001,11 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>1/4 Seite</t>
+          <t>1/3 Seite</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>1360</v>
+        <v>1805</v>
       </c>
       <c r="G315" t="n">
         <v>760</v>
@@ -15050,14 +15050,14 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2/1 Doppelseite</t>
+          <t>1/4 Seite</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>7990</v>
+        <v>1360</v>
       </c>
       <c r="G316" t="n">
-        <v>2250</v>
+        <v>760</v>
       </c>
       <c r="H316" t="inlineStr">
         <is>
@@ -48962,7 +48962,7 @@
       </c>
       <c r="E1086" t="inlineStr">
         <is>
-          <t>1.rechte Anzeigenseite</t>
+          <t>Seite ggü. Herausgeber 1</t>
         </is>
       </c>
       <c r="F1086" t="n">
@@ -49553,24 +49553,24 @@
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t>PNEUMONEWS</t>
+          <t>Zeitschrift für Pneumologie</t>
         </is>
       </c>
       <c r="C1100" t="n">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1100" t="inlineStr">
         <is>
-          <t>1/1 Seite 4c</t>
+          <t>Seite ggü. Herausgeber 2</t>
         </is>
       </c>
       <c r="F1100" t="n">
-        <v>4100</v>
+        <v>4170</v>
       </c>
       <c r="H1100" t="inlineStr">
         <is>
@@ -49612,11 +49612,11 @@
       </c>
       <c r="E1101" t="inlineStr">
         <is>
-          <t>1/2 Seite 4c</t>
+          <t>1/1 Seite 4c</t>
         </is>
       </c>
       <c r="F1101" t="n">
-        <v>2820</v>
+        <v>4100</v>
       </c>
       <c r="H1101" t="inlineStr">
         <is>
@@ -49658,11 +49658,11 @@
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t>1/3 Seite 4c</t>
+          <t>1/2 Seite 4c</t>
         </is>
       </c>
       <c r="F1102" t="n">
-        <v>1930</v>
+        <v>2820</v>
       </c>
       <c r="H1102" t="inlineStr">
         <is>
@@ -49704,11 +49704,11 @@
       </c>
       <c r="E1103" t="inlineStr">
         <is>
-          <t>1/4 Seite 4c</t>
+          <t>1/3 Seite 4c</t>
         </is>
       </c>
       <c r="F1103" t="n">
-        <v>1730</v>
+        <v>1930</v>
       </c>
       <c r="H1103" t="inlineStr">
         <is>
@@ -49745,16 +49745,16 @@
       </c>
       <c r="D1104" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1104" t="inlineStr">
         <is>
-          <t>2. Umschlagseite</t>
+          <t>1/4 Seite 4c</t>
         </is>
       </c>
       <c r="F1104" t="n">
-        <v>4400</v>
+        <v>1730</v>
       </c>
       <c r="H1104" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
       </c>
       <c r="E1105" t="inlineStr">
         <is>
-          <t>4. Umschlagseite</t>
+          <t>2. Umschlagseite</t>
         </is>
       </c>
       <c r="F1105" t="n">
@@ -49842,7 +49842,7 @@
       </c>
       <c r="E1106" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt</t>
+          <t>4. Umschlagseite</t>
         </is>
       </c>
       <c r="F1106" t="n">
@@ -49883,12 +49883,12 @@
       </c>
       <c r="D1107" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1107" t="inlineStr">
         <is>
-          <t>EH/DH 2 Seiten</t>
+          <t>Seite ggü. Inhalt</t>
         </is>
       </c>
       <c r="F1107" t="n">
@@ -49896,7 +49896,7 @@
       </c>
       <c r="H1107" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="I1107" t="inlineStr">
@@ -49906,7 +49906,7 @@
       </c>
       <c r="J1107" t="inlineStr">
         <is>
-          <t>EH</t>
+          <t>DU</t>
         </is>
       </c>
       <c r="K1107" t="inlineStr">
@@ -49934,11 +49934,11 @@
       </c>
       <c r="E1108" t="inlineStr">
         <is>
-          <t>EH/DH 4 Seiten</t>
+          <t>EH/DH 2 Seiten</t>
         </is>
       </c>
       <c r="F1108" t="n">
-        <v>8800</v>
+        <v>4400</v>
       </c>
       <c r="H1108" t="inlineStr">
         <is>
@@ -49975,16 +49975,16 @@
       </c>
       <c r="D1109" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1109" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (pro 1.000)</t>
+          <t>EH/DH 4 Seiten</t>
         </is>
       </c>
       <c r="F1109" t="n">
-        <v>410</v>
+        <v>8800</v>
       </c>
       <c r="H1109" t="inlineStr">
         <is>
@@ -50021,16 +50021,16 @@
       </c>
       <c r="D1110" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1110" t="inlineStr">
         <is>
-          <t>Titelklappe</t>
+          <t>Werbebeilage bis 25g (pro 1.000)</t>
         </is>
       </c>
       <c r="F1110" t="n">
-        <v>6040</v>
+        <v>410</v>
       </c>
       <c r="H1110" t="inlineStr">
         <is>
@@ -50044,7 +50044,7 @@
       </c>
       <c r="J1110" t="inlineStr">
         <is>
-          <t>DU</t>
+          <t>EH</t>
         </is>
       </c>
       <c r="K1110" t="inlineStr">
@@ -50072,11 +50072,11 @@
       </c>
       <c r="E1111" t="inlineStr">
         <is>
-          <t>French-Cover</t>
+          <t>Titelklappe</t>
         </is>
       </c>
       <c r="F1111" t="n">
-        <v>7600</v>
+        <v>6040</v>
       </c>
       <c r="H1111" t="inlineStr">
         <is>
@@ -50086,6 +50086,11 @@
       <c r="I1111" t="inlineStr">
         <is>
           <t>ja</t>
+        </is>
+      </c>
+      <c r="J1111" t="inlineStr">
+        <is>
+          <t>DU</t>
         </is>
       </c>
       <c r="K1111" t="inlineStr">
@@ -50113,11 +50118,11 @@
       </c>
       <c r="E1112" t="inlineStr">
         <is>
-          <t>halbe ausklappbare 2.US</t>
+          <t>French-Cover</t>
         </is>
       </c>
       <c r="F1112" t="n">
-        <v>6070</v>
+        <v>7600</v>
       </c>
       <c r="H1112" t="inlineStr">
         <is>
@@ -50154,11 +50159,11 @@
       </c>
       <c r="E1113" t="inlineStr">
         <is>
-          <t>ausklappbare 2.US</t>
+          <t>halbe ausklappbare 2.US</t>
         </is>
       </c>
       <c r="F1113" t="n">
-        <v>7600</v>
+        <v>6070</v>
       </c>
       <c r="H1113" t="inlineStr">
         <is>
@@ -50195,11 +50200,11 @@
       </c>
       <c r="E1114" t="inlineStr">
         <is>
-          <t>Sogbanderole</t>
+          <t>ausklappbare 2.US</t>
         </is>
       </c>
       <c r="F1114" t="n">
-        <v>5400</v>
+        <v>7600</v>
       </c>
       <c r="H1114" t="inlineStr">
         <is>
@@ -50236,11 +50241,11 @@
       </c>
       <c r="E1115" t="inlineStr">
         <is>
-          <t>Pfeilbanderole</t>
+          <t>Sogbanderole</t>
         </is>
       </c>
       <c r="F1115" t="n">
-        <v>9670</v>
+        <v>5400</v>
       </c>
       <c r="H1115" t="inlineStr">
         <is>
@@ -50250,11 +50255,6 @@
       <c r="I1115" t="inlineStr">
         <is>
           <t>ja</t>
-        </is>
-      </c>
-      <c r="J1115" t="inlineStr">
-        <is>
-          <t>DU</t>
         </is>
       </c>
       <c r="K1115" t="inlineStr">
@@ -50282,11 +50282,11 @@
       </c>
       <c r="E1116" t="inlineStr">
         <is>
-          <t>Flipp-Einhefter</t>
+          <t>Pfeilbanderole</t>
         </is>
       </c>
       <c r="F1116" t="n">
-        <v>8750</v>
+        <v>9670</v>
       </c>
       <c r="H1116" t="inlineStr">
         <is>
@@ -50296,6 +50296,11 @@
       <c r="I1116" t="inlineStr">
         <is>
           <t>ja</t>
+        </is>
+      </c>
+      <c r="J1116" t="inlineStr">
+        <is>
+          <t>DU</t>
         </is>
       </c>
       <c r="K1116" t="inlineStr">
@@ -50323,11 +50328,11 @@
       </c>
       <c r="E1117" t="inlineStr">
         <is>
-          <t>Tip-On-Element</t>
+          <t>Flipp-Einhefter</t>
         </is>
       </c>
       <c r="F1117" t="n">
-        <v>1490</v>
+        <v>8750</v>
       </c>
       <c r="H1117" t="inlineStr">
         <is>
@@ -50364,11 +50369,11 @@
       </c>
       <c r="E1118" t="inlineStr">
         <is>
-          <t>Oversize-Beilage</t>
+          <t>Tip-On-Element</t>
         </is>
       </c>
       <c r="F1118" t="n">
-        <v>4000</v>
+        <v>1490</v>
       </c>
       <c r="H1118" t="inlineStr">
         <is>
@@ -50405,11 +50410,11 @@
       </c>
       <c r="E1119" t="inlineStr">
         <is>
-          <t>Lesezeichen mit Bändchen</t>
+          <t>Oversize-Beilage</t>
         </is>
       </c>
       <c r="F1119" t="n">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="H1119" t="inlineStr">
         <is>
@@ -50433,28 +50438,28 @@
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t>Cardio News</t>
+          <t>PNEUMONEWS</t>
         </is>
       </c>
       <c r="C1120" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1120" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1120" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
+          <t>Lesezeichen mit Bändchen</t>
         </is>
       </c>
       <c r="F1120" t="n">
-        <v>7760</v>
+        <v>3500</v>
       </c>
       <c r="H1120" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="I1120" t="inlineStr">
@@ -50462,14 +50467,9 @@
           <t>ja</t>
         </is>
       </c>
-      <c r="J1120" t="inlineStr">
-        <is>
-          <t>DU</t>
-        </is>
-      </c>
       <c r="K1120" t="inlineStr">
         <is>
-          <t>Kardiologie</t>
+          <t>Pneumologie</t>
         </is>
       </c>
     </row>
@@ -50479,24 +50479,24 @@
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t>Cardio News</t>
+          <t>PNEUMONEWS</t>
         </is>
       </c>
       <c r="C1121" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1121" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1121" t="inlineStr">
         <is>
-          <t>A4 hoch</t>
+          <t>Seite ggü. Inhalt Journal Screen</t>
         </is>
       </c>
       <c r="F1121" t="n">
-        <v>6720</v>
+        <v>4400</v>
       </c>
       <c r="H1121" t="inlineStr">
         <is>
@@ -50515,7 +50515,7 @@
       </c>
       <c r="K1121" t="inlineStr">
         <is>
-          <t>Kardiologie</t>
+          <t>Pneumologie</t>
         </is>
       </c>
     </row>
@@ -50538,11 +50538,11 @@
       </c>
       <c r="E1122" t="inlineStr">
         <is>
-          <t>3/4 Seite</t>
+          <t>1/1 Seite</t>
         </is>
       </c>
       <c r="F1122" t="n">
-        <v>7400</v>
+        <v>7760</v>
       </c>
       <c r="H1122" t="inlineStr">
         <is>
@@ -50584,11 +50584,11 @@
       </c>
       <c r="E1123" t="inlineStr">
         <is>
-          <t>3/5 Seite</t>
+          <t>A4 hoch</t>
         </is>
       </c>
       <c r="F1123" t="n">
-        <v>6100</v>
+        <v>6720</v>
       </c>
       <c r="H1123" t="inlineStr">
         <is>
@@ -50630,11 +50630,11 @@
       </c>
       <c r="E1124" t="inlineStr">
         <is>
-          <t>2/3 Seite</t>
+          <t>3/4 Seite</t>
         </is>
       </c>
       <c r="F1124" t="n">
-        <v>6000</v>
+        <v>7400</v>
       </c>
       <c r="H1124" t="inlineStr">
         <is>
@@ -50676,11 +50676,11 @@
       </c>
       <c r="E1125" t="inlineStr">
         <is>
-          <t>1/2 Seite</t>
+          <t>3/5 Seite</t>
         </is>
       </c>
       <c r="F1125" t="n">
-        <v>4900</v>
+        <v>6100</v>
       </c>
       <c r="H1125" t="inlineStr">
         <is>
@@ -50722,11 +50722,11 @@
       </c>
       <c r="E1126" t="inlineStr">
         <is>
-          <t>2/5 Seite</t>
+          <t>2/3 Seite</t>
         </is>
       </c>
       <c r="F1126" t="n">
-        <v>4380</v>
+        <v>6000</v>
       </c>
       <c r="H1126" t="inlineStr">
         <is>
@@ -50768,11 +50768,11 @@
       </c>
       <c r="E1127" t="inlineStr">
         <is>
-          <t>1/3 Seite</t>
+          <t>1/2 Seite</t>
         </is>
       </c>
       <c r="F1127" t="n">
-        <v>3700</v>
+        <v>4900</v>
       </c>
       <c r="H1127" t="inlineStr">
         <is>
@@ -50814,11 +50814,11 @@
       </c>
       <c r="E1128" t="inlineStr">
         <is>
-          <t>1/4 Seite</t>
+          <t>2/5 Seite</t>
         </is>
       </c>
       <c r="F1128" t="n">
-        <v>3690</v>
+        <v>4380</v>
       </c>
       <c r="H1128" t="inlineStr">
         <is>
@@ -50860,11 +50860,11 @@
       </c>
       <c r="E1129" t="inlineStr">
         <is>
-          <t>2/10 Seite</t>
+          <t>1/3 Seite</t>
         </is>
       </c>
       <c r="F1129" t="n">
-        <v>3590</v>
+        <v>3700</v>
       </c>
       <c r="H1129" t="inlineStr">
         <is>
@@ -50906,11 +50906,11 @@
       </c>
       <c r="E1130" t="inlineStr">
         <is>
-          <t>Tunnel groß</t>
+          <t>1/4 Seite</t>
         </is>
       </c>
       <c r="F1130" t="n">
-        <v>4690</v>
+        <v>3690</v>
       </c>
       <c r="H1130" t="inlineStr">
         <is>
@@ -50952,11 +50952,11 @@
       </c>
       <c r="E1131" t="inlineStr">
         <is>
-          <t>Insel maxi</t>
+          <t>2/10 Seite</t>
         </is>
       </c>
       <c r="F1131" t="n">
-        <v>4990</v>
+        <v>3590</v>
       </c>
       <c r="H1131" t="inlineStr">
         <is>
@@ -50993,16 +50993,16 @@
       </c>
       <c r="D1132" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1132" t="inlineStr">
         <is>
-          <t>Seite 2 A4</t>
+          <t>Tunnel groß</t>
         </is>
       </c>
       <c r="F1132" t="n">
-        <v>8170</v>
+        <v>4690</v>
       </c>
       <c r="H1132" t="inlineStr">
         <is>
@@ -51039,16 +51039,16 @@
       </c>
       <c r="D1133" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1133" t="inlineStr">
         <is>
-          <t>Seite 5 1/1</t>
+          <t>Insel maxi</t>
         </is>
       </c>
       <c r="F1133" t="n">
-        <v>8650</v>
+        <v>4990</v>
       </c>
       <c r="H1133" t="inlineStr">
         <is>
@@ -51090,11 +51090,11 @@
       </c>
       <c r="E1134" t="inlineStr">
         <is>
-          <t>Seite 5 A4</t>
+          <t>Seite 2 A4</t>
         </is>
       </c>
       <c r="F1134" t="n">
-        <v>7400</v>
+        <v>8170</v>
       </c>
       <c r="H1134" t="inlineStr">
         <is>
@@ -51136,11 +51136,11 @@
       </c>
       <c r="E1135" t="inlineStr">
         <is>
-          <t>Letzte Seite 1/1</t>
+          <t>Seite 5 1/1</t>
         </is>
       </c>
       <c r="F1135" t="n">
-        <v>8200</v>
+        <v>8650</v>
       </c>
       <c r="H1135" t="inlineStr">
         <is>
@@ -51182,11 +51182,11 @@
       </c>
       <c r="E1136" t="inlineStr">
         <is>
-          <t>Letzte Seite A4</t>
+          <t>Seite 5 A4</t>
         </is>
       </c>
       <c r="F1136" t="n">
-        <v>7080</v>
+        <v>7400</v>
       </c>
       <c r="H1136" t="inlineStr">
         <is>
@@ -51223,25 +51223,30 @@
       </c>
       <c r="D1137" t="inlineStr">
         <is>
-          <t>AdSpecials</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1137" t="inlineStr">
         <is>
-          <t>Banderole</t>
+          <t>Letzte Seite 1/1</t>
         </is>
       </c>
       <c r="F1137" t="n">
-        <v>9990</v>
+        <v>8200</v>
       </c>
       <c r="H1137" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="I1137" t="inlineStr">
         <is>
           <t>ja</t>
+        </is>
+      </c>
+      <c r="J1137" t="inlineStr">
+        <is>
+          <t>DU</t>
         </is>
       </c>
       <c r="K1137" t="inlineStr">
@@ -51256,24 +51261,24 @@
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t>DGU Kongresszeitung</t>
+          <t>Cardio News</t>
         </is>
       </c>
       <c r="C1138" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D1138" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1138" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
+          <t>Letzte Seite A4</t>
         </is>
       </c>
       <c r="F1138" t="n">
-        <v>6100</v>
+        <v>7080</v>
       </c>
       <c r="H1138" t="inlineStr">
         <is>
@@ -51292,7 +51297,7 @@
       </c>
       <c r="K1138" t="inlineStr">
         <is>
-          <t>Urologie</t>
+          <t>Kardiologie</t>
         </is>
       </c>
     </row>
@@ -51302,28 +51307,28 @@
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>DGU Kongresszeitung</t>
+          <t>Cardio News</t>
         </is>
       </c>
       <c r="C1139" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D1139" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>AdSpecials</t>
         </is>
       </c>
       <c r="E1139" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>Banderole</t>
         </is>
       </c>
       <c r="F1139" t="n">
-        <v>5540</v>
+        <v>9990</v>
       </c>
       <c r="H1139" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="I1139" t="inlineStr">
@@ -51331,14 +51336,9 @@
           <t>ja</t>
         </is>
       </c>
-      <c r="J1139" t="inlineStr">
-        <is>
-          <t>DU</t>
-        </is>
-      </c>
       <c r="K1139" t="inlineStr">
         <is>
-          <t>Urologie</t>
+          <t>Kardiologie</t>
         </is>
       </c>
     </row>
@@ -51361,11 +51361,11 @@
       </c>
       <c r="E1140" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>1/1 Seite</t>
         </is>
       </c>
       <c r="F1140" t="n">
-        <v>4150</v>
+        <v>6100</v>
       </c>
       <c r="H1140" t="inlineStr">
         <is>
@@ -51407,11 +51407,11 @@
       </c>
       <c r="E1141" t="inlineStr">
         <is>
-          <t>3/4 Seite quer</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="F1141" t="n">
-        <v>5630</v>
+        <v>5540</v>
       </c>
       <c r="H1141" t="inlineStr">
         <is>
@@ -51453,11 +51453,11 @@
       </c>
       <c r="E1142" t="inlineStr">
         <is>
-          <t>1/2 Seite</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="F1142" t="n">
-        <v>5250</v>
+        <v>4150</v>
       </c>
       <c r="H1142" t="inlineStr">
         <is>
@@ -51499,11 +51499,11 @@
       </c>
       <c r="E1143" t="inlineStr">
         <is>
-          <t>1/4 seite</t>
+          <t>3/4 Seite quer</t>
         </is>
       </c>
       <c r="F1143" t="n">
-        <v>2850</v>
+        <v>5630</v>
       </c>
       <c r="H1143" t="inlineStr">
         <is>
@@ -51540,16 +51540,16 @@
       </c>
       <c r="D1144" t="inlineStr">
         <is>
-          <t>Sonderplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1144" t="inlineStr">
         <is>
-          <t>Titelseitenfuß</t>
+          <t>1/2 Seite</t>
         </is>
       </c>
       <c r="F1144" t="n">
-        <v>5300</v>
+        <v>5250</v>
       </c>
       <c r="H1144" t="inlineStr">
         <is>
@@ -51586,20 +51586,20 @@
       </c>
       <c r="D1145" t="inlineStr">
         <is>
-          <t>Sonderplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1145" t="inlineStr">
         <is>
-          <t>Insel</t>
+          <t>1/4 seite</t>
         </is>
       </c>
       <c r="F1145" t="n">
-        <v>3260</v>
+        <v>2850</v>
       </c>
       <c r="H1145" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="I1145" t="inlineStr">
@@ -51637,7 +51637,7 @@
       </c>
       <c r="E1146" t="inlineStr">
         <is>
-          <t>Insel maxi</t>
+          <t>Titelseitenfuß</t>
         </is>
       </c>
       <c r="F1146" t="n">
@@ -51645,7 +51645,7 @@
       </c>
       <c r="H1146" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="I1146" t="inlineStr">
@@ -51683,11 +51683,11 @@
       </c>
       <c r="E1147" t="inlineStr">
         <is>
-          <t>Tunnel klein</t>
+          <t>Insel</t>
         </is>
       </c>
       <c r="F1147" t="n">
-        <v>2930</v>
+        <v>3260</v>
       </c>
       <c r="H1147" t="inlineStr">
         <is>
@@ -51729,11 +51729,11 @@
       </c>
       <c r="E1148" t="inlineStr">
         <is>
-          <t>Tunnel groß</t>
+          <t>Insel maxi</t>
         </is>
       </c>
       <c r="F1148" t="n">
-        <v>4160</v>
+        <v>5300</v>
       </c>
       <c r="H1148" t="inlineStr">
         <is>
@@ -51775,11 +51775,11 @@
       </c>
       <c r="E1149" t="inlineStr">
         <is>
-          <t>Großumleger</t>
+          <t>Tunnel klein</t>
         </is>
       </c>
       <c r="F1149" t="n">
-        <v>18500</v>
+        <v>2930</v>
       </c>
       <c r="H1149" t="inlineStr">
         <is>
@@ -51821,11 +51821,11 @@
       </c>
       <c r="E1150" t="inlineStr">
         <is>
-          <t>Titelseite + 2.Seite</t>
+          <t>Tunnel groß</t>
         </is>
       </c>
       <c r="F1150" t="n">
-        <v>14900</v>
+        <v>4160</v>
       </c>
       <c r="H1150" t="inlineStr">
         <is>
@@ -51867,11 +51867,11 @@
       </c>
       <c r="E1151" t="inlineStr">
         <is>
-          <t>Transparenzumleger</t>
+          <t>Großumleger</t>
         </is>
       </c>
       <c r="F1151" t="n">
-        <v>14900</v>
+        <v>18500</v>
       </c>
       <c r="H1151" t="inlineStr">
         <is>
@@ -51913,11 +51913,11 @@
       </c>
       <c r="E1152" t="inlineStr">
         <is>
-          <t>Banderole</t>
+          <t>Titelseite + 2.Seite</t>
         </is>
       </c>
       <c r="F1152" t="n">
-        <v>5100</v>
+        <v>14900</v>
       </c>
       <c r="H1152" t="inlineStr">
         <is>
@@ -51931,7 +51931,7 @@
       </c>
       <c r="J1152" t="inlineStr">
         <is>
-          <t>EH</t>
+          <t>DU</t>
         </is>
       </c>
       <c r="K1152" t="inlineStr">
@@ -51959,11 +51959,11 @@
       </c>
       <c r="E1153" t="inlineStr">
         <is>
-          <t>Aufkleber + Trägeranzeige</t>
+          <t>Transparenzumleger</t>
         </is>
       </c>
       <c r="F1153" t="n">
-        <v>2300</v>
+        <v>14900</v>
       </c>
       <c r="H1153" t="inlineStr">
         <is>
@@ -51977,7 +51977,7 @@
       </c>
       <c r="J1153" t="inlineStr">
         <is>
-          <t>EH</t>
+          <t>DU</t>
         </is>
       </c>
       <c r="K1153" t="inlineStr">
@@ -52000,16 +52000,16 @@
       </c>
       <c r="D1154" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Sonderplatzierungen</t>
         </is>
       </c>
       <c r="E1154" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (pro 1.000)</t>
+          <t>Banderole</t>
         </is>
       </c>
       <c r="F1154" t="n">
-        <v>580</v>
+        <v>5100</v>
       </c>
       <c r="H1154" t="inlineStr">
         <is>
@@ -52034,25 +52034,28 @@
     </row>
     <row r="1155">
       <c r="A1155" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t>Die Onkologie</t>
+          <t>DGU Kongresszeitung</t>
         </is>
       </c>
       <c r="C1155" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="D1155" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderplatzierungen</t>
         </is>
       </c>
       <c r="E1155" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
-        </is>
+          <t>Aufkleber + Trägeranzeige</t>
+        </is>
+      </c>
+      <c r="F1155" t="n">
+        <v>2300</v>
       </c>
       <c r="H1155" t="inlineStr">
         <is>
@@ -52064,33 +52067,41 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J1155" t="inlineStr">
+        <is>
+          <t>EH</t>
+        </is>
+      </c>
       <c r="K1155" t="inlineStr">
         <is>
-          <t>Onkologie</t>
+          <t>Urologie</t>
         </is>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t>Die Onkologie</t>
+          <t>DGU Kongresszeitung</t>
         </is>
       </c>
       <c r="C1156" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="D1156" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1156" t="inlineStr">
         <is>
-          <t>1/2 Seite</t>
-        </is>
+          <t>Werbebeilage bis 25g (pro 1.000)</t>
+        </is>
+      </c>
+      <c r="F1156" t="n">
+        <v>580</v>
       </c>
       <c r="H1156" t="inlineStr">
         <is>
@@ -52102,9 +52113,14 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J1156" t="inlineStr">
+        <is>
+          <t>EH</t>
+        </is>
+      </c>
       <c r="K1156" t="inlineStr">
         <is>
-          <t>Onkologie</t>
+          <t>Urologie</t>
         </is>
       </c>
     </row>
@@ -52127,7 +52143,7 @@
       </c>
       <c r="E1157" t="inlineStr">
         <is>
-          <t>1/3 Seite</t>
+          <t>1/1 Seite</t>
         </is>
       </c>
       <c r="H1157" t="inlineStr">
@@ -52165,7 +52181,7 @@
       </c>
       <c r="E1158" t="inlineStr">
         <is>
-          <t>1/4 Seite</t>
+          <t>1/2 Seite</t>
         </is>
       </c>
       <c r="H1158" t="inlineStr">
@@ -52203,7 +52219,7 @@
       </c>
       <c r="E1159" t="inlineStr">
         <is>
-          <t>2/1 Doppelseite</t>
+          <t>1/3 Seite</t>
         </is>
       </c>
       <c r="H1159" t="inlineStr">
@@ -52241,7 +52257,7 @@
       </c>
       <c r="E1160" t="inlineStr">
         <is>
-          <t>Advertorial (1/1 Seite)</t>
+          <t>1/4 Seite</t>
         </is>
       </c>
       <c r="H1160" t="inlineStr">
@@ -52274,12 +52290,12 @@
       </c>
       <c r="D1161" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1161" t="inlineStr">
         <is>
-          <t>4. Umschlagseite</t>
+          <t>2/1 Doppelseite</t>
         </is>
       </c>
       <c r="H1161" t="inlineStr">
@@ -52312,12 +52328,12 @@
       </c>
       <c r="D1162" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1162" t="inlineStr">
         <is>
-          <t>2. Umschlagseite</t>
+          <t>Advertorial (1/1 Seite)</t>
         </is>
       </c>
       <c r="H1162" t="inlineStr">
@@ -52355,7 +52371,7 @@
       </c>
       <c r="E1163" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt / red. Info</t>
+          <t>4. Umschlagseite</t>
         </is>
       </c>
       <c r="H1163" t="inlineStr">
@@ -52393,7 +52409,7 @@
       </c>
       <c r="E1164" t="inlineStr">
         <is>
-          <t>Seite ggü. Hrsg. 1</t>
+          <t>2. Umschlagseite</t>
         </is>
       </c>
       <c r="H1164" t="inlineStr">
@@ -52431,7 +52447,7 @@
       </c>
       <c r="E1165" t="inlineStr">
         <is>
-          <t>Seite ggü. Hrsg. 2</t>
+          <t>Seite ggü. Inhalt / red. Info</t>
         </is>
       </c>
       <c r="H1165" t="inlineStr">
@@ -52469,7 +52485,7 @@
       </c>
       <c r="E1166" t="inlineStr">
         <is>
-          <t>Seite ggü. Textanfang</t>
+          <t>Seite ggü. Hrsg. 1</t>
         </is>
       </c>
       <c r="H1166" t="inlineStr">
@@ -52507,7 +52523,7 @@
       </c>
       <c r="E1167" t="inlineStr">
         <is>
-          <t>1/1 Seite Festplatzierung</t>
+          <t>Seite ggü. Hrsg. 2</t>
         </is>
       </c>
       <c r="H1167" t="inlineStr">
@@ -52545,7 +52561,7 @@
       </c>
       <c r="E1168" t="inlineStr">
         <is>
-          <t>1. rechte Einschaltseite</t>
+          <t>Seite ggü. Textanfang</t>
         </is>
       </c>
       <c r="H1168" t="inlineStr">
@@ -52583,7 +52599,7 @@
       </c>
       <c r="E1169" t="inlineStr">
         <is>
-          <t>2. rechte Einschaltseite</t>
+          <t>1/1 Seite Festplatzierung</t>
         </is>
       </c>
       <c r="H1169" t="inlineStr">
@@ -52621,7 +52637,7 @@
       </c>
       <c r="E1170" t="inlineStr">
         <is>
-          <t>3. rechte Einschaltseite</t>
+          <t>1. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1170" t="inlineStr">
@@ -52659,7 +52675,7 @@
       </c>
       <c r="E1171" t="inlineStr">
         <is>
-          <t>4. rechte Einschaltseite</t>
+          <t>2. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1171" t="inlineStr">
@@ -52697,7 +52713,7 @@
       </c>
       <c r="E1172" t="inlineStr">
         <is>
-          <t>5. rechte Einschaltseite</t>
+          <t>3. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1172" t="inlineStr">
@@ -52735,7 +52751,7 @@
       </c>
       <c r="E1173" t="inlineStr">
         <is>
-          <t>6. rechte Einschaltseite</t>
+          <t>4. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1173" t="inlineStr">
@@ -52773,7 +52789,7 @@
       </c>
       <c r="E1174" t="inlineStr">
         <is>
-          <t>7. rechte Einschaltseite</t>
+          <t>5. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1174" t="inlineStr">
@@ -52811,7 +52827,7 @@
       </c>
       <c r="E1175" t="inlineStr">
         <is>
-          <t>8. rechte Einschaltseite</t>
+          <t>6. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1175" t="inlineStr">
@@ -52849,7 +52865,7 @@
       </c>
       <c r="E1176" t="inlineStr">
         <is>
-          <t>9. rechte Einschaltseite</t>
+          <t>7. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1176" t="inlineStr">
@@ -52887,7 +52903,7 @@
       </c>
       <c r="E1177" t="inlineStr">
         <is>
-          <t>10. rechte Einschaltseite</t>
+          <t>8. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1177" t="inlineStr">
@@ -52920,12 +52936,12 @@
       </c>
       <c r="D1178" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1178" t="inlineStr">
         <is>
-          <t>EH/DH 1 Seite</t>
+          <t>9. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1178" t="inlineStr">
@@ -52958,12 +52974,12 @@
       </c>
       <c r="D1179" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1179" t="inlineStr">
         <is>
-          <t>EH/DH 2 Seiten</t>
+          <t>10. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1179" t="inlineStr">
@@ -53001,7 +53017,7 @@
       </c>
       <c r="E1180" t="inlineStr">
         <is>
-          <t>EH/DH 4 Seiten</t>
+          <t>EH/DH 1 Seite</t>
         </is>
       </c>
       <c r="H1180" t="inlineStr">
@@ -53039,7 +53055,7 @@
       </c>
       <c r="E1181" t="inlineStr">
         <is>
-          <t>V-Koop MWO/Wefra</t>
+          <t>EH/DH 2 Seiten</t>
         </is>
       </c>
       <c r="H1181" t="inlineStr">
@@ -53072,12 +53088,12 @@
       </c>
       <c r="D1182" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1182" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (pro 1.000)</t>
+          <t>EH/DH 4 Seiten</t>
         </is>
       </c>
       <c r="H1182" t="inlineStr">
@@ -53110,12 +53126,12 @@
       </c>
       <c r="D1183" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1183" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (gesamt)</t>
+          <t>V-Koop MWO/Wefra</t>
         </is>
       </c>
       <c r="H1183" t="inlineStr">
@@ -53153,7 +53169,7 @@
       </c>
       <c r="E1184" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 50g (gesamt)</t>
+          <t>Werbebeilage bis 25g (pro 1.000)</t>
         </is>
       </c>
       <c r="H1184" t="inlineStr">
@@ -53186,12 +53202,12 @@
       </c>
       <c r="D1185" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1185" t="inlineStr">
         <is>
-          <t>Titelseitenklappe</t>
+          <t>Werbebeilage bis 25g (gesamt)</t>
         </is>
       </c>
       <c r="H1185" t="inlineStr">
@@ -53224,12 +53240,12 @@
       </c>
       <c r="D1186" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1186" t="inlineStr">
         <is>
-          <t>French Cover</t>
+          <t>Werbebeilage bis 50g (gesamt)</t>
         </is>
       </c>
       <c r="H1186" t="inlineStr">
@@ -53267,7 +53283,7 @@
       </c>
       <c r="E1187" t="inlineStr">
         <is>
-          <t>ausklappbare 2. US</t>
+          <t>Titelseitenklappe</t>
         </is>
       </c>
       <c r="H1187" t="inlineStr">
@@ -53305,7 +53321,7 @@
       </c>
       <c r="E1188" t="inlineStr">
         <is>
-          <t>1/2 ausklappbare 2. US</t>
+          <t>French Cover</t>
         </is>
       </c>
       <c r="H1188" t="inlineStr">
@@ -53343,7 +53359,7 @@
       </c>
       <c r="E1189" t="inlineStr">
         <is>
-          <t>Banderole (umlaufend)</t>
+          <t>ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1189" t="inlineStr">
@@ -53381,7 +53397,7 @@
       </c>
       <c r="E1190" t="inlineStr">
         <is>
-          <t>Sogbanderole</t>
+          <t>1/2 ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1190" t="inlineStr">
@@ -53419,7 +53435,7 @@
       </c>
       <c r="E1191" t="inlineStr">
         <is>
-          <t>Zangenbanderole</t>
+          <t>Banderole (umlaufend)</t>
         </is>
       </c>
       <c r="H1191" t="inlineStr">
@@ -53457,7 +53473,7 @@
       </c>
       <c r="E1192" t="inlineStr">
         <is>
-          <t>Pfeilbanderole</t>
+          <t>Sogbanderole</t>
         </is>
       </c>
       <c r="H1192" t="inlineStr">
@@ -53495,7 +53511,7 @@
       </c>
       <c r="E1193" t="inlineStr">
         <is>
-          <t>Oversize-Beilage</t>
+          <t>Zangenbanderole</t>
         </is>
       </c>
       <c r="H1193" t="inlineStr">
@@ -53533,7 +53549,7 @@
       </c>
       <c r="E1194" t="inlineStr">
         <is>
-          <t>Lesezeichen (unbestimmte Stelle)</t>
+          <t>Pfeilbanderole</t>
         </is>
       </c>
       <c r="H1194" t="inlineStr">
@@ -53571,7 +53587,7 @@
       </c>
       <c r="E1195" t="inlineStr">
         <is>
-          <t>Lesezeichen (bestimmte Stelle)</t>
+          <t>Oversize-Beilage</t>
         </is>
       </c>
       <c r="H1195" t="inlineStr">
@@ -53604,12 +53620,12 @@
       </c>
       <c r="D1196" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1196" t="inlineStr">
         <is>
-          <t>Klappohr-Einhefter</t>
+          <t>Lesezeichen (unbestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1196" t="inlineStr">
@@ -53642,12 +53658,12 @@
       </c>
       <c r="D1197" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1197" t="inlineStr">
         <is>
-          <t>gestanzter Einhefter</t>
+          <t>Lesezeichen (bestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1197" t="inlineStr">
@@ -53685,7 +53701,7 @@
       </c>
       <c r="E1198" t="inlineStr">
         <is>
-          <t>perforierter Einhefter</t>
+          <t>Klappohr-Einhefter</t>
         </is>
       </c>
       <c r="H1198" t="inlineStr">
@@ -53723,7 +53739,7 @@
       </c>
       <c r="E1199" t="inlineStr">
         <is>
-          <t>Einhefter mit Klappe</t>
+          <t>gestanzter Einhefter</t>
         </is>
       </c>
       <c r="H1199" t="inlineStr">
@@ -53761,7 +53777,7 @@
       </c>
       <c r="E1200" t="inlineStr">
         <is>
-          <t>Flip-Einhefter</t>
+          <t>perforierter Einhefter</t>
         </is>
       </c>
       <c r="H1200" t="inlineStr">
@@ -53786,20 +53802,20 @@
       </c>
       <c r="B1201" t="inlineStr">
         <is>
-          <t>best practice onkologie</t>
+          <t>Die Onkologie</t>
         </is>
       </c>
       <c r="C1201" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="D1201" t="inlineStr">
         <is>
-          <t>Normalplatzierungen (4c inkl.)</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1201" t="inlineStr">
         <is>
-          <t>1/1 Seite 4c</t>
+          <t>Einhefter mit Klappe</t>
         </is>
       </c>
       <c r="H1201" t="inlineStr">
@@ -53824,20 +53840,20 @@
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t>best practice onkologie</t>
+          <t>Die Onkologie</t>
         </is>
       </c>
       <c r="C1202" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="D1202" t="inlineStr">
         <is>
-          <t>Normalplatzierungen (4c inkl.)</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1202" t="inlineStr">
         <is>
-          <t>1/2 Seite 4c</t>
+          <t>Flip-Einhefter</t>
         </is>
       </c>
       <c r="H1202" t="inlineStr">
@@ -53875,7 +53891,7 @@
       </c>
       <c r="E1203" t="inlineStr">
         <is>
-          <t>1/3 Seite 4c</t>
+          <t>1/1 Seite 4c</t>
         </is>
       </c>
       <c r="H1203" t="inlineStr">
@@ -53913,7 +53929,7 @@
       </c>
       <c r="E1204" t="inlineStr">
         <is>
-          <t>1/4 Seite 4c</t>
+          <t>1/2 Seite 4c</t>
         </is>
       </c>
       <c r="H1204" t="inlineStr">
@@ -53951,7 +53967,7 @@
       </c>
       <c r="E1205" t="inlineStr">
         <is>
-          <t>2/1 Doppelseite</t>
+          <t>1/3 Seite 4c</t>
         </is>
       </c>
       <c r="H1205" t="inlineStr">
@@ -53989,7 +54005,7 @@
       </c>
       <c r="E1206" t="inlineStr">
         <is>
-          <t>Advertorial (1/1 Seite 4c)</t>
+          <t>1/4 Seite 4c</t>
         </is>
       </c>
       <c r="H1206" t="inlineStr">
@@ -54022,12 +54038,12 @@
       </c>
       <c r="D1207" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen (4c inkl.)</t>
+          <t>Normalplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1207" t="inlineStr">
         <is>
-          <t>4. Umschlagseite</t>
+          <t>2/1 Doppelseite</t>
         </is>
       </c>
       <c r="H1207" t="inlineStr">
@@ -54060,12 +54076,12 @@
       </c>
       <c r="D1208" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen (4c inkl.)</t>
+          <t>Normalplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1208" t="inlineStr">
         <is>
-          <t>2. Umschlagseite</t>
+          <t>Advertorial (1/1 Seite 4c)</t>
         </is>
       </c>
       <c r="H1208" t="inlineStr">
@@ -54103,7 +54119,7 @@
       </c>
       <c r="E1209" t="inlineStr">
         <is>
-          <t>Seite ggü. red. Info / Inhalt</t>
+          <t>4. Umschlagseite</t>
         </is>
       </c>
       <c r="H1209" t="inlineStr">
@@ -54141,7 +54157,7 @@
       </c>
       <c r="E1210" t="inlineStr">
         <is>
-          <t>Seite ggü. Hrsg.</t>
+          <t>2. Umschlagseite</t>
         </is>
       </c>
       <c r="H1210" t="inlineStr">
@@ -54179,7 +54195,7 @@
       </c>
       <c r="E1211" t="inlineStr">
         <is>
-          <t>Seite ggü. Editorial</t>
+          <t>Seite ggü. red. Info / Inhalt</t>
         </is>
       </c>
       <c r="H1211" t="inlineStr">
@@ -54217,7 +54233,7 @@
       </c>
       <c r="E1212" t="inlineStr">
         <is>
-          <t>Seite ggü. Textanfang</t>
+          <t>Seite ggü. Hrsg.</t>
         </is>
       </c>
       <c r="H1212" t="inlineStr">
@@ -54255,7 +54271,7 @@
       </c>
       <c r="E1213" t="inlineStr">
         <is>
-          <t>1/1 Seite 4c Festplatzierung</t>
+          <t>Seite ggü. Editorial</t>
         </is>
       </c>
       <c r="H1213" t="inlineStr">
@@ -54293,7 +54309,7 @@
       </c>
       <c r="E1214" t="inlineStr">
         <is>
-          <t>1. rechte Einschaltseite</t>
+          <t>Seite ggü. Textanfang</t>
         </is>
       </c>
       <c r="H1214" t="inlineStr">
@@ -54331,7 +54347,7 @@
       </c>
       <c r="E1215" t="inlineStr">
         <is>
-          <t>2. rechte Einschaltseite</t>
+          <t>1/1 Seite 4c Festplatzierung</t>
         </is>
       </c>
       <c r="H1215" t="inlineStr">
@@ -54369,7 +54385,7 @@
       </c>
       <c r="E1216" t="inlineStr">
         <is>
-          <t>3. rechte Einschaltseite</t>
+          <t>1. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1216" t="inlineStr">
@@ -54407,7 +54423,7 @@
       </c>
       <c r="E1217" t="inlineStr">
         <is>
-          <t>4. rechte Einschaltseite</t>
+          <t>2. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1217" t="inlineStr">
@@ -54445,7 +54461,7 @@
       </c>
       <c r="E1218" t="inlineStr">
         <is>
-          <t>5. rechte Einschaltseite</t>
+          <t>3. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1218" t="inlineStr">
@@ -54483,7 +54499,7 @@
       </c>
       <c r="E1219" t="inlineStr">
         <is>
-          <t>6. rechte Einschaltseite</t>
+          <t>4. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1219" t="inlineStr">
@@ -54521,7 +54537,7 @@
       </c>
       <c r="E1220" t="inlineStr">
         <is>
-          <t>7. rechte Einschaltseite</t>
+          <t>5. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1220" t="inlineStr">
@@ -54559,7 +54575,7 @@
       </c>
       <c r="E1221" t="inlineStr">
         <is>
-          <t>8. rechte Einschaltseite</t>
+          <t>6. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1221" t="inlineStr">
@@ -54597,7 +54613,7 @@
       </c>
       <c r="E1222" t="inlineStr">
         <is>
-          <t>9. rechte Einschaltseite</t>
+          <t>7. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1222" t="inlineStr">
@@ -54635,7 +54651,7 @@
       </c>
       <c r="E1223" t="inlineStr">
         <is>
-          <t>10. rechte Einschaltseite</t>
+          <t>8. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1223" t="inlineStr">
@@ -54668,12 +54684,12 @@
       </c>
       <c r="D1224" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1224" t="inlineStr">
         <is>
-          <t>EH/DH 1 Seite</t>
+          <t>9. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1224" t="inlineStr">
@@ -54706,12 +54722,12 @@
       </c>
       <c r="D1225" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1225" t="inlineStr">
         <is>
-          <t>EH/DH 2 Seiten</t>
+          <t>10. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1225" t="inlineStr">
@@ -54749,7 +54765,7 @@
       </c>
       <c r="E1226" t="inlineStr">
         <is>
-          <t>EH/DH 4 Seiten</t>
+          <t>EH/DH 1 Seite</t>
         </is>
       </c>
       <c r="H1226" t="inlineStr">
@@ -54787,7 +54803,7 @@
       </c>
       <c r="E1227" t="inlineStr">
         <is>
-          <t>V-Koop MWO/Wefra</t>
+          <t>EH/DH 2 Seiten</t>
         </is>
       </c>
       <c r="H1227" t="inlineStr">
@@ -54820,12 +54836,12 @@
       </c>
       <c r="D1228" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1228" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (pro 1.000)</t>
+          <t>EH/DH 4 Seiten</t>
         </is>
       </c>
       <c r="H1228" t="inlineStr">
@@ -54858,12 +54874,12 @@
       </c>
       <c r="D1229" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1229" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (gesamt)</t>
+          <t>V-Koop MWO/Wefra</t>
         </is>
       </c>
       <c r="H1229" t="inlineStr">
@@ -54901,7 +54917,7 @@
       </c>
       <c r="E1230" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 50g (gesamt)</t>
+          <t>Werbebeilage bis 25g (pro 1.000)</t>
         </is>
       </c>
       <c r="H1230" t="inlineStr">
@@ -54934,12 +54950,12 @@
       </c>
       <c r="D1231" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1231" t="inlineStr">
         <is>
-          <t>Titelseitenklappe</t>
+          <t>Werbebeilage bis 25g (gesamt)</t>
         </is>
       </c>
       <c r="H1231" t="inlineStr">
@@ -54972,12 +54988,12 @@
       </c>
       <c r="D1232" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1232" t="inlineStr">
         <is>
-          <t>French Cover</t>
+          <t>Werbebeilage bis 50g (gesamt)</t>
         </is>
       </c>
       <c r="H1232" t="inlineStr">
@@ -55015,7 +55031,7 @@
       </c>
       <c r="E1233" t="inlineStr">
         <is>
-          <t>ausklappbare 2. US</t>
+          <t>Titelseitenklappe</t>
         </is>
       </c>
       <c r="H1233" t="inlineStr">
@@ -55053,7 +55069,7 @@
       </c>
       <c r="E1234" t="inlineStr">
         <is>
-          <t>1/2 ausklappbare 2. US</t>
+          <t>French Cover</t>
         </is>
       </c>
       <c r="H1234" t="inlineStr">
@@ -55091,7 +55107,7 @@
       </c>
       <c r="E1235" t="inlineStr">
         <is>
-          <t>Banderole (umlaufend)</t>
+          <t>ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1235" t="inlineStr">
@@ -55129,7 +55145,7 @@
       </c>
       <c r="E1236" t="inlineStr">
         <is>
-          <t>Sogbanderole</t>
+          <t>1/2 ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1236" t="inlineStr">
@@ -55167,7 +55183,7 @@
       </c>
       <c r="E1237" t="inlineStr">
         <is>
-          <t>Zangenbanderole</t>
+          <t>Banderole (umlaufend)</t>
         </is>
       </c>
       <c r="H1237" t="inlineStr">
@@ -55205,7 +55221,7 @@
       </c>
       <c r="E1238" t="inlineStr">
         <is>
-          <t>Pfeilbanderole</t>
+          <t>Sogbanderole</t>
         </is>
       </c>
       <c r="H1238" t="inlineStr">
@@ -55243,7 +55259,7 @@
       </c>
       <c r="E1239" t="inlineStr">
         <is>
-          <t>Oversize-Beilage</t>
+          <t>Zangenbanderole</t>
         </is>
       </c>
       <c r="H1239" t="inlineStr">
@@ -55281,7 +55297,7 @@
       </c>
       <c r="E1240" t="inlineStr">
         <is>
-          <t>Lesezeichen (unbestimmte Stelle)</t>
+          <t>Pfeilbanderole</t>
         </is>
       </c>
       <c r="H1240" t="inlineStr">
@@ -55319,7 +55335,7 @@
       </c>
       <c r="E1241" t="inlineStr">
         <is>
-          <t>Lesezeichen (bestimmte Stelle)</t>
+          <t>Oversize-Beilage</t>
         </is>
       </c>
       <c r="H1241" t="inlineStr">
@@ -55357,7 +55373,7 @@
       </c>
       <c r="E1242" t="inlineStr">
         <is>
-          <t>Teaser-Anzeige im red. Text</t>
+          <t>Lesezeichen (unbestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1242" t="inlineStr">
@@ -55395,7 +55411,7 @@
       </c>
       <c r="E1243" t="inlineStr">
         <is>
-          <t>Griffecke im red. Text</t>
+          <t>Lesezeichen (bestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1243" t="inlineStr">
@@ -55428,12 +55444,12 @@
       </c>
       <c r="D1244" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1244" t="inlineStr">
         <is>
-          <t>Klappohr-Einhefter</t>
+          <t>Teaser-Anzeige im red. Text</t>
         </is>
       </c>
       <c r="H1244" t="inlineStr">
@@ -55466,12 +55482,12 @@
       </c>
       <c r="D1245" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1245" t="inlineStr">
         <is>
-          <t>gestanzter Einhefter</t>
+          <t>Griffecke im red. Text</t>
         </is>
       </c>
       <c r="H1245" t="inlineStr">
@@ -55509,7 +55525,7 @@
       </c>
       <c r="E1246" t="inlineStr">
         <is>
-          <t>perforierter Einhefter</t>
+          <t>Klappohr-Einhefter</t>
         </is>
       </c>
       <c r="H1246" t="inlineStr">
@@ -55547,7 +55563,7 @@
       </c>
       <c r="E1247" t="inlineStr">
         <is>
-          <t>Einhefter mit Klappe</t>
+          <t>gestanzter Einhefter</t>
         </is>
       </c>
       <c r="H1247" t="inlineStr">
@@ -55585,7 +55601,7 @@
       </c>
       <c r="E1248" t="inlineStr">
         <is>
-          <t>Flip-Einhefter</t>
+          <t>perforierter Einhefter</t>
         </is>
       </c>
       <c r="H1248" t="inlineStr">
@@ -55610,20 +55626,20 @@
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>FORUM DKG</t>
+          <t>best practice onkologie</t>
         </is>
       </c>
       <c r="C1249" t="n">
-        <v>8700</v>
+        <v>10000</v>
       </c>
       <c r="D1249" t="inlineStr">
         <is>
-          <t>Normalplatzierungen (4c inkl.)</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1249" t="inlineStr">
         <is>
-          <t>1/1 Seite 4c</t>
+          <t>Einhefter mit Klappe</t>
         </is>
       </c>
       <c r="H1249" t="inlineStr">
@@ -55648,20 +55664,20 @@
       </c>
       <c r="B1250" t="inlineStr">
         <is>
-          <t>FORUM DKG</t>
+          <t>best practice onkologie</t>
         </is>
       </c>
       <c r="C1250" t="n">
-        <v>8700</v>
+        <v>10000</v>
       </c>
       <c r="D1250" t="inlineStr">
         <is>
-          <t>Normalplatzierungen (4c inkl.)</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1250" t="inlineStr">
         <is>
-          <t>1/2 Seite 4c</t>
+          <t>Flip-Einhefter</t>
         </is>
       </c>
       <c r="H1250" t="inlineStr">
@@ -55699,7 +55715,7 @@
       </c>
       <c r="E1251" t="inlineStr">
         <is>
-          <t>1/3 Seite 4c</t>
+          <t>1/1 Seite 4c</t>
         </is>
       </c>
       <c r="H1251" t="inlineStr">
@@ -55737,7 +55753,7 @@
       </c>
       <c r="E1252" t="inlineStr">
         <is>
-          <t>1/4 Seite 4c</t>
+          <t>1/2 Seite 4c</t>
         </is>
       </c>
       <c r="H1252" t="inlineStr">
@@ -55775,7 +55791,7 @@
       </c>
       <c r="E1253" t="inlineStr">
         <is>
-          <t>2/1 Doppelseite</t>
+          <t>1/3 Seite 4c</t>
         </is>
       </c>
       <c r="H1253" t="inlineStr">
@@ -55813,7 +55829,7 @@
       </c>
       <c r="E1254" t="inlineStr">
         <is>
-          <t>Advertorial (1/1 Seite 4c)</t>
+          <t>1/4 Seite 4c</t>
         </is>
       </c>
       <c r="H1254" t="inlineStr">
@@ -55846,12 +55862,12 @@
       </c>
       <c r="D1255" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen (4c inkl.)</t>
+          <t>Normalplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1255" t="inlineStr">
         <is>
-          <t>4. Umschlagseite</t>
+          <t>2/1 Doppelseite</t>
         </is>
       </c>
       <c r="H1255" t="inlineStr">
@@ -55884,12 +55900,12 @@
       </c>
       <c r="D1256" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen (4c inkl.)</t>
+          <t>Normalplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1256" t="inlineStr">
         <is>
-          <t>2. Umschlagseite</t>
+          <t>Advertorial (1/1 Seite 4c)</t>
         </is>
       </c>
       <c r="H1256" t="inlineStr">
@@ -55927,7 +55943,7 @@
       </c>
       <c r="E1257" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 1</t>
+          <t>4. Umschlagseite</t>
         </is>
       </c>
       <c r="H1257" t="inlineStr">
@@ -55965,7 +55981,7 @@
       </c>
       <c r="E1258" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 2</t>
+          <t>2. Umschlagseite</t>
         </is>
       </c>
       <c r="H1258" t="inlineStr">
@@ -56003,7 +56019,7 @@
       </c>
       <c r="E1259" t="inlineStr">
         <is>
-          <t>Seite ggü. Editorial 2</t>
+          <t>Seite ggü. Inhalt 1</t>
         </is>
       </c>
       <c r="H1259" t="inlineStr">
@@ -56041,7 +56057,7 @@
       </c>
       <c r="E1260" t="inlineStr">
         <is>
-          <t>Seite ggü. Textanfang</t>
+          <t>Seite ggü. Inhalt 2</t>
         </is>
       </c>
       <c r="H1260" t="inlineStr">
@@ -56079,7 +56095,7 @@
       </c>
       <c r="E1261" t="inlineStr">
         <is>
-          <t>1/1 Seite 4c Festplatzierung</t>
+          <t>Seite ggü. Editorial 2</t>
         </is>
       </c>
       <c r="H1261" t="inlineStr">
@@ -56117,7 +56133,7 @@
       </c>
       <c r="E1262" t="inlineStr">
         <is>
-          <t>1. rechte Einschaltseite</t>
+          <t>Seite ggü. Textanfang</t>
         </is>
       </c>
       <c r="H1262" t="inlineStr">
@@ -56155,7 +56171,7 @@
       </c>
       <c r="E1263" t="inlineStr">
         <is>
-          <t>2. rechte Einschaltseite</t>
+          <t>1/1 Seite 4c Festplatzierung</t>
         </is>
       </c>
       <c r="H1263" t="inlineStr">
@@ -56193,7 +56209,7 @@
       </c>
       <c r="E1264" t="inlineStr">
         <is>
-          <t>3. rechte Einschaltseite</t>
+          <t>1. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1264" t="inlineStr">
@@ -56231,7 +56247,7 @@
       </c>
       <c r="E1265" t="inlineStr">
         <is>
-          <t>4. rechte Einschaltseite</t>
+          <t>2. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1265" t="inlineStr">
@@ -56269,7 +56285,7 @@
       </c>
       <c r="E1266" t="inlineStr">
         <is>
-          <t>5. rechte Einschaltseite</t>
+          <t>3. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1266" t="inlineStr">
@@ -56307,7 +56323,7 @@
       </c>
       <c r="E1267" t="inlineStr">
         <is>
-          <t>6. rechte Einschaltseite</t>
+          <t>4. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1267" t="inlineStr">
@@ -56345,7 +56361,7 @@
       </c>
       <c r="E1268" t="inlineStr">
         <is>
-          <t>7. rechte Einschaltseite</t>
+          <t>5. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1268" t="inlineStr">
@@ -56383,7 +56399,7 @@
       </c>
       <c r="E1269" t="inlineStr">
         <is>
-          <t>8. rechte Einschaltseite</t>
+          <t>6. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1269" t="inlineStr">
@@ -56421,7 +56437,7 @@
       </c>
       <c r="E1270" t="inlineStr">
         <is>
-          <t>9. rechte Einschaltseite</t>
+          <t>7. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1270" t="inlineStr">
@@ -56459,7 +56475,7 @@
       </c>
       <c r="E1271" t="inlineStr">
         <is>
-          <t>10. rechte Einschaltseite</t>
+          <t>8. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1271" t="inlineStr">
@@ -56492,12 +56508,12 @@
       </c>
       <c r="D1272" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1272" t="inlineStr">
         <is>
-          <t>EH/DH 1 Seite</t>
+          <t>9. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1272" t="inlineStr">
@@ -56530,12 +56546,12 @@
       </c>
       <c r="D1273" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1273" t="inlineStr">
         <is>
-          <t>EH/DH 2 Seiten</t>
+          <t>10. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1273" t="inlineStr">
@@ -56573,7 +56589,7 @@
       </c>
       <c r="E1274" t="inlineStr">
         <is>
-          <t>EH/DH 4 Seiten</t>
+          <t>EH/DH 1 Seite</t>
         </is>
       </c>
       <c r="H1274" t="inlineStr">
@@ -56611,7 +56627,7 @@
       </c>
       <c r="E1275" t="inlineStr">
         <is>
-          <t>V-Koop MWO/Wefra</t>
+          <t>EH/DH 2 Seiten</t>
         </is>
       </c>
       <c r="H1275" t="inlineStr">
@@ -56644,12 +56660,12 @@
       </c>
       <c r="D1276" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1276" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (pro 1.000)</t>
+          <t>EH/DH 4 Seiten</t>
         </is>
       </c>
       <c r="H1276" t="inlineStr">
@@ -56682,12 +56698,12 @@
       </c>
       <c r="D1277" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1277" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (gesamt)</t>
+          <t>V-Koop MWO/Wefra</t>
         </is>
       </c>
       <c r="H1277" t="inlineStr">
@@ -56725,7 +56741,7 @@
       </c>
       <c r="E1278" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 50g (gesamt)</t>
+          <t>Werbebeilage bis 25g (pro 1.000)</t>
         </is>
       </c>
       <c r="H1278" t="inlineStr">
@@ -56758,12 +56774,12 @@
       </c>
       <c r="D1279" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1279" t="inlineStr">
         <is>
-          <t>Titelseitenklappe</t>
+          <t>Werbebeilage bis 25g (gesamt)</t>
         </is>
       </c>
       <c r="H1279" t="inlineStr">
@@ -56796,12 +56812,12 @@
       </c>
       <c r="D1280" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1280" t="inlineStr">
         <is>
-          <t>French Cover</t>
+          <t>Werbebeilage bis 50g (gesamt)</t>
         </is>
       </c>
       <c r="H1280" t="inlineStr">
@@ -56839,7 +56855,7 @@
       </c>
       <c r="E1281" t="inlineStr">
         <is>
-          <t>ausklappbare 2. US</t>
+          <t>Titelseitenklappe</t>
         </is>
       </c>
       <c r="H1281" t="inlineStr">
@@ -56877,7 +56893,7 @@
       </c>
       <c r="E1282" t="inlineStr">
         <is>
-          <t>1/2 ausklappbare 2. US</t>
+          <t>French Cover</t>
         </is>
       </c>
       <c r="H1282" t="inlineStr">
@@ -56915,7 +56931,7 @@
       </c>
       <c r="E1283" t="inlineStr">
         <is>
-          <t>Banderole (umlaufend)</t>
+          <t>ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1283" t="inlineStr">
@@ -56953,7 +56969,7 @@
       </c>
       <c r="E1284" t="inlineStr">
         <is>
-          <t>Sogbanderole</t>
+          <t>1/2 ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1284" t="inlineStr">
@@ -56991,7 +57007,7 @@
       </c>
       <c r="E1285" t="inlineStr">
         <is>
-          <t>Zangenbanderole</t>
+          <t>Banderole (umlaufend)</t>
         </is>
       </c>
       <c r="H1285" t="inlineStr">
@@ -57029,7 +57045,7 @@
       </c>
       <c r="E1286" t="inlineStr">
         <is>
-          <t>Pfeilbanderole</t>
+          <t>Sogbanderole</t>
         </is>
       </c>
       <c r="H1286" t="inlineStr">
@@ -57067,7 +57083,7 @@
       </c>
       <c r="E1287" t="inlineStr">
         <is>
-          <t>Oversize-Beilage</t>
+          <t>Zangenbanderole</t>
         </is>
       </c>
       <c r="H1287" t="inlineStr">
@@ -57105,7 +57121,7 @@
       </c>
       <c r="E1288" t="inlineStr">
         <is>
-          <t>Lesezeichen (unbestimmte Stelle)</t>
+          <t>Pfeilbanderole</t>
         </is>
       </c>
       <c r="H1288" t="inlineStr">
@@ -57143,7 +57159,7 @@
       </c>
       <c r="E1289" t="inlineStr">
         <is>
-          <t>Lesezeichen (bestimmte Stelle)</t>
+          <t>Oversize-Beilage</t>
         </is>
       </c>
       <c r="H1289" t="inlineStr">
@@ -57181,7 +57197,7 @@
       </c>
       <c r="E1290" t="inlineStr">
         <is>
-          <t>Teaser-Anzeige im red. Text</t>
+          <t>Lesezeichen (unbestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1290" t="inlineStr">
@@ -57219,7 +57235,7 @@
       </c>
       <c r="E1291" t="inlineStr">
         <is>
-          <t>Griffecke im red. Text</t>
+          <t>Lesezeichen (bestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1291" t="inlineStr">
@@ -57252,12 +57268,12 @@
       </c>
       <c r="D1292" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1292" t="inlineStr">
         <is>
-          <t>Klappohr-Einhefter</t>
+          <t>Teaser-Anzeige im red. Text</t>
         </is>
       </c>
       <c r="H1292" t="inlineStr">
@@ -57290,12 +57306,12 @@
       </c>
       <c r="D1293" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1293" t="inlineStr">
         <is>
-          <t>gestanzter Einhefter</t>
+          <t>Griffecke im red. Text</t>
         </is>
       </c>
       <c r="H1293" t="inlineStr">
@@ -57333,7 +57349,7 @@
       </c>
       <c r="E1294" t="inlineStr">
         <is>
-          <t>Einhefter mit Klappe</t>
+          <t>Klappohr-Einhefter</t>
         </is>
       </c>
       <c r="H1294" t="inlineStr">
@@ -57371,7 +57387,7 @@
       </c>
       <c r="E1295" t="inlineStr">
         <is>
-          <t>Flip-Einhefter</t>
+          <t>gestanzter Einhefter</t>
         </is>
       </c>
       <c r="H1295" t="inlineStr">
@@ -57396,20 +57412,20 @@
       </c>
       <c r="B1296" t="inlineStr">
         <is>
-          <t>Im Fokus Onkologie</t>
+          <t>FORUM DKG</t>
         </is>
       </c>
       <c r="C1296" t="n">
-        <v>8000</v>
+        <v>8700</v>
       </c>
       <c r="D1296" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1296" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
+          <t>Einhefter mit Klappe</t>
         </is>
       </c>
       <c r="H1296" t="inlineStr">
@@ -57434,20 +57450,20 @@
       </c>
       <c r="B1297" t="inlineStr">
         <is>
-          <t>Im Fokus Onkologie</t>
+          <t>FORUM DKG</t>
         </is>
       </c>
       <c r="C1297" t="n">
-        <v>8000</v>
+        <v>8700</v>
       </c>
       <c r="D1297" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1297" t="inlineStr">
         <is>
-          <t>1/2 Seite</t>
+          <t>Flip-Einhefter</t>
         </is>
       </c>
       <c r="H1297" t="inlineStr">
@@ -57485,7 +57501,7 @@
       </c>
       <c r="E1298" t="inlineStr">
         <is>
-          <t>1/3 Seite</t>
+          <t>1/1 Seite</t>
         </is>
       </c>
       <c r="H1298" t="inlineStr">
@@ -57523,7 +57539,7 @@
       </c>
       <c r="E1299" t="inlineStr">
         <is>
-          <t>1/4 Seite</t>
+          <t>1/2 Seite</t>
         </is>
       </c>
       <c r="H1299" t="inlineStr">
@@ -57561,7 +57577,7 @@
       </c>
       <c r="E1300" t="inlineStr">
         <is>
-          <t>2/1 Doppelseite</t>
+          <t>1/3 Seite</t>
         </is>
       </c>
       <c r="H1300" t="inlineStr">
@@ -57599,7 +57615,7 @@
       </c>
       <c r="E1301" t="inlineStr">
         <is>
-          <t>Advertorial (1/1 Seite)</t>
+          <t>1/4 Seite</t>
         </is>
       </c>
       <c r="H1301" t="inlineStr">
@@ -57632,12 +57648,12 @@
       </c>
       <c r="D1302" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1302" t="inlineStr">
         <is>
-          <t>4. Umschlagseite</t>
+          <t>2/1 Doppelseite</t>
         </is>
       </c>
       <c r="H1302" t="inlineStr">
@@ -57670,12 +57686,12 @@
       </c>
       <c r="D1303" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1303" t="inlineStr">
         <is>
-          <t>2. Umschlagseite</t>
+          <t>Advertorial (1/1 Seite)</t>
         </is>
       </c>
       <c r="H1303" t="inlineStr">
@@ -57713,7 +57729,7 @@
       </c>
       <c r="E1304" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 1</t>
+          <t>4. Umschlagseite</t>
         </is>
       </c>
       <c r="H1304" t="inlineStr">
@@ -57751,7 +57767,7 @@
       </c>
       <c r="E1305" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 2</t>
+          <t>2. Umschlagseite</t>
         </is>
       </c>
       <c r="H1305" t="inlineStr">
@@ -57789,7 +57805,7 @@
       </c>
       <c r="E1306" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 3</t>
+          <t>Seite ggü. Inhalt 1</t>
         </is>
       </c>
       <c r="H1306" t="inlineStr">
@@ -57827,7 +57843,7 @@
       </c>
       <c r="E1307" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 4</t>
+          <t>Seite ggü. Inhalt 2</t>
         </is>
       </c>
       <c r="H1307" t="inlineStr">
@@ -57865,7 +57881,7 @@
       </c>
       <c r="E1308" t="inlineStr">
         <is>
-          <t>Seite ggü. Textanfang</t>
+          <t>Seite ggü. Inhalt 3</t>
         </is>
       </c>
       <c r="H1308" t="inlineStr">
@@ -57903,7 +57919,7 @@
       </c>
       <c r="E1309" t="inlineStr">
         <is>
-          <t>1/1 Seite Festplatzierung</t>
+          <t>Seite ggü. Inhalt 4</t>
         </is>
       </c>
       <c r="H1309" t="inlineStr">
@@ -57941,7 +57957,7 @@
       </c>
       <c r="E1310" t="inlineStr">
         <is>
-          <t>1. rechte Einschaltseite</t>
+          <t>Seite ggü. Textanfang</t>
         </is>
       </c>
       <c r="H1310" t="inlineStr">
@@ -57979,7 +57995,7 @@
       </c>
       <c r="E1311" t="inlineStr">
         <is>
-          <t>2. rechte Einschaltseite</t>
+          <t>1/1 Seite Festplatzierung</t>
         </is>
       </c>
       <c r="H1311" t="inlineStr">
@@ -58017,7 +58033,7 @@
       </c>
       <c r="E1312" t="inlineStr">
         <is>
-          <t>3. rechte Einschaltseite</t>
+          <t>1. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1312" t="inlineStr">
@@ -58055,7 +58071,7 @@
       </c>
       <c r="E1313" t="inlineStr">
         <is>
-          <t>4. rechte Einschaltseite</t>
+          <t>2. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1313" t="inlineStr">
@@ -58093,7 +58109,7 @@
       </c>
       <c r="E1314" t="inlineStr">
         <is>
-          <t>5. rechte Einschaltseite</t>
+          <t>3. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1314" t="inlineStr">
@@ -58131,7 +58147,7 @@
       </c>
       <c r="E1315" t="inlineStr">
         <is>
-          <t>6. rechte Einschaltseite</t>
+          <t>4. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1315" t="inlineStr">
@@ -58169,7 +58185,7 @@
       </c>
       <c r="E1316" t="inlineStr">
         <is>
-          <t>7. rechte Einschaltseite</t>
+          <t>5. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1316" t="inlineStr">
@@ -58207,7 +58223,7 @@
       </c>
       <c r="E1317" t="inlineStr">
         <is>
-          <t>8. rechte Einschaltseite</t>
+          <t>6. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1317" t="inlineStr">
@@ -58245,7 +58261,7 @@
       </c>
       <c r="E1318" t="inlineStr">
         <is>
-          <t>9. rechte Einschaltseite</t>
+          <t>7. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1318" t="inlineStr">
@@ -58283,7 +58299,7 @@
       </c>
       <c r="E1319" t="inlineStr">
         <is>
-          <t>10. rechte Einschaltseite</t>
+          <t>8. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1319" t="inlineStr">
@@ -58316,12 +58332,12 @@
       </c>
       <c r="D1320" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1320" t="inlineStr">
         <is>
-          <t>EH/DH 1 Seite</t>
+          <t>9. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1320" t="inlineStr">
@@ -58354,12 +58370,12 @@
       </c>
       <c r="D1321" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1321" t="inlineStr">
         <is>
-          <t>EH/DH 2 Seiten</t>
+          <t>10. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1321" t="inlineStr">
@@ -58397,7 +58413,7 @@
       </c>
       <c r="E1322" t="inlineStr">
         <is>
-          <t>EH/DH 4 Seiten</t>
+          <t>EH/DH 1 Seite</t>
         </is>
       </c>
       <c r="H1322" t="inlineStr">
@@ -58435,7 +58451,7 @@
       </c>
       <c r="E1323" t="inlineStr">
         <is>
-          <t>V-Koop MWO/Wefra</t>
+          <t>EH/DH 2 Seiten</t>
         </is>
       </c>
       <c r="H1323" t="inlineStr">
@@ -58468,12 +58484,12 @@
       </c>
       <c r="D1324" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1324" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (pro 1.000)</t>
+          <t>EH/DH 4 Seiten</t>
         </is>
       </c>
       <c r="H1324" t="inlineStr">
@@ -58506,12 +58522,12 @@
       </c>
       <c r="D1325" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1325" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (gesamt)</t>
+          <t>V-Koop MWO/Wefra</t>
         </is>
       </c>
       <c r="H1325" t="inlineStr">
@@ -58549,7 +58565,7 @@
       </c>
       <c r="E1326" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 50g (gesamt)</t>
+          <t>Werbebeilage bis 25g (pro 1.000)</t>
         </is>
       </c>
       <c r="H1326" t="inlineStr">
@@ -58582,12 +58598,12 @@
       </c>
       <c r="D1327" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1327" t="inlineStr">
         <is>
-          <t>Titelseitenklappe</t>
+          <t>Werbebeilage bis 25g (gesamt)</t>
         </is>
       </c>
       <c r="H1327" t="inlineStr">
@@ -58620,12 +58636,12 @@
       </c>
       <c r="D1328" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1328" t="inlineStr">
         <is>
-          <t>French Cover</t>
+          <t>Werbebeilage bis 50g (gesamt)</t>
         </is>
       </c>
       <c r="H1328" t="inlineStr">
@@ -58663,7 +58679,7 @@
       </c>
       <c r="E1329" t="inlineStr">
         <is>
-          <t>ausklappbare 2. US</t>
+          <t>Titelseitenklappe</t>
         </is>
       </c>
       <c r="H1329" t="inlineStr">
@@ -58701,7 +58717,7 @@
       </c>
       <c r="E1330" t="inlineStr">
         <is>
-          <t>1/2 ausklappbare 2. US</t>
+          <t>French Cover</t>
         </is>
       </c>
       <c r="H1330" t="inlineStr">
@@ -58739,7 +58755,7 @@
       </c>
       <c r="E1331" t="inlineStr">
         <is>
-          <t>Banderole (umlaufend)</t>
+          <t>ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1331" t="inlineStr">
@@ -58777,7 +58793,7 @@
       </c>
       <c r="E1332" t="inlineStr">
         <is>
-          <t>Sogbanderole</t>
+          <t>1/2 ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1332" t="inlineStr">
@@ -58815,7 +58831,7 @@
       </c>
       <c r="E1333" t="inlineStr">
         <is>
-          <t>Zangenbanderole</t>
+          <t>Banderole (umlaufend)</t>
         </is>
       </c>
       <c r="H1333" t="inlineStr">
@@ -58853,7 +58869,7 @@
       </c>
       <c r="E1334" t="inlineStr">
         <is>
-          <t>Pfeilbanderole</t>
+          <t>Sogbanderole</t>
         </is>
       </c>
       <c r="H1334" t="inlineStr">
@@ -58891,7 +58907,7 @@
       </c>
       <c r="E1335" t="inlineStr">
         <is>
-          <t>Oversize-Beilage</t>
+          <t>Zangenbanderole</t>
         </is>
       </c>
       <c r="H1335" t="inlineStr">
@@ -58929,7 +58945,7 @@
       </c>
       <c r="E1336" t="inlineStr">
         <is>
-          <t>Lesezeichen (unbestimmte Stelle)</t>
+          <t>Pfeilbanderole</t>
         </is>
       </c>
       <c r="H1336" t="inlineStr">
@@ -58967,7 +58983,7 @@
       </c>
       <c r="E1337" t="inlineStr">
         <is>
-          <t>Lesezeichen (bestimmte Stelle)</t>
+          <t>Oversize-Beilage</t>
         </is>
       </c>
       <c r="H1337" t="inlineStr">
@@ -59005,7 +59021,7 @@
       </c>
       <c r="E1338" t="inlineStr">
         <is>
-          <t>Teaser-Anzeige auf Inhalt-Seite</t>
+          <t>Lesezeichen (unbestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1338" t="inlineStr">
@@ -59043,7 +59059,7 @@
       </c>
       <c r="E1339" t="inlineStr">
         <is>
-          <t>Teaser-Anzeige im red. Text</t>
+          <t>Lesezeichen (bestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1339" t="inlineStr">
@@ -59081,7 +59097,7 @@
       </c>
       <c r="E1340" t="inlineStr">
         <is>
-          <t>Griffecke auf Inhalt-Seite</t>
+          <t>Teaser-Anzeige auf Inhalt-Seite</t>
         </is>
       </c>
       <c r="H1340" t="inlineStr">
@@ -59119,7 +59135,7 @@
       </c>
       <c r="E1341" t="inlineStr">
         <is>
-          <t>Griffecke im red. Text</t>
+          <t>Teaser-Anzeige im red. Text</t>
         </is>
       </c>
       <c r="H1341" t="inlineStr">
@@ -59152,12 +59168,12 @@
       </c>
       <c r="D1342" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1342" t="inlineStr">
         <is>
-          <t>Klappohr-Einhefter</t>
+          <t>Griffecke auf Inhalt-Seite</t>
         </is>
       </c>
       <c r="H1342" t="inlineStr">
@@ -59190,12 +59206,12 @@
       </c>
       <c r="D1343" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1343" t="inlineStr">
         <is>
-          <t>gestanzter Einhefter</t>
+          <t>Griffecke im red. Text</t>
         </is>
       </c>
       <c r="H1343" t="inlineStr">
@@ -59233,7 +59249,7 @@
       </c>
       <c r="E1344" t="inlineStr">
         <is>
-          <t>Einhefter mit Klappe</t>
+          <t>Klappohr-Einhefter</t>
         </is>
       </c>
       <c r="H1344" t="inlineStr">
@@ -59271,7 +59287,7 @@
       </c>
       <c r="E1345" t="inlineStr">
         <is>
-          <t>Flip-Einhefter</t>
+          <t>gestanzter Einhefter</t>
         </is>
       </c>
       <c r="H1345" t="inlineStr">
@@ -59296,20 +59312,20 @@
       </c>
       <c r="B1346" t="inlineStr">
         <is>
-          <t>InFo Hämatologie + Onkologie</t>
+          <t>Im Fokus Onkologie</t>
         </is>
       </c>
       <c r="C1346" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="D1346" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1346" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
+          <t>Einhefter mit Klappe</t>
         </is>
       </c>
       <c r="H1346" t="inlineStr">
@@ -59334,20 +59350,20 @@
       </c>
       <c r="B1347" t="inlineStr">
         <is>
-          <t>InFo Hämatologie + Onkologie</t>
+          <t>Im Fokus Onkologie</t>
         </is>
       </c>
       <c r="C1347" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="D1347" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1347" t="inlineStr">
         <is>
-          <t>1/2 Seite</t>
+          <t>Flip-Einhefter</t>
         </is>
       </c>
       <c r="H1347" t="inlineStr">
@@ -59385,7 +59401,7 @@
       </c>
       <c r="E1348" t="inlineStr">
         <is>
-          <t>1/3 Seite</t>
+          <t>1/1 Seite</t>
         </is>
       </c>
       <c r="H1348" t="inlineStr">
@@ -59423,7 +59439,7 @@
       </c>
       <c r="E1349" t="inlineStr">
         <is>
-          <t>1/4 Seite</t>
+          <t>1/2 Seite</t>
         </is>
       </c>
       <c r="H1349" t="inlineStr">
@@ -59461,7 +59477,7 @@
       </c>
       <c r="E1350" t="inlineStr">
         <is>
-          <t>2/1 Doppelseite</t>
+          <t>1/3 Seite</t>
         </is>
       </c>
       <c r="H1350" t="inlineStr">
@@ -59499,7 +59515,7 @@
       </c>
       <c r="E1351" t="inlineStr">
         <is>
-          <t>Advertorial (1/1 Seite)</t>
+          <t>1/4 Seite</t>
         </is>
       </c>
       <c r="H1351" t="inlineStr">
@@ -59532,12 +59548,12 @@
       </c>
       <c r="D1352" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1352" t="inlineStr">
         <is>
-          <t>4. Umschlagseite</t>
+          <t>2/1 Doppelseite</t>
         </is>
       </c>
       <c r="H1352" t="inlineStr">
@@ -59570,12 +59586,12 @@
       </c>
       <c r="D1353" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1353" t="inlineStr">
         <is>
-          <t>2. Umschlagseite</t>
+          <t>Advertorial (1/1 Seite)</t>
         </is>
       </c>
       <c r="H1353" t="inlineStr">
@@ -59613,7 +59629,7 @@
       </c>
       <c r="E1354" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 1</t>
+          <t>4. Umschlagseite</t>
         </is>
       </c>
       <c r="H1354" t="inlineStr">
@@ -59651,7 +59667,7 @@
       </c>
       <c r="E1355" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 2</t>
+          <t>2. Umschlagseite</t>
         </is>
       </c>
       <c r="H1355" t="inlineStr">
@@ -59689,7 +59705,7 @@
       </c>
       <c r="E1356" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 3</t>
+          <t>Seite ggü. Inhalt 1</t>
         </is>
       </c>
       <c r="H1356" t="inlineStr">
@@ -59727,7 +59743,7 @@
       </c>
       <c r="E1357" t="inlineStr">
         <is>
-          <t>Seite ggü. Textanfang</t>
+          <t>Seite ggü. Inhalt 2</t>
         </is>
       </c>
       <c r="H1357" t="inlineStr">
@@ -59765,7 +59781,7 @@
       </c>
       <c r="E1358" t="inlineStr">
         <is>
-          <t>1/1 Seite Festplatzierung</t>
+          <t>Seite ggü. Inhalt 3</t>
         </is>
       </c>
       <c r="H1358" t="inlineStr">
@@ -59803,7 +59819,7 @@
       </c>
       <c r="E1359" t="inlineStr">
         <is>
-          <t>1. rechte Einschaltseite</t>
+          <t>Seite ggü. Textanfang</t>
         </is>
       </c>
       <c r="H1359" t="inlineStr">
@@ -59841,7 +59857,7 @@
       </c>
       <c r="E1360" t="inlineStr">
         <is>
-          <t>2. rechte Einschaltseite</t>
+          <t>1/1 Seite Festplatzierung</t>
         </is>
       </c>
       <c r="H1360" t="inlineStr">
@@ -59879,7 +59895,7 @@
       </c>
       <c r="E1361" t="inlineStr">
         <is>
-          <t>3. rechte Einschaltseite</t>
+          <t>1. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1361" t="inlineStr">
@@ -59917,7 +59933,7 @@
       </c>
       <c r="E1362" t="inlineStr">
         <is>
-          <t>4. rechte Einschaltseite</t>
+          <t>2. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1362" t="inlineStr">
@@ -59955,7 +59971,7 @@
       </c>
       <c r="E1363" t="inlineStr">
         <is>
-          <t>5. rechte Einschaltseite</t>
+          <t>3. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1363" t="inlineStr">
@@ -59993,7 +60009,7 @@
       </c>
       <c r="E1364" t="inlineStr">
         <is>
-          <t>6. rechte Einschaltseite</t>
+          <t>4. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1364" t="inlineStr">
@@ -60031,7 +60047,7 @@
       </c>
       <c r="E1365" t="inlineStr">
         <is>
-          <t>7. rechte Einschaltseite</t>
+          <t>5. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1365" t="inlineStr">
@@ -60069,7 +60085,7 @@
       </c>
       <c r="E1366" t="inlineStr">
         <is>
-          <t>8. rechte Einschaltseite</t>
+          <t>6. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1366" t="inlineStr">
@@ -60107,7 +60123,7 @@
       </c>
       <c r="E1367" t="inlineStr">
         <is>
-          <t>9. rechte Einschaltseite</t>
+          <t>7. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1367" t="inlineStr">
@@ -60145,7 +60161,7 @@
       </c>
       <c r="E1368" t="inlineStr">
         <is>
-          <t>10. rechte Einschaltseite</t>
+          <t>8. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1368" t="inlineStr">
@@ -60178,12 +60194,12 @@
       </c>
       <c r="D1369" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1369" t="inlineStr">
         <is>
-          <t>EH/DH 1 Seite</t>
+          <t>9. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1369" t="inlineStr">
@@ -60216,12 +60232,12 @@
       </c>
       <c r="D1370" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1370" t="inlineStr">
         <is>
-          <t>EH/DH 2 Seiten</t>
+          <t>10. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1370" t="inlineStr">
@@ -60259,7 +60275,7 @@
       </c>
       <c r="E1371" t="inlineStr">
         <is>
-          <t>EH/DH 4 Seiten</t>
+          <t>EH/DH 1 Seite</t>
         </is>
       </c>
       <c r="H1371" t="inlineStr">
@@ -60292,12 +60308,12 @@
       </c>
       <c r="D1372" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1372" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (pro 1.000)</t>
+          <t>EH/DH 2 Seiten</t>
         </is>
       </c>
       <c r="H1372" t="inlineStr">
@@ -60330,12 +60346,12 @@
       </c>
       <c r="D1373" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1373" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (gesamt)</t>
+          <t>EH/DH 4 Seiten</t>
         </is>
       </c>
       <c r="H1373" t="inlineStr">
@@ -60373,7 +60389,7 @@
       </c>
       <c r="E1374" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 50g (gesamt)</t>
+          <t>Werbebeilage bis 25g (pro 1.000)</t>
         </is>
       </c>
       <c r="H1374" t="inlineStr">
@@ -60406,12 +60422,12 @@
       </c>
       <c r="D1375" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1375" t="inlineStr">
         <is>
-          <t>Titelseitenklappe</t>
+          <t>Werbebeilage bis 25g (gesamt)</t>
         </is>
       </c>
       <c r="H1375" t="inlineStr">
@@ -60444,12 +60460,12 @@
       </c>
       <c r="D1376" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1376" t="inlineStr">
         <is>
-          <t>French Cover</t>
+          <t>Werbebeilage bis 50g (gesamt)</t>
         </is>
       </c>
       <c r="H1376" t="inlineStr">
@@ -60487,7 +60503,7 @@
       </c>
       <c r="E1377" t="inlineStr">
         <is>
-          <t>ausklappbare 2. US</t>
+          <t>Titelseitenklappe</t>
         </is>
       </c>
       <c r="H1377" t="inlineStr">
@@ -60525,7 +60541,7 @@
       </c>
       <c r="E1378" t="inlineStr">
         <is>
-          <t>1/2 ausklappbare 2. US</t>
+          <t>French Cover</t>
         </is>
       </c>
       <c r="H1378" t="inlineStr">
@@ -60563,7 +60579,7 @@
       </c>
       <c r="E1379" t="inlineStr">
         <is>
-          <t>Banderole (umlaufend)</t>
+          <t>ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1379" t="inlineStr">
@@ -60601,7 +60617,7 @@
       </c>
       <c r="E1380" t="inlineStr">
         <is>
-          <t>Sogbanderole</t>
+          <t>1/2 ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1380" t="inlineStr">
@@ -60639,7 +60655,7 @@
       </c>
       <c r="E1381" t="inlineStr">
         <is>
-          <t>Zangenbanderole</t>
+          <t>Banderole (umlaufend)</t>
         </is>
       </c>
       <c r="H1381" t="inlineStr">
@@ -60677,7 +60693,7 @@
       </c>
       <c r="E1382" t="inlineStr">
         <is>
-          <t>Pfeilbanderole</t>
+          <t>Sogbanderole</t>
         </is>
       </c>
       <c r="H1382" t="inlineStr">
@@ -60715,7 +60731,7 @@
       </c>
       <c r="E1383" t="inlineStr">
         <is>
-          <t>Oversize-Beilage</t>
+          <t>Zangenbanderole</t>
         </is>
       </c>
       <c r="H1383" t="inlineStr">
@@ -60753,7 +60769,7 @@
       </c>
       <c r="E1384" t="inlineStr">
         <is>
-          <t>Lesezeichen (unbestimmte Stelle)</t>
+          <t>Pfeilbanderole</t>
         </is>
       </c>
       <c r="H1384" t="inlineStr">
@@ -60791,7 +60807,7 @@
       </c>
       <c r="E1385" t="inlineStr">
         <is>
-          <t>Lesezeichen (bestimmte Stelle)</t>
+          <t>Oversize-Beilage</t>
         </is>
       </c>
       <c r="H1385" t="inlineStr">
@@ -60829,7 +60845,7 @@
       </c>
       <c r="E1386" t="inlineStr">
         <is>
-          <t>Teaser-Anzeige auf Inhalt-Seite</t>
+          <t>Lesezeichen (unbestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1386" t="inlineStr">
@@ -60867,7 +60883,7 @@
       </c>
       <c r="E1387" t="inlineStr">
         <is>
-          <t>Teaser-Anzeige im red. Text</t>
+          <t>Lesezeichen (bestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1387" t="inlineStr">
@@ -60905,7 +60921,7 @@
       </c>
       <c r="E1388" t="inlineStr">
         <is>
-          <t>Griffecke auf Inhalt-Seite</t>
+          <t>Teaser-Anzeige auf Inhalt-Seite</t>
         </is>
       </c>
       <c r="H1388" t="inlineStr">
@@ -60943,7 +60959,7 @@
       </c>
       <c r="E1389" t="inlineStr">
         <is>
-          <t>Griffecke im red. Text</t>
+          <t>Teaser-Anzeige im red. Text</t>
         </is>
       </c>
       <c r="H1389" t="inlineStr">
@@ -60976,12 +60992,12 @@
       </c>
       <c r="D1390" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1390" t="inlineStr">
         <is>
-          <t>Klappohr-Einhefter</t>
+          <t>Griffecke auf Inhalt-Seite</t>
         </is>
       </c>
       <c r="H1390" t="inlineStr">
@@ -61014,12 +61030,12 @@
       </c>
       <c r="D1391" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1391" t="inlineStr">
         <is>
-          <t>gestanzter Einhefter</t>
+          <t>Griffecke im red. Text</t>
         </is>
       </c>
       <c r="H1391" t="inlineStr">
@@ -61057,7 +61073,7 @@
       </c>
       <c r="E1392" t="inlineStr">
         <is>
-          <t>Einhefter mit Klappe</t>
+          <t>Klappohr-Einhefter</t>
         </is>
       </c>
       <c r="H1392" t="inlineStr">
@@ -61095,7 +61111,7 @@
       </c>
       <c r="E1393" t="inlineStr">
         <is>
-          <t>Flip-Einhefter</t>
+          <t>gestanzter Einhefter</t>
         </is>
       </c>
       <c r="H1393" t="inlineStr">
@@ -61120,20 +61136,20 @@
       </c>
       <c r="B1394" t="inlineStr">
         <is>
-          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+          <t>InFo Hämatologie + Onkologie</t>
         </is>
       </c>
       <c r="C1394" t="n">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="D1394" t="inlineStr">
         <is>
-          <t>Anzeigenformate</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1394" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
+          <t>Einhefter mit Klappe</t>
         </is>
       </c>
       <c r="H1394" t="inlineStr">
@@ -61158,20 +61174,20 @@
       </c>
       <c r="B1395" t="inlineStr">
         <is>
-          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+          <t>InFo Hämatologie + Onkologie</t>
         </is>
       </c>
       <c r="C1395" t="n">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="D1395" t="inlineStr">
         <is>
-          <t>Anzeigenformate</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1395" t="inlineStr">
         <is>
-          <t>A4 Seite hoch</t>
+          <t>Flip-Einhefter</t>
         </is>
       </c>
       <c r="H1395" t="inlineStr">
@@ -61209,7 +61225,7 @@
       </c>
       <c r="E1396" t="inlineStr">
         <is>
-          <t>A5 Seite hoch</t>
+          <t>1/1 Seite</t>
         </is>
       </c>
       <c r="H1396" t="inlineStr">
@@ -61247,7 +61263,7 @@
       </c>
       <c r="E1397" t="inlineStr">
         <is>
-          <t>3/4 Seite quer</t>
+          <t>A4 Seite hoch</t>
         </is>
       </c>
       <c r="H1397" t="inlineStr">
@@ -61285,7 +61301,7 @@
       </c>
       <c r="E1398" t="inlineStr">
         <is>
-          <t>1/2 Seite quer</t>
+          <t>A5 Seite hoch</t>
         </is>
       </c>
       <c r="H1398" t="inlineStr">
@@ -61323,7 +61339,7 @@
       </c>
       <c r="E1399" t="inlineStr">
         <is>
-          <t>1/3 Seite quer</t>
+          <t>3/4 Seite quer</t>
         </is>
       </c>
       <c r="H1399" t="inlineStr">
@@ -61361,7 +61377,7 @@
       </c>
       <c r="E1400" t="inlineStr">
         <is>
-          <t>1/4 Seite quer</t>
+          <t>1/2 Seite quer</t>
         </is>
       </c>
       <c r="H1400" t="inlineStr">
@@ -61399,7 +61415,7 @@
       </c>
       <c r="E1401" t="inlineStr">
         <is>
-          <t>Advertorial (A4 hoch)</t>
+          <t>1/3 Seite quer</t>
         </is>
       </c>
       <c r="H1401" t="inlineStr">
@@ -61432,12 +61448,12 @@
       </c>
       <c r="D1402" t="inlineStr">
         <is>
-          <t>Sonder- und Festplatzierungen</t>
+          <t>Anzeigenformate</t>
         </is>
       </c>
       <c r="E1402" t="inlineStr">
         <is>
-          <t>Titelseitenfuß</t>
+          <t>1/4 Seite quer</t>
         </is>
       </c>
       <c r="H1402" t="inlineStr">
@@ -61470,12 +61486,12 @@
       </c>
       <c r="D1403" t="inlineStr">
         <is>
-          <t>Sonder- und Festplatzierungen</t>
+          <t>Anzeigenformate</t>
         </is>
       </c>
       <c r="E1403" t="inlineStr">
         <is>
-          <t>Insel</t>
+          <t>Advertorial (A4 hoch)</t>
         </is>
       </c>
       <c r="H1403" t="inlineStr">
@@ -61513,7 +61529,7 @@
       </c>
       <c r="E1404" t="inlineStr">
         <is>
-          <t>Insel maxi</t>
+          <t>Titelseitenfuß</t>
         </is>
       </c>
       <c r="H1404" t="inlineStr">
@@ -61551,7 +61567,7 @@
       </c>
       <c r="E1405" t="inlineStr">
         <is>
-          <t>Tunnel klein</t>
+          <t>Insel</t>
         </is>
       </c>
       <c r="H1405" t="inlineStr">
@@ -61589,7 +61605,7 @@
       </c>
       <c r="E1406" t="inlineStr">
         <is>
-          <t>Tunnel groß</t>
+          <t>Insel maxi</t>
         </is>
       </c>
       <c r="H1406" t="inlineStr">
@@ -61627,7 +61643,7 @@
       </c>
       <c r="E1407" t="inlineStr">
         <is>
-          <t>Seite 3, 1/1 Seite</t>
+          <t>Tunnel klein</t>
         </is>
       </c>
       <c r="H1407" t="inlineStr">
@@ -61665,7 +61681,7 @@
       </c>
       <c r="E1408" t="inlineStr">
         <is>
-          <t>Seite 5, 1/1 Seite</t>
+          <t>Tunnel groß</t>
         </is>
       </c>
       <c r="H1408" t="inlineStr">
@@ -61703,7 +61719,7 @@
       </c>
       <c r="E1409" t="inlineStr">
         <is>
-          <t>Seite 7, 1/1 Seite</t>
+          <t>Seite 3, 1/1 Seite</t>
         </is>
       </c>
       <c r="H1409" t="inlineStr">
@@ -61741,7 +61757,7 @@
       </c>
       <c r="E1410" t="inlineStr">
         <is>
-          <t>Seite 9, 1/1 Seite</t>
+          <t>Seite 5, 1/1 Seite</t>
         </is>
       </c>
       <c r="H1410" t="inlineStr">
@@ -61779,7 +61795,7 @@
       </c>
       <c r="E1411" t="inlineStr">
         <is>
-          <t>Seite 11, 1/1 Seite</t>
+          <t>Seite 7, 1/1 Seite</t>
         </is>
       </c>
       <c r="H1411" t="inlineStr">
@@ -61817,7 +61833,7 @@
       </c>
       <c r="E1412" t="inlineStr">
         <is>
-          <t>Seite 3, A4 hoch</t>
+          <t>Seite 9, 1/1 Seite</t>
         </is>
       </c>
       <c r="H1412" t="inlineStr">
@@ -61855,7 +61871,7 @@
       </c>
       <c r="E1413" t="inlineStr">
         <is>
-          <t>Seite 5, A4 hoch</t>
+          <t>Seite 11, 1/1 Seite</t>
         </is>
       </c>
       <c r="H1413" t="inlineStr">
@@ -61893,7 +61909,7 @@
       </c>
       <c r="E1414" t="inlineStr">
         <is>
-          <t>Seite 7, A4 hoch</t>
+          <t>Seite 3, A4 hoch</t>
         </is>
       </c>
       <c r="H1414" t="inlineStr">
@@ -61931,7 +61947,7 @@
       </c>
       <c r="E1415" t="inlineStr">
         <is>
-          <t>Seite 9, A4 hoch</t>
+          <t>Seite 5, A4 hoch</t>
         </is>
       </c>
       <c r="H1415" t="inlineStr">
@@ -61969,7 +61985,7 @@
       </c>
       <c r="E1416" t="inlineStr">
         <is>
-          <t>Seite 11, A4 hoch</t>
+          <t>Seite 7, A4 hoch</t>
         </is>
       </c>
       <c r="H1416" t="inlineStr">
@@ -62002,12 +62018,12 @@
       </c>
       <c r="D1417" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Sonder- und Festplatzierungen</t>
         </is>
       </c>
       <c r="E1417" t="inlineStr">
         <is>
-          <t>Flex-Tarif – 1/1 Seite 4c</t>
+          <t>Seite 9, A4 hoch</t>
         </is>
       </c>
       <c r="H1417" t="inlineStr">
@@ -62040,12 +62056,12 @@
       </c>
       <c r="D1418" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Sonder- und Festplatzierungen</t>
         </is>
       </c>
       <c r="E1418" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (pro 1.000)</t>
+          <t>Seite 11, A4 hoch</t>
         </is>
       </c>
       <c r="H1418" t="inlineStr">
@@ -62078,12 +62094,12 @@
       </c>
       <c r="D1419" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1419" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (gesamt)</t>
+          <t>Flex-Tarif – 1/1 Seite 4c</t>
         </is>
       </c>
       <c r="H1419" t="inlineStr">
@@ -62121,7 +62137,7 @@
       </c>
       <c r="E1420" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 50g (gesamt)</t>
+          <t>Werbebeilage bis 25g (pro 1.000)</t>
         </is>
       </c>
       <c r="H1420" t="inlineStr">
@@ -62154,12 +62170,12 @@
       </c>
       <c r="D1421" t="inlineStr">
         <is>
-          <t>AdSpecials</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1421" t="inlineStr">
         <is>
-          <t>Großumleger 4-seitig</t>
+          <t>Werbebeilage bis 25g (gesamt)</t>
         </is>
       </c>
       <c r="H1421" t="inlineStr">
@@ -62192,12 +62208,12 @@
       </c>
       <c r="D1422" t="inlineStr">
         <is>
-          <t>AdSpecials</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1422" t="inlineStr">
         <is>
-          <t>Titelseite + 2. Seite</t>
+          <t>Werbebeilage bis 50g (gesamt)</t>
         </is>
       </c>
       <c r="H1422" t="inlineStr">
@@ -62235,7 +62251,7 @@
       </c>
       <c r="E1423" t="inlineStr">
         <is>
-          <t>Transparenzumleger 4-seitig</t>
+          <t>Großumleger 4-seitig</t>
         </is>
       </c>
       <c r="H1423" t="inlineStr">
@@ -62273,7 +62289,7 @@
       </c>
       <c r="E1424" t="inlineStr">
         <is>
-          <t>HalfCover TSK (voll)</t>
+          <t>Titelseite + 2. Seite</t>
         </is>
       </c>
       <c r="H1424" t="inlineStr">
@@ -62311,7 +62327,7 @@
       </c>
       <c r="E1425" t="inlineStr">
         <is>
-          <t>HalfCover TSK (1/2 Vorder-/Rückseite)</t>
+          <t>Transparenzumleger 4-seitig</t>
         </is>
       </c>
       <c r="H1425" t="inlineStr">
@@ -62349,7 +62365,7 @@
       </c>
       <c r="E1426" t="inlineStr">
         <is>
-          <t>Banderole</t>
+          <t>HalfCover TSK (voll)</t>
         </is>
       </c>
       <c r="H1426" t="inlineStr">
@@ -62387,7 +62403,7 @@
       </c>
       <c r="E1427" t="inlineStr">
         <is>
-          <t>Transparent-Flieger</t>
+          <t>HalfCover TSK (1/2 Vorder-/Rückseite)</t>
         </is>
       </c>
       <c r="H1427" t="inlineStr">
@@ -62425,32 +62441,108 @@
       </c>
       <c r="E1428" t="inlineStr">
         <is>
+          <t>Banderole</t>
+        </is>
+      </c>
+      <c r="H1428" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="I1428" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="K1428" t="inlineStr">
+        <is>
+          <t>Onkologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+        </is>
+      </c>
+      <c r="C1429" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>AdSpecials</t>
+        </is>
+      </c>
+      <c r="E1429" t="inlineStr">
+        <is>
+          <t>Transparent-Flieger</t>
+        </is>
+      </c>
+      <c r="H1429" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="I1429" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="K1429" t="inlineStr">
+        <is>
+          <t>Onkologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+        </is>
+      </c>
+      <c r="C1430" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>AdSpecials</t>
+        </is>
+      </c>
+      <c r="E1430" t="inlineStr">
+        <is>
           <t>Aufkleber maschinell</t>
         </is>
       </c>
-      <c r="H1428" t="inlineStr">
-        <is>
-          <t>nein</t>
-        </is>
-      </c>
-      <c r="I1428" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="K1428" t="inlineStr">
+      <c r="H1430" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="I1430" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="K1430" t="inlineStr">
         <is>
           <t>Onkologie</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1428"/>
+  <autoFilter ref="A1:L1430"/>
   <dataValidations count="2">
-    <dataValidation sqref="H2:I1428" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:I1430" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J1428" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J1430" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"DU,EH"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Angebotsdaten.xlsx
+++ b/Angebotsdaten.xlsx
@@ -69248,8 +69248,10 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>DGIM Kongress (Auslage), 10.04.−13.04.2027, Wiesbaden
-DGP Kongress (Auslage), 03.03.–06.03.2027, Köln</t>
+          <t>DGP Kongress (Auslage), 03.03.–06.03.2027, Köln
+AEK Cancer Congress (Auslage), 03.03.–05.03.2027, Essen
+DGHO Frühjahrstagung (Auslage), 12.03.2027, Berlin
+DGIM Kongress (Auslage), 10.04.–13.04.2027, Wiesbaden</t>
         </is>
       </c>
     </row>
@@ -69299,7 +69301,8 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>DCK (Auslage), 21.04.−23.04.2027, München</t>
+          <t>GTH Jahrestagung (Auslage), 02.03.–05.03.2027, Hamburg
+DCK (Auslage), 21.04.–23.04.2027, München</t>
         </is>
       </c>
     </row>
@@ -69347,6 +69350,11 @@
           <t>Zervixkarzinom</t>
         </is>
       </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>ISALXX (Auslage), 14.03.–17.03.2027, München</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -69392,6 +69400,12 @@
           <t>Chronische Leukämien (CLL &amp; CML)</t>
         </is>
       </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Röko (Auslage), 05.05.–07.05.2027, Leipzig
+DGHNO-KHC Kongress (Auslage), 05.05.–08.05.2027, Dresden</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -69439,7 +69453,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>DGS Kongress (Auslage), 17.06.−19.06.2027, Berlin</t>
+          <t>DGS Senologiekongress (Auslage), 17.06.–19.06.2027, Berlin</t>
         </is>
       </c>
     </row>
@@ -69487,6 +69501,12 @@
           <t>Lebensstil und Krebs</t>
         </is>
       </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>EPCM Meeting (Auslage), 17.06.–18.06.2027, Hamburg
+DEGRO Kongress (Auslage), 24.06.–26.06.2027, Leipzig</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -69532,6 +69552,11 @@
           <t>Gehirneigene Karzinome</t>
         </is>
       </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Heidelberger Myelomtage (Auslage), September, Heidelberg</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -69579,8 +69604,8 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>ADO Kongress (Auslage), 08.09.–11.09.2027, Nürnberg
-DGT Jahrestagung (Auslage), 09.09–11.09.2027, Mainz</t>
+          <t>DGT Jahrestagung (Auslage), 08.09.–10.09.2027, Münster
+ADO Kongress (Auslage), 08.09.–11.09.2027, Erlangen/Nürnberg</t>
         </is>
       </c>
     </row>
@@ -69630,8 +69655,8 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>DGU Kongress (Auslage), 15.09.−18.09.2027, Frankfurt/Main
-DGHO Jahrestagung (Auslage), 08.10.−11.10.2027, Leipzig</t>
+          <t>DGU-Kongress (Auslage), 15.09.–18.09.2027, Frankfurt am Main
+DGHO Jahrestagung (Auslage), 08.10.–11.10.2027, Leipzig</t>
         </is>
       </c>
     </row>
@@ -69769,6 +69794,11 @@
           <t>Nierenzellkarzinom</t>
         </is>
       </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>onko-update (Auslage), Januar 2028, Berlin</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -69816,7 +69846,10 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>DGP Kongress (Auslage), 03.03.–06.03.2027, Köln</t>
+          <t>DGP Kongress (Auslage), 03.03.–06.03.2027, Köln
+AEK Cancer Congress (Auslage), 03.03.–05.03.2027, Essen
+DGHO Frühjahrstagung (Auslage), 12.03.2027, Berlin
+ISALXX (Auslage), 14.03.–17.03.2027, München</t>
         </is>
       </c>
     </row>
@@ -69866,8 +69899,8 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>DGIM Kongress (Auslage), 10.04.−13.04.2027, Wiesbaden
-DCK (Auslage), 21.04.−23.04.2027, München</t>
+          <t>DGIM Kongress (Auslage), 10.04.–13.04.2027, Wiesbaden
+DCK (Auslage), 21.04.–23.04.2027, München</t>
         </is>
       </c>
     </row>
@@ -69915,6 +69948,12 @@
           <t>ca. 3 TOPIC-THEMEN / 1 CME-TOPIC (werden aktuell pro Ausgabe festgelegt)</t>
         </is>
       </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Röko (Auslage), 05.05.–07.05.2027, Leipzig
+DGHNO-KHC Kongress (Auslage), 05.05.–08.05.2027, Dresden</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -69962,7 +70001,9 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>DGS Kongress (Auslage), 17.06.−19.06.2027, Berlin</t>
+          <t>DGS Senologiekongress (Auslage), 17.06.–19.06.2027, Berlin
+EPCM Meeting (Auslage), 17.06.–18.06.2027, Hamburg
+DEGRO Kongress (Auslage), 24.06.–26.06.2027, Leipzig</t>
         </is>
       </c>
     </row>
@@ -70010,6 +70051,11 @@
           <t>ca. 3 TOPIC-THEMEN / 1 CME-TOPIC (werden aktuell pro Ausgabe festgelegt)</t>
         </is>
       </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Heidelberger Myelomtage (Auslage), September, Heidelberg</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -70057,9 +70103,9 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>DGU Kongress (Auslage), 15.09.−18.09.2027, Frankfurt/Main
-ADO Kongress (Auslage), 08.09.−11.09.2027, Nürnberg
-DGT Jahrestagung (Auslage), 09.09.–11.09.2027, Mainz</t>
+          <t>DGT Jahrestagung (Auslage), 08.09.–10.09.2027, Münster
+ADO Kongress (Auslage), 08.09.–11.09.2027, Erlangen/Nürnberg
+DGU-Kongress (Auslage), 15.09.–18.09.2027, Frankfurt am Main</t>
         </is>
       </c>
     </row>
@@ -70109,7 +70155,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>DGHO Jahrestagung (Auslage), 08.10.−11.10.2027, Leipzig</t>
+          <t>DGHO Jahrestagung (Auslage), 08.10.–11.10.2027, Leipzig</t>
         </is>
       </c>
     </row>
@@ -70247,6 +70293,11 @@
           <t>ca. 3 TOPIC-THEMEN / 1 CME-TOPIC (werden aktuell pro Ausgabe festgelegt)</t>
         </is>
       </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>onko-update (Auslage), Januar 2028, Berlin</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -70294,9 +70345,10 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>DGHO Frühjahrstagung (Auslage), 12.03.2027, Berlin
-DGIM Kongress (Auslage),10.04.−13.04.2027, Wiesbaden
-DGP Kongress (Auslage), 03.03.–06.03.2027, Köln</t>
+          <t>DGP Kongress (Auslage), 03.03.–06.03.2027, Köln
+AEK Cancer Congress (Auslage), 03.03.–05.03.2027, Essen
+DGHO Frühjahrstagung (Auslage), 12.03.2027, Berlin
+DGIM Kongress (Auslage), 10.04.–13.04.2027, Wiesbaden</t>
         </is>
       </c>
     </row>
@@ -70346,7 +70398,9 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>DCK (Auslage), 21.04.−23.04.2027, München</t>
+          <t>DCK (Auslage), 21.04.–23.04.2027, München
+DGHNO-KHC Kongress (Auslage), 05.05.–08.05.2027, Dresden
+EPCM Meeting (Auslage), 17.06.–18.06.2027, Hamburg</t>
         </is>
       </c>
     </row>
@@ -70396,8 +70450,9 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>DGS Kongress (Auslage), 17.06.−19.06.2027, Berlin
-DGT Jahrestagung (Auslage), 09.09.–11.09.2027, Mainz</t>
+          <t>DGS Senologiekongress (Auslage), 17.06.–19.06.2027, Berlin
+DGT Jahrestagung (Auslage), 08.09.–10.09.2027, Münster
+ADO Kongress (Auslage), 08.09.–11.09.2027, Erlangen/Nürnberg</t>
         </is>
       </c>
     </row>
@@ -70447,8 +70502,8 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>DGU Kongress (Auslage), 15.09.−18.09.2027, Frankfurt/Main
-DGHO Jahrestagung (Auslage), 08.10.−11.10.2027, Leipzig</t>
+          <t>DGU-Kongress (Auslage), 15.09.–18.09.2027, Frankfurt am Main
+DGHO Jahrestagung (Auslage), 08.10.–11.10.2027, Leipzig</t>
         </is>
       </c>
     </row>
@@ -70541,6 +70596,11 @@
           <t>Ernährung und Krebs</t>
         </is>
       </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>onko-update (Auslage), Januar 2028, Berlin</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -70588,10 +70648,13 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>DGP Kongress (Auslage), 03.03.–06.03.2027, Köln
-23. AIO-Herbstkongress 2026 (Bericht)
-68th ASH Annual Meeting and Exposition 2026 (ASH 2026) (Bericht)
-48th Annual San Antonio Breast Cancer Symposium (SABCS 2026)</t>
+          <t>GTH Jahrestagung (Auslage), 02.03.–05.03.2027, Hamburg
+DGP Kongress (Auslage), 03.03.–06.03.2027, Köln
+AEK Cancer Congress (Auslage), 03.03.–05.03.2027, Essen
+ISALXX (Auslage), 14.03.–17.03.2027, München
+AIO-Herbstkongress 2026 (Bericht), 19.11.–21.11.2026, Berlin
+SABCS (Bericht), 08.12.–11.12.2026, San Antonio
+ASH Annual Meeting (Bericht), 12.12.–15.12.2026, New Orleans</t>
         </is>
       </c>
     </row>
@@ -70641,9 +70704,11 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>ASCO-GI Gastrointestinal Cancer Symposium 2027 (Bericht)
-Onkologie-Update-Seminar Berlin (Bericht)
-ASCO-GU Genitourinary Cancers Symposium 2027 (Bericht)</t>
+          <t>DGIM Kongress (Auslage), 10.04.–13.04.2027, Wiesbaden
+DCK (Auslage), 21.04.–23.04.2027, München
+ASCO-GI Symposium (Bericht), 21.01.–23.01.2027, San Francisco
+onko-update (Bericht), 22.01.–23.01.2027, Berlin
+ASCO-GU Symposium (Bericht), 11.02.–13.02.2027, San Francisco</t>
         </is>
       </c>
     </row>
@@ -70693,10 +70758,12 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>67. Kongress der Deutschen Gesellschaft für Pneumologie (DGP) (Bericht)
-ESMO Sarcoma and Rare Cancers Congress 2027 (Bericht)
-DGHO Frühjahrstagung 2025 (Bericht)
-ACUTE LEUKEMIAS XX (ISAL) (Bericht)</t>
+          <t>Röko (Auslage), 05.05.–07.05.2027, Leipzig
+DGHNO-KHC Kongress (Auslage), 05.05.–08.05.2027, Dresden
+DGP Kongress (Bericht), 03.03.–06.03.2027, Köln
+ESMO Sarcoma and Rare Cancers (Bericht), 04.03.–06.03.2027, Lugano
+DGHO Frühjahrstagung (Bericht), 12.03.2027, Berlin
+ISALXX (Bericht), 14.03.–17.03.2027, München</t>
         </is>
       </c>
     </row>
@@ -70746,11 +70813,13 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>DGS Kongress (Auslage), 17.06.−19.06.2027, Berlin
-20th St. Gallen International Breast Cancer Conference (Bericht)
-53. Annual Meeting of the EBMT (Bericht)
-The 19th International Congress on Myelodysplastic Syndrome (Bericht)
-23. EADO Congress</t>
+          <t>DGS Senologiekongress (Auslage), 17.06.–19.06.2027, Berlin
+EPCM Meeting (Auslage), 17.06.–18.06.2027, Hamburg
+DEGRO Kongress (Auslage), 24.06.–26.06.2027, Leipzig
+SGBCC (Bericht), 17.03.–20.03.2027, Wien
+EBMT Annual Meeting (Bericht), 11.04.–14.04.2027, Rotterdam
+MDS Congress (Bericht), 14.04.–16.04.2027, Leipzig
+EADO Congress (Bericht), 15.04.–17.04.2027, Wien</t>
         </is>
       </c>
     </row>
@@ -70800,8 +70869,9 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>DGHNO-KHC-Tagung (Bericht)
-ESMO Breast Cancer Congress 2027 (Bericht)</t>
+          <t>DGT Jahrestagung (Auslage), 08.09.–10.09.2027, Münster
+DGHNO-KHC Kongress (Bericht), 05.05.–08.05.2027, Dresden
+ESMO Breast Cancer (Bericht), 12.05.–14.05.2027, Mailand</t>
         </is>
       </c>
     </row>
@@ -70851,9 +70921,12 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>2027 ASCO ANNUAL MEETING of the American Society of Clinical Oncology (Bericht)
-EHA 2027 Congress of the European Hematology Association (Bericht)
-46. Jahreskongress der DGS e.V. 2027 (Bericht)</t>
+          <t>Heidelberger Myelomtage (Auslage), September, Heidelberg
+ADO Kongress (Auslage), 08.09.–11.09.2027, Erlangen/Nürnberg
+DGU-Kongress (Auslage), 15.09.–18.09.2027, Frankfurt am Main
+ASCO Annual Meeting (Bericht), 04.06.–08.06.2027, Chicago
+EHA Congress (Bericht), 10.06.–13.06.2027, Barcelona
+DGS Senologiekongress (Bericht), 17.06.–19.06.2027, Berlin</t>
         </is>
       </c>
     </row>
@@ -70903,10 +70976,10 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>DGHO Jahrestagung (Auslage), 08.10.−11.10.2027, Leipzig
-19th International Conference on Malignant Lymphoma (ICML 2027) (Bericht)
-ESMO Gynaecological Cancers Congress 2026 (Bericht)
-ESMO Gastrointestinal Cancers Congress 2027 (Bericht)</t>
+          <t>DGHO Jahrestagung (Auslage), 08.10.–11.10.2027, Leipzig
+ICML (Bericht), 15.06.–19.06.2027, Lugano
+ESMO Gynaecological Cancers (Bericht), 16.06.–18.06.2027, Wien
+ESMO Gastrointestinal Cancers (Bericht), 30.06.–03.07.2027, Barcelona</t>
         </is>
       </c>
     </row>
@@ -70956,9 +71029,9 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>37. Deutscher Hautkrebskongress (ADO 2027) (Bericht)
-World Conference on Lung Cancer (WCLC 2027)  (Bericht)
-79. Jahreskongress der Deutschen Gesellschaft für Urologie (DGU 2027) (Bericht)</t>
+          <t>ADO Kongress (Bericht), 08.09.–11.09.2027, Erlangen/Nürnberg
+WCLC (Bericht), 11.09.–14.09.2027, Denver
+DGU-Kongress (Bericht), 15.09.–18.09.2027, Frankfurt am Main</t>
         </is>
       </c>
     </row>
@@ -71008,7 +71081,7 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>DGHO-Jahrestagung 2027 (Bericht)</t>
+          <t>DGHO Jahrestagung (Bericht), 08.10.–11.10.2027, Leipzig</t>
         </is>
       </c>
     </row>
@@ -71058,7 +71131,8 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>ESMO Congress 2027 (Bericht)</t>
+          <t>onko-update (Auslage), Januar 2028, Berlin
+ESMO Congress (Bericht), 17.09.–21.09.2027, Barcelona</t>
         </is>
       </c>
     </row>
@@ -71108,10 +71182,13 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>DGP Kongress (Auslage), 03.03.–06.03.2027, Köln
+          <t>GTH Jahrestagung (Auslage), 02.03.–05.03.2027, Hamburg
+DGP Kongress (Auslage), 03.03.–06.03.2027, Köln
+AEK Cancer Congress (Auslage), 03.03.–05.03.2027, Essen
+ISALXX (Auslage), 14.03.–17.03.2027, München
 AIO-Herbstkongress 2026 (Bericht), 19.11.–21.11.2026, Berlin
-ASH Annual Meeting 2026 (Bericht), 12.12.–15.12.2026, New Orleans
-SABCS 2026 (Bericht), 08.12.–11.12.2026, San Antonio</t>
+SABCS (Bericht), 08.12.–11.12.2026, San Antonio
+ASH Annual Meeting (Bericht), 12.12.–15.12.2026, New Orleans</t>
         </is>
       </c>
     </row>
@@ -71161,8 +71238,10 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>DCK (Auslage), 21.04.−23.04.2027, München
-ASCO-GI Cancers Symposium (Bericht), 21.01.–23.01.2027, San Francisco</t>
+          <t>DGIM Kongress (Auslage), 10.04.–13.04.2027, Wiesbaden
+DCK (Auslage), 21.04.–23.04.2027, München
+Röko (Auslage), 05.05.–07.05.2027, Leipzig
+ASCO-GI Symposium (Bericht), 21.01.–23.01.2027, San Francisco</t>
         </is>
       </c>
     </row>
@@ -71212,9 +71291,11 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>DGS Kongress (Auslage), 17.06.−19.06.2027, Berlin
+          <t>DGS Senologiekongress (Auslage), 17.06.–19.06.2027, Berlin
+EPCM Meeting (Auslage), 17.06.–18.06.2027, Hamburg
+DEGRO Kongress (Auslage), 24.06.–26.06.2027, Leipzig
 GTH Jahrestagung (Bericht), 02.03.–05.03.2027, Hamburg
-ACUTE LEUKEMIAS XX (Bericht), 14.04.–17.03.2027, München
+ISALXX (Bericht), 14.03.–17.03.2027, München
 SGBCC (Bericht), 17.03.–20.03.2027, Wien
 ELCC (Bericht), 17.03.–20.03.2027, München
 DGIM Kongress (Bericht), 10.04.–13.04.2027, Wiesbaden</t>
@@ -71267,7 +71348,10 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>DGT Jahrestagung (Auslage), 09.09.–11.09.2027, Mainz
+          <t>Heidelberger Myelomtage (Auslage), September, Heidelberg
+DGT Jahrestagung (Auslage), 08.09.–10.09.2027, Münster
+ADO Kongress (Auslage), 08.09.–11.09.2027, Erlangen/Nürnberg
+DGU-Kongress (Auslage), 15.09.–18.09.2027, Frankfurt am Main
 EADO Congress (Bericht), 15.04.–17.04.2027, Wien
 ASCO Annual Meeting (Bericht), 04.06.–08.06.2027, Chicago
 EHA Congress (Bericht), 10.06.–13.06.2027, Barcelona</t>
@@ -71320,11 +71404,11 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>DGHO Jahrestagung (Auslage), 08.11.−11.10.2027, Leipzig
+          <t>DGHO Jahrestagung (Auslage), 08.10.–11.10.2027, Leipzig
 ICML (Bericht), 15.06.–19.06.2027, Lugano
-DGS Jahreskongress (Bericht), 17.07.–19.06.2027, Berlin
-EPCM (Bericht), 08.09.–11.09.2027, Hamburg
-ESMO-GI Cancers Congress (Bericht), 30.06.–03.07.2027, Barcelona</t>
+DGS Senologiekongress (Bericht), 17.06.–19.06.2027, Berlin
+EPCM Meeting (Bericht), 17.06.–18.06.2027, Hamburg
+ESMO Gastrointestinal Cancers (Bericht), 30.06.–03.07.2027, Barcelona</t>
         </is>
       </c>
     </row>
@@ -71374,7 +71458,8 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>SOHO Annual Meeting  (Bericht), 25.08.–28.08.2027, Houston
+          <t>onko-update (Auslage), Januar 2028, Berlin
+SOHO Annual Meeting (Bericht), 25.08.–28.08.2027, Houston
 WCLC (Bericht), 11.09.–14.09.2027, Denver
 DGHO Jahrestagung (Bericht), 08.10.–11.10.2027, Leipzig</t>
         </is>
@@ -71428,8 +71513,11 @@
       <c r="J186" t="inlineStr">
         <is>
           <t>DGP Kongress (Auslage), 03.03.–06.03.2027, Köln
-68th ASH Annual Meeting and Exposition 2026 (ASH 2026) (Bericht)
-48th Annual San Antonio Breast Cancer Symposium (SABCS 2026)</t>
+AEK Cancer Congress (Auslage), 03.03.–05.03.2027, Essen
+DGHO Frühjahrstagung (Auslage), 12.03.2027, Berlin
+ISALXX (Auslage), 14.03.–17.03.2027, München
+SABCS (Bericht), 08.12.–11.12.2026, San Antonio
+ASH Annual Meeting (Bericht), 12.12.–15.12.2026, New Orleans</t>
         </is>
       </c>
     </row>
@@ -71480,10 +71568,11 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>DCK (Auslage), 21.04.−23.04.2027, München
-ASCO-GI Gastrointestinal Cancer Symposium 2027 (Bericht)
-Onkologie-Update-Seminar Berlin (Bericht)
-ASCO-GU Genitourinary Cancers Symposium 2027 (Bericht)</t>
+          <t>DGIM Kongress (Auslage), 10.04.–13.04.2027, Wiesbaden
+DCK (Auslage), 21.04.–23.04.2027, München
+ASCO-GI Symposium (Bericht), 21.01.–23.01.2027, San Francisco
+onko-update (Bericht), 22.01.–23.01.2027, Berlin
+ASCO-GU Symposium (Bericht), 11.02.–13.02.2027, San Francisco</t>
         </is>
       </c>
     </row>
@@ -71534,9 +71623,11 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>67. Kongress der Deutschen Gesellschaft für Pneumologie (DGP) (Bericht)
-DGHO Frühjahrstagung 2025 (Bericht)
-ACUTE LEUKEMIAS XX (ISAL) (Bericht)</t>
+          <t>Röko (Auslage), 05.05.–07.05.2027, Leipzig
+DGHNO-KHC Kongress (Auslage), 05.05.–08.05.2027, Dresden
+DGP Kongress (Bericht), 03.03.–06.03.2027, Köln
+DGHO Frühjahrstagung (Bericht), 12.03.2027, Berlin
+ISALXX (Bericht), 14.03.–17.03.2027, München</t>
         </is>
       </c>
     </row>
@@ -71587,10 +71678,12 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>DGS Kongress (Auslage), 17.06.−19.06.2027, Berlin
-European Lung Cancer Congress (ELCC 2027) (Bericht)
-23. EADO Congress (Bericht)
-8th European Myeloma Network Meeting (EMN) (Bericht)</t>
+          <t>DGS Senologiekongress (Auslage), 17.06.–19.06.2027, Berlin
+EPCM Meeting (Auslage), 17.06.–18.06.2027, Hamburg
+DEGRO Kongress (Auslage), 24.06.–26.06.2027, Leipzig
+ELCC (Bericht), 17.03.–20.03.2027, München
+EMN Meeting (Bericht), 08.04.–10.04.2027, Würzburg
+EADO Congress (Bericht), 15.04.–17.04.2027, Wien</t>
         </is>
       </c>
     </row>
@@ -71641,8 +71734,9 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>ASCO Annual Meeting (Bericht), 04.–08.06.2027, Chicago
-ESMO Breast Cancer Congress 2027 (Bericht)</t>
+          <t>DGT Jahrestagung (Auslage), 08.09.–10.09.2027, Münster
+ESMO Breast Cancer (Bericht), 12.05.–14.05.2027, Mailand
+ASCO Annual Meeting (Bericht), 04.06.–08.06.2027, Chicago</t>
         </is>
       </c>
     </row>
@@ -71693,9 +71787,12 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>EHA Congress (Bericht), 13.–17.06.2027, Barcelona
-ESMO Gynaecological Cancers Congress 2026 (Bericht)
-46. Jahreskongress der DGS e.V. 2027 (Bericht)</t>
+          <t>Heidelberger Myelomtage (Auslage), September, Heidelberg
+ADO Kongress (Auslage), 08.09.–11.09.2027, Erlangen/Nürnberg
+DGU-Kongress (Auslage), 15.09.–18.09.2027, Frankfurt am Main
+EHA Congress (Bericht), 10.06.–13.06.2027, Barcelona
+ESMO Gynaecological Cancers (Bericht), 16.06.–18.06.2027, Wien
+DGS Senologiekongress (Bericht), 17.06.–19.06.2027, Berlin</t>
         </is>
       </c>
     </row>
@@ -71746,10 +71843,10 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>DGHO Jahrestagung (Auslage), 08.11.−11.10.2027, Leipzig
-19th International Conference on Malignant Lymphoma (ICML 2027) (Bericht)
-15th European Post-Chicago Melanoma/Skin Cancer Meeting 2027 (Bericht)
-ESMO Gastrointestinal Cancers Congress 2027 (Bericht)</t>
+          <t>DGHO Jahrestagung (Auslage), 08.10.–11.10.2027, Leipzig
+ICML (Bericht), 15.06.–19.06.2027, Lugano
+EPCM Meeting (Bericht), 17.06.–18.06.2027, Hamburg
+ESMO Gastrointestinal Cancers (Bericht), 30.06.–03.07.2027, Barcelona</t>
         </is>
       </c>
     </row>
@@ -71800,9 +71897,9 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>SOHO 2027 Annual Meeting  (Bericht)
-37. Deutscher Hautkrebskongress (ADO 2027) (Bericht)
-World Conference on Lung Cancer (WCLC 2027) (Bericht)</t>
+          <t>SOHO Annual Meeting (Bericht), 25.08.–28.08.2027, Houston
+ADO Kongress (Bericht), 08.09.–11.09.2027, Erlangen/Nürnberg
+WCLC (Bericht), 11.09.–14.09.2027, Denver</t>
         </is>
       </c>
     </row>
@@ -71853,8 +71950,8 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>DGHO Jahrestagung (Bericht), 08.11.−11.10.2027, Leipzig
-79. Jahreskongress der Deutschen Gesellschaft für Urologie (DGU 2027) (Bericht)</t>
+          <t>DGU-Kongress (Bericht), 15.09.–18.09.2027, Frankfurt am Main
+DGHO Jahrestagung (Bericht), 08.10.–11.10.2027, Leipzig</t>
         </is>
       </c>
     </row>
@@ -71905,7 +72002,8 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>ESMO Congress 2027 (Bericht)</t>
+          <t>onko-update (Auslage), Januar 2028, Berlin
+ESMO Congress (Bericht), 17.09.–21.09.2027, Barcelona</t>
         </is>
       </c>
     </row>

--- a/Angebotsdaten.xlsx
+++ b/Angebotsdaten.xlsx
@@ -68923,7 +68923,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>3–4</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -74971,6 +74971,11 @@
           <t>16.02.</t>
         </is>
       </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Junge Pneumologinnen und Pneumologen: Welche Wege gibt es in die Praxis, in die Klinik und in die Forschung?</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -75011,6 +75016,11 @@
           <t>13.04.</t>
         </is>
       </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Interstitielle Lungenerkrankungen</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -75051,6 +75061,11 @@
           <t>15.06.</t>
         </is>
       </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Pneumonie</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -75091,6 +75106,11 @@
           <t>24.08.</t>
         </is>
       </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Schlafmedizin</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -75131,6 +75151,11 @@
           <t>18.10.</t>
         </is>
       </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Eosinophile Systemerkrankungen: Asthma, EGPA und HES im interdisziplinären Fokus</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -75169,6 +75194,11 @@
       <c r="H271" t="inlineStr">
         <is>
           <t>30.11.</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Der pneumologische Patient auf Reisen: Höhen- und Tauchmedizin</t>
         </is>
       </c>
     </row>

--- a/Angebotsdaten.xlsx
+++ b/Angebotsdaten.xlsx
@@ -689,14 +689,14 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
+          <t>2/1 Doppelseite</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3475</v>
+        <v>6950</v>
       </c>
       <c r="G2" t="n">
-        <v>1780</v>
+        <v>2670</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -738,14 +738,14 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1/2 Seite</t>
+          <t>1/1 Seite</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2265</v>
+        <v>3475</v>
       </c>
       <c r="G3" t="n">
-        <v>1335</v>
+        <v>1780</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -787,14 +787,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1/3 Seite</t>
+          <t>1/2 Seite</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1700</v>
+        <v>2265</v>
       </c>
       <c r="G4" t="n">
-        <v>890</v>
+        <v>1335</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -836,11 +836,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1/4 Seite</t>
+          <t>1/3 Seite</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1390</v>
+        <v>1700</v>
       </c>
       <c r="G5" t="n">
         <v>890</v>
@@ -885,14 +885,14 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2/1 Doppelseite</t>
+          <t>1/4 Seite</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6950</v>
+        <v>1390</v>
       </c>
       <c r="G6" t="n">
-        <v>2670</v>
+        <v>890</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2825,11 +2825,11 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1/1 Seite 4c</t>
+          <t>2/1 Doppelseite</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>5435</v>
+        <v>9975</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2871,11 +2871,11 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1/2 Seite 4c</t>
+          <t>1/1 Seite 4c</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>3500</v>
+        <v>5435</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2917,11 +2917,11 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1/3 Seite 4c</t>
+          <t>1/2 Seite 4c</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2575</v>
+        <v>3500</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2963,11 +2963,11 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1/4 Seite 4c</t>
+          <t>1/3 Seite 4c</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2165</v>
+        <v>2575</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3009,11 +3009,11 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2/1 Doppelseite</t>
+          <t>1/4 Seite 4c</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>9975</v>
+        <v>2165</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -4907,11 +4907,11 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1/1 Seite 4c</t>
+          <t>2/1 Doppelseite</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>5435</v>
+        <v>9975</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -4953,11 +4953,11 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1/2 Seite 4c</t>
+          <t>1/1 Seite 4c</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>3500</v>
+        <v>5435</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -4999,11 +4999,11 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1/3 Seite 4c</t>
+          <t>1/2 Seite 4c</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>2575</v>
+        <v>3500</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -5045,11 +5045,11 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1/4 Seite 4c</t>
+          <t>1/3 Seite 4c</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>2165</v>
+        <v>2575</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -5091,11 +5091,11 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2/1 Doppelseite</t>
+          <t>1/4 Seite 4c</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>9975</v>
+        <v>2165</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -6948,14 +6948,14 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
+          <t>2/1 Doppelseite</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>3630</v>
+        <v>7260</v>
       </c>
       <c r="G140" t="n">
-        <v>1780</v>
+        <v>2670</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -6997,14 +6997,14 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>1/2 Seite</t>
+          <t>1/1 Seite</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>2345</v>
+        <v>3630</v>
       </c>
       <c r="G141" t="n">
-        <v>1335</v>
+        <v>1780</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -7046,14 +7046,14 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>1/3 Seite</t>
+          <t>1/2 Seite</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1750</v>
+        <v>2345</v>
       </c>
       <c r="G142" t="n">
-        <v>890</v>
+        <v>1335</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -7095,11 +7095,11 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>1/4 Seite</t>
+          <t>1/3 Seite</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1440</v>
+        <v>1750</v>
       </c>
       <c r="G143" t="n">
         <v>890</v>
@@ -7144,14 +7144,14 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2/1 Doppelseite</t>
+          <t>1/4 Seite</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>7260</v>
+        <v>1440</v>
       </c>
       <c r="G144" t="n">
-        <v>2670</v>
+        <v>890</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -9186,14 +9186,14 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
+          <t>2/1 Doppelseite</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>3605</v>
+        <v>7210</v>
       </c>
       <c r="G189" t="n">
-        <v>1780</v>
+        <v>2670</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -9235,14 +9235,14 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>1/2 Seite</t>
+          <t>1/1 Seite</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>2345</v>
+        <v>3605</v>
       </c>
       <c r="G190" t="n">
-        <v>1335</v>
+        <v>1780</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -9284,14 +9284,14 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>1/3 Seite</t>
+          <t>1/2 Seite</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>1725</v>
+        <v>2345</v>
       </c>
       <c r="G191" t="n">
-        <v>890</v>
+        <v>1335</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -9333,11 +9333,11 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>1/4 Seite</t>
+          <t>1/3 Seite</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>1440</v>
+        <v>1725</v>
       </c>
       <c r="G192" t="n">
         <v>890</v>
@@ -9382,14 +9382,14 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2/1 Doppelseite</t>
+          <t>1/4 Seite</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>7210</v>
+        <v>1440</v>
       </c>
       <c r="G193" t="n">
-        <v>2670</v>
+        <v>890</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -11378,11 +11378,11 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>A4 Seite hoch</t>
+          <t>3/4 Seite quer</t>
         </is>
       </c>
       <c r="F237" t="n">
-        <v>3555</v>
+        <v>3810</v>
       </c>
       <c r="G237" t="n">
         <v>1780</v>
@@ -11427,14 +11427,14 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>A5 Seite hoch</t>
+          <t>A4 Seite hoch</t>
         </is>
       </c>
       <c r="F238" t="n">
-        <v>2575</v>
+        <v>3555</v>
       </c>
       <c r="G238" t="n">
-        <v>1335</v>
+        <v>1780</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -11476,11 +11476,11 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>3/4 Seite quer</t>
+          <t>1/2 Seite quer</t>
         </is>
       </c>
       <c r="F239" t="n">
-        <v>3810</v>
+        <v>3195</v>
       </c>
       <c r="G239" t="n">
         <v>1780</v>
@@ -11525,14 +11525,14 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>1/2 Seite quer</t>
+          <t>1/3 Seite quer</t>
         </is>
       </c>
       <c r="F240" t="n">
-        <v>3195</v>
+        <v>2665</v>
       </c>
       <c r="G240" t="n">
-        <v>1780</v>
+        <v>1335</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -11574,11 +11574,11 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>1/3 Seite quer</t>
+          <t>A5 Seite hoch</t>
         </is>
       </c>
       <c r="F241" t="n">
-        <v>2665</v>
+        <v>2575</v>
       </c>
       <c r="G241" t="n">
         <v>1335</v>

--- a/Angebotsdaten.xlsx
+++ b/Angebotsdaten.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Staffeln" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Preise'!$A$1:$L$1761</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Preise'!$A$1:$L$1763</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Termine'!$A$1:$J$375</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Staffeln'!$A$1:$E$17</definedName>
   </definedNames>
@@ -636,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1761"/>
+  <dimension ref="A1:L1763"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -64282,11 +64282,8 @@
       </c>
       <c r="E1406" t="inlineStr">
         <is>
-          <t>1/1 Seite 4c</t>
-        </is>
-      </c>
-      <c r="F1406" t="n">
-        <v>4170</v>
+          <t>2/1 Doppelseite 4c</t>
+        </is>
       </c>
       <c r="H1406" t="inlineStr">
         <is>
@@ -64307,6 +64304,9 @@
         <is>
           <t>Pneumologie</t>
         </is>
+      </c>
+      <c r="L1406" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="1407">
@@ -64328,11 +64328,11 @@
       </c>
       <c r="E1407" t="inlineStr">
         <is>
-          <t>1/2 Seite 4c</t>
+          <t>1/1 Seite 4c</t>
         </is>
       </c>
       <c r="F1407" t="n">
-        <v>2670</v>
+        <v>4170</v>
       </c>
       <c r="H1407" t="inlineStr">
         <is>
@@ -64353,6 +64353,9 @@
         <is>
           <t>Pneumologie</t>
         </is>
+      </c>
+      <c r="L1407" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1408">
@@ -64374,11 +64377,11 @@
       </c>
       <c r="E1408" t="inlineStr">
         <is>
-          <t>1/3 Seite 4c</t>
+          <t>1/2 Seite 4c</t>
         </is>
       </c>
       <c r="F1408" t="n">
-        <v>1920</v>
+        <v>2670</v>
       </c>
       <c r="H1408" t="inlineStr">
         <is>
@@ -64399,6 +64402,9 @@
         <is>
           <t>Pneumologie</t>
         </is>
+      </c>
+      <c r="L1408" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="1409">
@@ -64420,11 +64426,11 @@
       </c>
       <c r="E1409" t="inlineStr">
         <is>
-          <t>1/4 Seite 4c</t>
+          <t>1/3 Seite 4c</t>
         </is>
       </c>
       <c r="F1409" t="n">
-        <v>1710</v>
+        <v>1920</v>
       </c>
       <c r="H1409" t="inlineStr">
         <is>
@@ -64445,6 +64451,9 @@
         <is>
           <t>Pneumologie</t>
         </is>
+      </c>
+      <c r="L1409" t="n">
+        <v>0.33</v>
       </c>
     </row>
     <row r="1410">
@@ -65333,11 +65342,11 @@
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>PNEUMONEWS</t>
+          <t>Zeitschrift für Pneumologie</t>
         </is>
       </c>
       <c r="C1430" t="n">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="D1430" t="inlineStr">
         <is>
@@ -65346,11 +65355,11 @@
       </c>
       <c r="E1430" t="inlineStr">
         <is>
-          <t>1/1 Seite 4c</t>
+          <t>1/4 Seite 4c</t>
         </is>
       </c>
       <c r="F1430" t="n">
-        <v>4100</v>
+        <v>1710</v>
       </c>
       <c r="H1430" t="inlineStr">
         <is>
@@ -65371,6 +65380,9 @@
         <is>
           <t>Pneumologie</t>
         </is>
+      </c>
+      <c r="L1430" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="1431">
@@ -65392,11 +65404,8 @@
       </c>
       <c r="E1431" t="inlineStr">
         <is>
-          <t>1/2 Seite 4c</t>
-        </is>
-      </c>
-      <c r="F1431" t="n">
-        <v>2820</v>
+          <t>2/1 Doppelseite im Text 4c</t>
+        </is>
       </c>
       <c r="H1431" t="inlineStr">
         <is>
@@ -65417,6 +65426,9 @@
         <is>
           <t>Pneumologie</t>
         </is>
+      </c>
+      <c r="L1431" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="1432">
@@ -65438,11 +65450,11 @@
       </c>
       <c r="E1432" t="inlineStr">
         <is>
-          <t>1/3 Seite 4c</t>
+          <t>1/1 Seite 4c</t>
         </is>
       </c>
       <c r="F1432" t="n">
-        <v>1930</v>
+        <v>4100</v>
       </c>
       <c r="H1432" t="inlineStr">
         <is>
@@ -65463,6 +65475,9 @@
         <is>
           <t>Pneumologie</t>
         </is>
+      </c>
+      <c r="L1432" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1433">
@@ -65484,11 +65499,11 @@
       </c>
       <c r="E1433" t="inlineStr">
         <is>
-          <t>1/4 Seite 4c</t>
+          <t>1/2 Seite 4c</t>
         </is>
       </c>
       <c r="F1433" t="n">
-        <v>1730</v>
+        <v>2820</v>
       </c>
       <c r="H1433" t="inlineStr">
         <is>
@@ -65509,6 +65524,9 @@
         <is>
           <t>Pneumologie</t>
         </is>
+      </c>
+      <c r="L1433" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="1434">
@@ -65525,16 +65543,16 @@
       </c>
       <c r="D1434" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1434" t="inlineStr">
         <is>
-          <t>2. Umschlagseite</t>
+          <t>1/3 Seite 4c</t>
         </is>
       </c>
       <c r="F1434" t="n">
-        <v>4400</v>
+        <v>1930</v>
       </c>
       <c r="H1434" t="inlineStr">
         <is>
@@ -65555,6 +65573,9 @@
         <is>
           <t>Pneumologie</t>
         </is>
+      </c>
+      <c r="L1434" t="n">
+        <v>0.33</v>
       </c>
     </row>
     <row r="1435">
@@ -65576,7 +65597,7 @@
       </c>
       <c r="E1435" t="inlineStr">
         <is>
-          <t>4. Umschlagseite</t>
+          <t>2. Umschlagseite</t>
         </is>
       </c>
       <c r="F1435" t="n">
@@ -65601,6 +65622,9 @@
         <is>
           <t>Pneumologie</t>
         </is>
+      </c>
+      <c r="L1435" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1436">
@@ -65622,7 +65646,7 @@
       </c>
       <c r="E1436" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt</t>
+          <t>4. Umschlagseite</t>
         </is>
       </c>
       <c r="F1436" t="n">
@@ -65647,6 +65671,9 @@
         <is>
           <t>Pneumologie</t>
         </is>
+      </c>
+      <c r="L1436" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1437">
@@ -65663,20 +65690,20 @@
       </c>
       <c r="D1437" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1437" t="inlineStr">
         <is>
-          <t>EH/DH 1 Seite</t>
+          <t>Seite ggü. Inhalt</t>
         </is>
       </c>
       <c r="F1437" t="n">
-        <v>2200</v>
+        <v>4400</v>
       </c>
       <c r="H1437" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="I1437" t="inlineStr">
@@ -65686,13 +65713,16 @@
       </c>
       <c r="J1437" t="inlineStr">
         <is>
-          <t>EH</t>
+          <t>DU</t>
         </is>
       </c>
       <c r="K1437" t="inlineStr">
         <is>
           <t>Pneumologie</t>
         </is>
+      </c>
+      <c r="L1437" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1438">
@@ -65714,11 +65744,11 @@
       </c>
       <c r="E1438" t="inlineStr">
         <is>
-          <t>EH/DH 2 Seiten</t>
+          <t>EH/DH 1 Seite</t>
         </is>
       </c>
       <c r="F1438" t="n">
-        <v>4400</v>
+        <v>2200</v>
       </c>
       <c r="H1438" t="inlineStr">
         <is>
@@ -65755,16 +65785,16 @@
       </c>
       <c r="D1439" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1439" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (pro 1.000)</t>
+          <t>EH/DH 2 Seiten</t>
         </is>
       </c>
       <c r="F1439" t="n">
-        <v>410</v>
+        <v>4400</v>
       </c>
       <c r="H1439" t="inlineStr">
         <is>
@@ -65801,16 +65831,16 @@
       </c>
       <c r="D1440" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1440" t="inlineStr">
         <is>
-          <t>Titelklappe</t>
+          <t>Werbebeilage bis 25g (pro 1.000)</t>
         </is>
       </c>
       <c r="F1440" t="n">
-        <v>6040</v>
+        <v>410</v>
       </c>
       <c r="H1440" t="inlineStr">
         <is>
@@ -65824,7 +65854,7 @@
       </c>
       <c r="J1440" t="inlineStr">
         <is>
-          <t>DU</t>
+          <t>EH</t>
         </is>
       </c>
       <c r="K1440" t="inlineStr">
@@ -65852,11 +65882,11 @@
       </c>
       <c r="E1441" t="inlineStr">
         <is>
-          <t>French-Cover</t>
+          <t>Titelklappe</t>
         </is>
       </c>
       <c r="F1441" t="n">
-        <v>7600</v>
+        <v>6040</v>
       </c>
       <c r="H1441" t="inlineStr">
         <is>
@@ -65866,6 +65896,11 @@
       <c r="I1441" t="inlineStr">
         <is>
           <t>ja</t>
+        </is>
+      </c>
+      <c r="J1441" t="inlineStr">
+        <is>
+          <t>DU</t>
         </is>
       </c>
       <c r="K1441" t="inlineStr">
@@ -65893,11 +65928,11 @@
       </c>
       <c r="E1442" t="inlineStr">
         <is>
-          <t>halbe ausklappbare 2.US</t>
+          <t>French-Cover</t>
         </is>
       </c>
       <c r="F1442" t="n">
-        <v>6070</v>
+        <v>7600</v>
       </c>
       <c r="H1442" t="inlineStr">
         <is>
@@ -65934,11 +65969,11 @@
       </c>
       <c r="E1443" t="inlineStr">
         <is>
-          <t>ausklappbare 2.US</t>
+          <t>halbe ausklappbare 2.US</t>
         </is>
       </c>
       <c r="F1443" t="n">
-        <v>7600</v>
+        <v>6070</v>
       </c>
       <c r="H1443" t="inlineStr">
         <is>
@@ -65975,11 +66010,11 @@
       </c>
       <c r="E1444" t="inlineStr">
         <is>
-          <t>Sogbanderole</t>
+          <t>ausklappbare 2.US</t>
         </is>
       </c>
       <c r="F1444" t="n">
-        <v>5400</v>
+        <v>7600</v>
       </c>
       <c r="H1444" t="inlineStr">
         <is>
@@ -66016,11 +66051,11 @@
       </c>
       <c r="E1445" t="inlineStr">
         <is>
-          <t>Pfeilbanderole</t>
+          <t>Sogbanderole</t>
         </is>
       </c>
       <c r="F1445" t="n">
-        <v>9670</v>
+        <v>5400</v>
       </c>
       <c r="H1445" t="inlineStr">
         <is>
@@ -66030,11 +66065,6 @@
       <c r="I1445" t="inlineStr">
         <is>
           <t>ja</t>
-        </is>
-      </c>
-      <c r="J1445" t="inlineStr">
-        <is>
-          <t>DU</t>
         </is>
       </c>
       <c r="K1445" t="inlineStr">
@@ -66062,11 +66092,11 @@
       </c>
       <c r="E1446" t="inlineStr">
         <is>
-          <t>Flipp-Einhefter</t>
+          <t>Pfeilbanderole</t>
         </is>
       </c>
       <c r="F1446" t="n">
-        <v>8750</v>
+        <v>9670</v>
       </c>
       <c r="H1446" t="inlineStr">
         <is>
@@ -66076,6 +66106,11 @@
       <c r="I1446" t="inlineStr">
         <is>
           <t>ja</t>
+        </is>
+      </c>
+      <c r="J1446" t="inlineStr">
+        <is>
+          <t>DU</t>
         </is>
       </c>
       <c r="K1446" t="inlineStr">
@@ -66103,11 +66138,11 @@
       </c>
       <c r="E1447" t="inlineStr">
         <is>
-          <t>Tip-On-Element</t>
+          <t>Flipp-Einhefter</t>
         </is>
       </c>
       <c r="F1447" t="n">
-        <v>1490</v>
+        <v>8750</v>
       </c>
       <c r="H1447" t="inlineStr">
         <is>
@@ -66144,11 +66179,11 @@
       </c>
       <c r="E1448" t="inlineStr">
         <is>
-          <t>Oversize-Beilage</t>
+          <t>Tip-On-Element</t>
         </is>
       </c>
       <c r="F1448" t="n">
-        <v>4000</v>
+        <v>1490</v>
       </c>
       <c r="H1448" t="inlineStr">
         <is>
@@ -66185,11 +66220,11 @@
       </c>
       <c r="E1449" t="inlineStr">
         <is>
-          <t>Lesezeichen mit Bändchen</t>
+          <t>Oversize-Beilage</t>
         </is>
       </c>
       <c r="F1449" t="n">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="H1449" t="inlineStr">
         <is>
@@ -66221,30 +66256,25 @@
       </c>
       <c r="D1450" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1450" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt Journal Screen</t>
+          <t>Lesezeichen mit Bändchen</t>
         </is>
       </c>
       <c r="F1450" t="n">
-        <v>4400</v>
+        <v>3500</v>
       </c>
       <c r="H1450" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="I1450" t="inlineStr">
         <is>
           <t>ja</t>
-        </is>
-      </c>
-      <c r="J1450" t="inlineStr">
-        <is>
-          <t>DU</t>
         </is>
       </c>
       <c r="K1450" t="inlineStr">
@@ -66267,20 +66297,20 @@
       </c>
       <c r="D1451" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1451" t="inlineStr">
         <is>
-          <t>EH/DH 4 Seiten</t>
+          <t>Seite ggü. Inhalt Journal Screen</t>
         </is>
       </c>
       <c r="F1451" t="n">
-        <v>8800</v>
+        <v>4400</v>
       </c>
       <c r="H1451" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="I1451" t="inlineStr">
@@ -66290,13 +66320,16 @@
       </c>
       <c r="J1451" t="inlineStr">
         <is>
-          <t>EH</t>
+          <t>DU</t>
         </is>
       </c>
       <c r="K1451" t="inlineStr">
         <is>
           <t>Pneumologie</t>
         </is>
+      </c>
+      <c r="L1451" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1452">
@@ -66318,11 +66351,11 @@
       </c>
       <c r="E1452" t="inlineStr">
         <is>
-          <t>V-Koop MWO/Wefra</t>
+          <t>EH/DH 4 Seiten</t>
         </is>
       </c>
       <c r="F1452" t="n">
-        <v>2710</v>
+        <v>8800</v>
       </c>
       <c r="H1452" t="inlineStr">
         <is>
@@ -66351,28 +66384,28 @@
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>Cardio News</t>
+          <t>PNEUMONEWS</t>
         </is>
       </c>
       <c r="C1453" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1453" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1453" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
+          <t>V-Koop MWO/Wefra</t>
         </is>
       </c>
       <c r="F1453" t="n">
-        <v>7760</v>
+        <v>2710</v>
       </c>
       <c r="H1453" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="I1453" t="inlineStr">
@@ -66382,12 +66415,12 @@
       </c>
       <c r="J1453" t="inlineStr">
         <is>
-          <t>DU</t>
+          <t>EH</t>
         </is>
       </c>
       <c r="K1453" t="inlineStr">
         <is>
-          <t>Kardiologie</t>
+          <t>Pneumologie</t>
         </is>
       </c>
     </row>
@@ -66397,11 +66430,11 @@
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>Cardio News</t>
+          <t>PNEUMONEWS</t>
         </is>
       </c>
       <c r="C1454" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1454" t="inlineStr">
         <is>
@@ -66410,11 +66443,11 @@
       </c>
       <c r="E1454" t="inlineStr">
         <is>
-          <t>A4 hoch</t>
+          <t>1/4 Seite 4c</t>
         </is>
       </c>
       <c r="F1454" t="n">
-        <v>6720</v>
+        <v>1730</v>
       </c>
       <c r="H1454" t="inlineStr">
         <is>
@@ -66433,8 +66466,11 @@
       </c>
       <c r="K1454" t="inlineStr">
         <is>
-          <t>Kardiologie</t>
-        </is>
+          <t>Pneumologie</t>
+        </is>
+      </c>
+      <c r="L1454" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="1455">
@@ -66456,11 +66492,11 @@
       </c>
       <c r="E1455" t="inlineStr">
         <is>
-          <t>3/4 Seite</t>
+          <t>1/1 Seite</t>
         </is>
       </c>
       <c r="F1455" t="n">
-        <v>7400</v>
+        <v>7760</v>
       </c>
       <c r="H1455" t="inlineStr">
         <is>
@@ -66502,11 +66538,11 @@
       </c>
       <c r="E1456" t="inlineStr">
         <is>
-          <t>3/5 Seite</t>
+          <t>A4 hoch</t>
         </is>
       </c>
       <c r="F1456" t="n">
-        <v>6100</v>
+        <v>6720</v>
       </c>
       <c r="H1456" t="inlineStr">
         <is>
@@ -66548,11 +66584,11 @@
       </c>
       <c r="E1457" t="inlineStr">
         <is>
-          <t>2/3 Seite</t>
+          <t>3/4 Seite</t>
         </is>
       </c>
       <c r="F1457" t="n">
-        <v>6000</v>
+        <v>7400</v>
       </c>
       <c r="H1457" t="inlineStr">
         <is>
@@ -66594,11 +66630,11 @@
       </c>
       <c r="E1458" t="inlineStr">
         <is>
-          <t>1/2 Seite</t>
+          <t>3/5 Seite</t>
         </is>
       </c>
       <c r="F1458" t="n">
-        <v>4900</v>
+        <v>6100</v>
       </c>
       <c r="H1458" t="inlineStr">
         <is>
@@ -66640,11 +66676,11 @@
       </c>
       <c r="E1459" t="inlineStr">
         <is>
-          <t>2/5 Seite</t>
+          <t>2/3 Seite</t>
         </is>
       </c>
       <c r="F1459" t="n">
-        <v>4380</v>
+        <v>6000</v>
       </c>
       <c r="H1459" t="inlineStr">
         <is>
@@ -66686,11 +66722,11 @@
       </c>
       <c r="E1460" t="inlineStr">
         <is>
-          <t>1/3 Seite</t>
+          <t>1/2 Seite</t>
         </is>
       </c>
       <c r="F1460" t="n">
-        <v>3700</v>
+        <v>4900</v>
       </c>
       <c r="H1460" t="inlineStr">
         <is>
@@ -66732,11 +66768,11 @@
       </c>
       <c r="E1461" t="inlineStr">
         <is>
-          <t>1/4 Seite</t>
+          <t>2/5 Seite</t>
         </is>
       </c>
       <c r="F1461" t="n">
-        <v>3690</v>
+        <v>4380</v>
       </c>
       <c r="H1461" t="inlineStr">
         <is>
@@ -66778,11 +66814,11 @@
       </c>
       <c r="E1462" t="inlineStr">
         <is>
-          <t>2/10 Seite</t>
+          <t>1/3 Seite</t>
         </is>
       </c>
       <c r="F1462" t="n">
-        <v>3590</v>
+        <v>3700</v>
       </c>
       <c r="H1462" t="inlineStr">
         <is>
@@ -66824,11 +66860,11 @@
       </c>
       <c r="E1463" t="inlineStr">
         <is>
-          <t>Tunnel groß</t>
+          <t>1/4 Seite</t>
         </is>
       </c>
       <c r="F1463" t="n">
-        <v>4690</v>
+        <v>3690</v>
       </c>
       <c r="H1463" t="inlineStr">
         <is>
@@ -66870,11 +66906,11 @@
       </c>
       <c r="E1464" t="inlineStr">
         <is>
-          <t>Insel maxi</t>
+          <t>2/10 Seite</t>
         </is>
       </c>
       <c r="F1464" t="n">
-        <v>4990</v>
+        <v>3590</v>
       </c>
       <c r="H1464" t="inlineStr">
         <is>
@@ -66911,16 +66947,16 @@
       </c>
       <c r="D1465" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1465" t="inlineStr">
         <is>
-          <t>Seite 2 A4</t>
+          <t>Tunnel groß</t>
         </is>
       </c>
       <c r="F1465" t="n">
-        <v>8170</v>
+        <v>4690</v>
       </c>
       <c r="H1465" t="inlineStr">
         <is>
@@ -66957,16 +66993,16 @@
       </c>
       <c r="D1466" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1466" t="inlineStr">
         <is>
-          <t>Seite 5 1/1</t>
+          <t>Insel maxi</t>
         </is>
       </c>
       <c r="F1466" t="n">
-        <v>8650</v>
+        <v>4990</v>
       </c>
       <c r="H1466" t="inlineStr">
         <is>
@@ -67008,11 +67044,11 @@
       </c>
       <c r="E1467" t="inlineStr">
         <is>
-          <t>Seite 5 A4</t>
+          <t>Seite 2 A4</t>
         </is>
       </c>
       <c r="F1467" t="n">
-        <v>7400</v>
+        <v>8170</v>
       </c>
       <c r="H1467" t="inlineStr">
         <is>
@@ -67054,11 +67090,11 @@
       </c>
       <c r="E1468" t="inlineStr">
         <is>
-          <t>Letzte Seite 1/1</t>
+          <t>Seite 5 1/1</t>
         </is>
       </c>
       <c r="F1468" t="n">
-        <v>8200</v>
+        <v>8650</v>
       </c>
       <c r="H1468" t="inlineStr">
         <is>
@@ -67100,11 +67136,11 @@
       </c>
       <c r="E1469" t="inlineStr">
         <is>
-          <t>Letzte Seite A4</t>
+          <t>Seite 5 A4</t>
         </is>
       </c>
       <c r="F1469" t="n">
-        <v>7080</v>
+        <v>7400</v>
       </c>
       <c r="H1469" t="inlineStr">
         <is>
@@ -67141,25 +67177,30 @@
       </c>
       <c r="D1470" t="inlineStr">
         <is>
-          <t>AdSpecials</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1470" t="inlineStr">
         <is>
-          <t>Banderole</t>
+          <t>Letzte Seite 1/1</t>
         </is>
       </c>
       <c r="F1470" t="n">
-        <v>9990</v>
+        <v>8200</v>
       </c>
       <c r="H1470" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="I1470" t="inlineStr">
         <is>
           <t>ja</t>
+        </is>
+      </c>
+      <c r="J1470" t="inlineStr">
+        <is>
+          <t>DU</t>
         </is>
       </c>
       <c r="K1470" t="inlineStr">
@@ -67174,24 +67215,24 @@
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>DGU Kongresszeitung</t>
+          <t>Cardio News</t>
         </is>
       </c>
       <c r="C1471" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D1471" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1471" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
+          <t>Letzte Seite A4</t>
         </is>
       </c>
       <c r="F1471" t="n">
-        <v>6100</v>
+        <v>7080</v>
       </c>
       <c r="H1471" t="inlineStr">
         <is>
@@ -67210,7 +67251,7 @@
       </c>
       <c r="K1471" t="inlineStr">
         <is>
-          <t>Urologie</t>
+          <t>Kardiologie</t>
         </is>
       </c>
     </row>
@@ -67220,28 +67261,28 @@
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>DGU Kongresszeitung</t>
+          <t>Cardio News</t>
         </is>
       </c>
       <c r="C1472" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D1472" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>AdSpecials</t>
         </is>
       </c>
       <c r="E1472" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>Banderole</t>
         </is>
       </c>
       <c r="F1472" t="n">
-        <v>5540</v>
+        <v>9990</v>
       </c>
       <c r="H1472" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="I1472" t="inlineStr">
@@ -67249,14 +67290,9 @@
           <t>ja</t>
         </is>
       </c>
-      <c r="J1472" t="inlineStr">
-        <is>
-          <t>DU</t>
-        </is>
-      </c>
       <c r="K1472" t="inlineStr">
         <is>
-          <t>Urologie</t>
+          <t>Kardiologie</t>
         </is>
       </c>
     </row>
@@ -67279,11 +67315,11 @@
       </c>
       <c r="E1473" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>1/1 Seite</t>
         </is>
       </c>
       <c r="F1473" t="n">
-        <v>4150</v>
+        <v>6100</v>
       </c>
       <c r="H1473" t="inlineStr">
         <is>
@@ -67325,11 +67361,11 @@
       </c>
       <c r="E1474" t="inlineStr">
         <is>
-          <t>3/4 Seite quer</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="F1474" t="n">
-        <v>5630</v>
+        <v>5540</v>
       </c>
       <c r="H1474" t="inlineStr">
         <is>
@@ -67371,11 +67407,11 @@
       </c>
       <c r="E1475" t="inlineStr">
         <is>
-          <t>1/2 Seite</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="F1475" t="n">
-        <v>5250</v>
+        <v>4150</v>
       </c>
       <c r="H1475" t="inlineStr">
         <is>
@@ -67417,11 +67453,11 @@
       </c>
       <c r="E1476" t="inlineStr">
         <is>
-          <t>1/4 seite</t>
+          <t>3/4 Seite quer</t>
         </is>
       </c>
       <c r="F1476" t="n">
-        <v>2850</v>
+        <v>5630</v>
       </c>
       <c r="H1476" t="inlineStr">
         <is>
@@ -67458,16 +67494,16 @@
       </c>
       <c r="D1477" t="inlineStr">
         <is>
-          <t>Sonderplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1477" t="inlineStr">
         <is>
-          <t>Titelseitenfuß</t>
+          <t>1/2 Seite</t>
         </is>
       </c>
       <c r="F1477" t="n">
-        <v>5300</v>
+        <v>5250</v>
       </c>
       <c r="H1477" t="inlineStr">
         <is>
@@ -67504,20 +67540,20 @@
       </c>
       <c r="D1478" t="inlineStr">
         <is>
-          <t>Sonderplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1478" t="inlineStr">
         <is>
-          <t>Insel</t>
+          <t>1/4 seite</t>
         </is>
       </c>
       <c r="F1478" t="n">
-        <v>3260</v>
+        <v>2850</v>
       </c>
       <c r="H1478" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="I1478" t="inlineStr">
@@ -67555,7 +67591,7 @@
       </c>
       <c r="E1479" t="inlineStr">
         <is>
-          <t>Insel maxi</t>
+          <t>Titelseitenfuß</t>
         </is>
       </c>
       <c r="F1479" t="n">
@@ -67563,7 +67599,7 @@
       </c>
       <c r="H1479" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="I1479" t="inlineStr">
@@ -67601,11 +67637,11 @@
       </c>
       <c r="E1480" t="inlineStr">
         <is>
-          <t>Tunnel klein</t>
+          <t>Insel</t>
         </is>
       </c>
       <c r="F1480" t="n">
-        <v>2930</v>
+        <v>3260</v>
       </c>
       <c r="H1480" t="inlineStr">
         <is>
@@ -67647,11 +67683,11 @@
       </c>
       <c r="E1481" t="inlineStr">
         <is>
-          <t>Tunnel groß</t>
+          <t>Insel maxi</t>
         </is>
       </c>
       <c r="F1481" t="n">
-        <v>4160</v>
+        <v>5300</v>
       </c>
       <c r="H1481" t="inlineStr">
         <is>
@@ -67693,11 +67729,11 @@
       </c>
       <c r="E1482" t="inlineStr">
         <is>
-          <t>Großumleger</t>
+          <t>Tunnel klein</t>
         </is>
       </c>
       <c r="F1482" t="n">
-        <v>18500</v>
+        <v>2930</v>
       </c>
       <c r="H1482" t="inlineStr">
         <is>
@@ -67739,11 +67775,11 @@
       </c>
       <c r="E1483" t="inlineStr">
         <is>
-          <t>Titelseite + 2.Seite</t>
+          <t>Tunnel groß</t>
         </is>
       </c>
       <c r="F1483" t="n">
-        <v>14900</v>
+        <v>4160</v>
       </c>
       <c r="H1483" t="inlineStr">
         <is>
@@ -67785,11 +67821,11 @@
       </c>
       <c r="E1484" t="inlineStr">
         <is>
-          <t>Transparenzumleger</t>
+          <t>Großumleger</t>
         </is>
       </c>
       <c r="F1484" t="n">
-        <v>14900</v>
+        <v>18500</v>
       </c>
       <c r="H1484" t="inlineStr">
         <is>
@@ -67831,11 +67867,11 @@
       </c>
       <c r="E1485" t="inlineStr">
         <is>
-          <t>Banderole</t>
+          <t>Titelseite + 2.Seite</t>
         </is>
       </c>
       <c r="F1485" t="n">
-        <v>5100</v>
+        <v>14900</v>
       </c>
       <c r="H1485" t="inlineStr">
         <is>
@@ -67849,7 +67885,7 @@
       </c>
       <c r="J1485" t="inlineStr">
         <is>
-          <t>EH</t>
+          <t>DU</t>
         </is>
       </c>
       <c r="K1485" t="inlineStr">
@@ -67877,11 +67913,11 @@
       </c>
       <c r="E1486" t="inlineStr">
         <is>
-          <t>Aufkleber + Trägeranzeige</t>
+          <t>Transparenzumleger</t>
         </is>
       </c>
       <c r="F1486" t="n">
-        <v>2300</v>
+        <v>14900</v>
       </c>
       <c r="H1486" t="inlineStr">
         <is>
@@ -67895,7 +67931,7 @@
       </c>
       <c r="J1486" t="inlineStr">
         <is>
-          <t>EH</t>
+          <t>DU</t>
         </is>
       </c>
       <c r="K1486" t="inlineStr">
@@ -67918,16 +67954,16 @@
       </c>
       <c r="D1487" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Sonderplatzierungen</t>
         </is>
       </c>
       <c r="E1487" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (pro 1.000)</t>
+          <t>Banderole</t>
         </is>
       </c>
       <c r="F1487" t="n">
-        <v>580</v>
+        <v>5100</v>
       </c>
       <c r="H1487" t="inlineStr">
         <is>
@@ -67952,25 +67988,28 @@
     </row>
     <row r="1488">
       <c r="A1488" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>Die Onkologie</t>
+          <t>DGU Kongresszeitung</t>
         </is>
       </c>
       <c r="C1488" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="D1488" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderplatzierungen</t>
         </is>
       </c>
       <c r="E1488" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
-        </is>
+          <t>Aufkleber + Trägeranzeige</t>
+        </is>
+      </c>
+      <c r="F1488" t="n">
+        <v>2300</v>
       </c>
       <c r="H1488" t="inlineStr">
         <is>
@@ -67982,33 +68021,41 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J1488" t="inlineStr">
+        <is>
+          <t>EH</t>
+        </is>
+      </c>
       <c r="K1488" t="inlineStr">
         <is>
-          <t>Onkologie</t>
+          <t>Urologie</t>
         </is>
       </c>
     </row>
     <row r="1489">
       <c r="A1489" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>Die Onkologie</t>
+          <t>DGU Kongresszeitung</t>
         </is>
       </c>
       <c r="C1489" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="D1489" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1489" t="inlineStr">
         <is>
-          <t>1/2 Seite</t>
-        </is>
+          <t>Werbebeilage bis 25g (pro 1.000)</t>
+        </is>
+      </c>
+      <c r="F1489" t="n">
+        <v>580</v>
       </c>
       <c r="H1489" t="inlineStr">
         <is>
@@ -68020,9 +68067,14 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J1489" t="inlineStr">
+        <is>
+          <t>EH</t>
+        </is>
+      </c>
       <c r="K1489" t="inlineStr">
         <is>
-          <t>Onkologie</t>
+          <t>Urologie</t>
         </is>
       </c>
     </row>
@@ -68045,7 +68097,7 @@
       </c>
       <c r="E1490" t="inlineStr">
         <is>
-          <t>1/3 Seite</t>
+          <t>1/1 Seite</t>
         </is>
       </c>
       <c r="H1490" t="inlineStr">
@@ -68083,7 +68135,7 @@
       </c>
       <c r="E1491" t="inlineStr">
         <is>
-          <t>1/4 Seite</t>
+          <t>1/2 Seite</t>
         </is>
       </c>
       <c r="H1491" t="inlineStr">
@@ -68121,7 +68173,7 @@
       </c>
       <c r="E1492" t="inlineStr">
         <is>
-          <t>2/1 Doppelseite</t>
+          <t>1/3 Seite</t>
         </is>
       </c>
       <c r="H1492" t="inlineStr">
@@ -68159,7 +68211,7 @@
       </c>
       <c r="E1493" t="inlineStr">
         <is>
-          <t>Advertorial (1/1 Seite)</t>
+          <t>1/4 Seite</t>
         </is>
       </c>
       <c r="H1493" t="inlineStr">
@@ -68192,12 +68244,12 @@
       </c>
       <c r="D1494" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1494" t="inlineStr">
         <is>
-          <t>4. Umschlagseite</t>
+          <t>2/1 Doppelseite</t>
         </is>
       </c>
       <c r="H1494" t="inlineStr">
@@ -68230,12 +68282,12 @@
       </c>
       <c r="D1495" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1495" t="inlineStr">
         <is>
-          <t>2. Umschlagseite</t>
+          <t>Advertorial (1/1 Seite)</t>
         </is>
       </c>
       <c r="H1495" t="inlineStr">
@@ -68273,7 +68325,7 @@
       </c>
       <c r="E1496" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt / red. Info</t>
+          <t>4. Umschlagseite</t>
         </is>
       </c>
       <c r="H1496" t="inlineStr">
@@ -68311,7 +68363,7 @@
       </c>
       <c r="E1497" t="inlineStr">
         <is>
-          <t>Seite ggü. Hrsg. 1</t>
+          <t>2. Umschlagseite</t>
         </is>
       </c>
       <c r="H1497" t="inlineStr">
@@ -68349,7 +68401,7 @@
       </c>
       <c r="E1498" t="inlineStr">
         <is>
-          <t>Seite ggü. Hrsg. 2</t>
+          <t>Seite ggü. Inhalt / red. Info</t>
         </is>
       </c>
       <c r="H1498" t="inlineStr">
@@ -68387,7 +68439,7 @@
       </c>
       <c r="E1499" t="inlineStr">
         <is>
-          <t>Seite ggü. Textanfang</t>
+          <t>Seite ggü. Hrsg. 1</t>
         </is>
       </c>
       <c r="H1499" t="inlineStr">
@@ -68425,7 +68477,7 @@
       </c>
       <c r="E1500" t="inlineStr">
         <is>
-          <t>1/1 Seite Festplatzierung</t>
+          <t>Seite ggü. Hrsg. 2</t>
         </is>
       </c>
       <c r="H1500" t="inlineStr">
@@ -68463,7 +68515,7 @@
       </c>
       <c r="E1501" t="inlineStr">
         <is>
-          <t>1. rechte Einschaltseite</t>
+          <t>Seite ggü. Textanfang</t>
         </is>
       </c>
       <c r="H1501" t="inlineStr">
@@ -68501,7 +68553,7 @@
       </c>
       <c r="E1502" t="inlineStr">
         <is>
-          <t>2. rechte Einschaltseite</t>
+          <t>1/1 Seite Festplatzierung</t>
         </is>
       </c>
       <c r="H1502" t="inlineStr">
@@ -68539,7 +68591,7 @@
       </c>
       <c r="E1503" t="inlineStr">
         <is>
-          <t>3. rechte Einschaltseite</t>
+          <t>1. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1503" t="inlineStr">
@@ -68577,7 +68629,7 @@
       </c>
       <c r="E1504" t="inlineStr">
         <is>
-          <t>4. rechte Einschaltseite</t>
+          <t>2. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1504" t="inlineStr">
@@ -68615,7 +68667,7 @@
       </c>
       <c r="E1505" t="inlineStr">
         <is>
-          <t>5. rechte Einschaltseite</t>
+          <t>3. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1505" t="inlineStr">
@@ -68653,7 +68705,7 @@
       </c>
       <c r="E1506" t="inlineStr">
         <is>
-          <t>6. rechte Einschaltseite</t>
+          <t>4. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1506" t="inlineStr">
@@ -68691,7 +68743,7 @@
       </c>
       <c r="E1507" t="inlineStr">
         <is>
-          <t>7. rechte Einschaltseite</t>
+          <t>5. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1507" t="inlineStr">
@@ -68729,7 +68781,7 @@
       </c>
       <c r="E1508" t="inlineStr">
         <is>
-          <t>8. rechte Einschaltseite</t>
+          <t>6. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1508" t="inlineStr">
@@ -68767,7 +68819,7 @@
       </c>
       <c r="E1509" t="inlineStr">
         <is>
-          <t>9. rechte Einschaltseite</t>
+          <t>7. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1509" t="inlineStr">
@@ -68805,7 +68857,7 @@
       </c>
       <c r="E1510" t="inlineStr">
         <is>
-          <t>10. rechte Einschaltseite</t>
+          <t>8. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1510" t="inlineStr">
@@ -68838,12 +68890,12 @@
       </c>
       <c r="D1511" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1511" t="inlineStr">
         <is>
-          <t>EH/DH 1 Seite</t>
+          <t>9. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1511" t="inlineStr">
@@ -68876,12 +68928,12 @@
       </c>
       <c r="D1512" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1512" t="inlineStr">
         <is>
-          <t>EH/DH 2 Seiten</t>
+          <t>10. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1512" t="inlineStr">
@@ -68919,7 +68971,7 @@
       </c>
       <c r="E1513" t="inlineStr">
         <is>
-          <t>EH/DH 4 Seiten</t>
+          <t>EH/DH 1 Seite</t>
         </is>
       </c>
       <c r="H1513" t="inlineStr">
@@ -68957,7 +69009,7 @@
       </c>
       <c r="E1514" t="inlineStr">
         <is>
-          <t>V-Koop MWO/Wefra</t>
+          <t>EH/DH 2 Seiten</t>
         </is>
       </c>
       <c r="H1514" t="inlineStr">
@@ -68990,12 +69042,12 @@
       </c>
       <c r="D1515" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1515" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (pro 1.000)</t>
+          <t>EH/DH 4 Seiten</t>
         </is>
       </c>
       <c r="H1515" t="inlineStr">
@@ -69028,12 +69080,12 @@
       </c>
       <c r="D1516" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1516" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (gesamt)</t>
+          <t>V-Koop MWO/Wefra</t>
         </is>
       </c>
       <c r="H1516" t="inlineStr">
@@ -69071,7 +69123,7 @@
       </c>
       <c r="E1517" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 50g (gesamt)</t>
+          <t>Werbebeilage bis 25g (pro 1.000)</t>
         </is>
       </c>
       <c r="H1517" t="inlineStr">
@@ -69104,12 +69156,12 @@
       </c>
       <c r="D1518" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1518" t="inlineStr">
         <is>
-          <t>Titelseitenklappe</t>
+          <t>Werbebeilage bis 25g (gesamt)</t>
         </is>
       </c>
       <c r="H1518" t="inlineStr">
@@ -69142,12 +69194,12 @@
       </c>
       <c r="D1519" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1519" t="inlineStr">
         <is>
-          <t>French Cover</t>
+          <t>Werbebeilage bis 50g (gesamt)</t>
         </is>
       </c>
       <c r="H1519" t="inlineStr">
@@ -69185,7 +69237,7 @@
       </c>
       <c r="E1520" t="inlineStr">
         <is>
-          <t>ausklappbare 2. US</t>
+          <t>Titelseitenklappe</t>
         </is>
       </c>
       <c r="H1520" t="inlineStr">
@@ -69223,7 +69275,7 @@
       </c>
       <c r="E1521" t="inlineStr">
         <is>
-          <t>1/2 ausklappbare 2. US</t>
+          <t>French Cover</t>
         </is>
       </c>
       <c r="H1521" t="inlineStr">
@@ -69261,7 +69313,7 @@
       </c>
       <c r="E1522" t="inlineStr">
         <is>
-          <t>Banderole (umlaufend)</t>
+          <t>ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1522" t="inlineStr">
@@ -69299,7 +69351,7 @@
       </c>
       <c r="E1523" t="inlineStr">
         <is>
-          <t>Sogbanderole</t>
+          <t>1/2 ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1523" t="inlineStr">
@@ -69337,7 +69389,7 @@
       </c>
       <c r="E1524" t="inlineStr">
         <is>
-          <t>Zangenbanderole</t>
+          <t>Banderole (umlaufend)</t>
         </is>
       </c>
       <c r="H1524" t="inlineStr">
@@ -69375,7 +69427,7 @@
       </c>
       <c r="E1525" t="inlineStr">
         <is>
-          <t>Pfeilbanderole</t>
+          <t>Sogbanderole</t>
         </is>
       </c>
       <c r="H1525" t="inlineStr">
@@ -69413,7 +69465,7 @@
       </c>
       <c r="E1526" t="inlineStr">
         <is>
-          <t>Oversize-Beilage</t>
+          <t>Zangenbanderole</t>
         </is>
       </c>
       <c r="H1526" t="inlineStr">
@@ -69451,7 +69503,7 @@
       </c>
       <c r="E1527" t="inlineStr">
         <is>
-          <t>Lesezeichen (unbestimmte Stelle)</t>
+          <t>Pfeilbanderole</t>
         </is>
       </c>
       <c r="H1527" t="inlineStr">
@@ -69489,7 +69541,7 @@
       </c>
       <c r="E1528" t="inlineStr">
         <is>
-          <t>Lesezeichen (bestimmte Stelle)</t>
+          <t>Oversize-Beilage</t>
         </is>
       </c>
       <c r="H1528" t="inlineStr">
@@ -69522,12 +69574,12 @@
       </c>
       <c r="D1529" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1529" t="inlineStr">
         <is>
-          <t>Klappohr-Einhefter</t>
+          <t>Lesezeichen (unbestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1529" t="inlineStr">
@@ -69560,12 +69612,12 @@
       </c>
       <c r="D1530" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1530" t="inlineStr">
         <is>
-          <t>gestanzter Einhefter</t>
+          <t>Lesezeichen (bestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1530" t="inlineStr">
@@ -69603,7 +69655,7 @@
       </c>
       <c r="E1531" t="inlineStr">
         <is>
-          <t>perforierter Einhefter</t>
+          <t>Klappohr-Einhefter</t>
         </is>
       </c>
       <c r="H1531" t="inlineStr">
@@ -69641,7 +69693,7 @@
       </c>
       <c r="E1532" t="inlineStr">
         <is>
-          <t>Einhefter mit Klappe</t>
+          <t>gestanzter Einhefter</t>
         </is>
       </c>
       <c r="H1532" t="inlineStr">
@@ -69679,7 +69731,7 @@
       </c>
       <c r="E1533" t="inlineStr">
         <is>
-          <t>Flip-Einhefter</t>
+          <t>perforierter Einhefter</t>
         </is>
       </c>
       <c r="H1533" t="inlineStr">
@@ -69704,20 +69756,20 @@
       </c>
       <c r="B1534" t="inlineStr">
         <is>
-          <t>best practice onkologie</t>
+          <t>Die Onkologie</t>
         </is>
       </c>
       <c r="C1534" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="D1534" t="inlineStr">
         <is>
-          <t>Normalplatzierungen (4c inkl.)</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1534" t="inlineStr">
         <is>
-          <t>1/1 Seite 4c</t>
+          <t>Einhefter mit Klappe</t>
         </is>
       </c>
       <c r="H1534" t="inlineStr">
@@ -69742,20 +69794,20 @@
       </c>
       <c r="B1535" t="inlineStr">
         <is>
-          <t>best practice onkologie</t>
+          <t>Die Onkologie</t>
         </is>
       </c>
       <c r="C1535" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="D1535" t="inlineStr">
         <is>
-          <t>Normalplatzierungen (4c inkl.)</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1535" t="inlineStr">
         <is>
-          <t>1/2 Seite 4c</t>
+          <t>Flip-Einhefter</t>
         </is>
       </c>
       <c r="H1535" t="inlineStr">
@@ -69793,7 +69845,7 @@
       </c>
       <c r="E1536" t="inlineStr">
         <is>
-          <t>1/3 Seite 4c</t>
+          <t>1/1 Seite 4c</t>
         </is>
       </c>
       <c r="H1536" t="inlineStr">
@@ -69831,7 +69883,7 @@
       </c>
       <c r="E1537" t="inlineStr">
         <is>
-          <t>1/4 Seite 4c</t>
+          <t>1/2 Seite 4c</t>
         </is>
       </c>
       <c r="H1537" t="inlineStr">
@@ -69869,7 +69921,7 @@
       </c>
       <c r="E1538" t="inlineStr">
         <is>
-          <t>2/1 Doppelseite</t>
+          <t>1/3 Seite 4c</t>
         </is>
       </c>
       <c r="H1538" t="inlineStr">
@@ -69907,7 +69959,7 @@
       </c>
       <c r="E1539" t="inlineStr">
         <is>
-          <t>Advertorial (1/1 Seite 4c)</t>
+          <t>1/4 Seite 4c</t>
         </is>
       </c>
       <c r="H1539" t="inlineStr">
@@ -69940,12 +69992,12 @@
       </c>
       <c r="D1540" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen (4c inkl.)</t>
+          <t>Normalplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1540" t="inlineStr">
         <is>
-          <t>4. Umschlagseite</t>
+          <t>2/1 Doppelseite</t>
         </is>
       </c>
       <c r="H1540" t="inlineStr">
@@ -69978,12 +70030,12 @@
       </c>
       <c r="D1541" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen (4c inkl.)</t>
+          <t>Normalplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1541" t="inlineStr">
         <is>
-          <t>2. Umschlagseite</t>
+          <t>Advertorial (1/1 Seite 4c)</t>
         </is>
       </c>
       <c r="H1541" t="inlineStr">
@@ -70021,7 +70073,7 @@
       </c>
       <c r="E1542" t="inlineStr">
         <is>
-          <t>Seite ggü. red. Info / Inhalt</t>
+          <t>4. Umschlagseite</t>
         </is>
       </c>
       <c r="H1542" t="inlineStr">
@@ -70059,7 +70111,7 @@
       </c>
       <c r="E1543" t="inlineStr">
         <is>
-          <t>Seite ggü. Hrsg.</t>
+          <t>2. Umschlagseite</t>
         </is>
       </c>
       <c r="H1543" t="inlineStr">
@@ -70097,7 +70149,7 @@
       </c>
       <c r="E1544" t="inlineStr">
         <is>
-          <t>Seite ggü. Editorial</t>
+          <t>Seite ggü. red. Info / Inhalt</t>
         </is>
       </c>
       <c r="H1544" t="inlineStr">
@@ -70135,7 +70187,7 @@
       </c>
       <c r="E1545" t="inlineStr">
         <is>
-          <t>Seite ggü. Textanfang</t>
+          <t>Seite ggü. Hrsg.</t>
         </is>
       </c>
       <c r="H1545" t="inlineStr">
@@ -70173,7 +70225,7 @@
       </c>
       <c r="E1546" t="inlineStr">
         <is>
-          <t>1/1 Seite 4c Festplatzierung</t>
+          <t>Seite ggü. Editorial</t>
         </is>
       </c>
       <c r="H1546" t="inlineStr">
@@ -70211,7 +70263,7 @@
       </c>
       <c r="E1547" t="inlineStr">
         <is>
-          <t>1. rechte Einschaltseite</t>
+          <t>Seite ggü. Textanfang</t>
         </is>
       </c>
       <c r="H1547" t="inlineStr">
@@ -70249,7 +70301,7 @@
       </c>
       <c r="E1548" t="inlineStr">
         <is>
-          <t>2. rechte Einschaltseite</t>
+          <t>1/1 Seite 4c Festplatzierung</t>
         </is>
       </c>
       <c r="H1548" t="inlineStr">
@@ -70287,7 +70339,7 @@
       </c>
       <c r="E1549" t="inlineStr">
         <is>
-          <t>3. rechte Einschaltseite</t>
+          <t>1. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1549" t="inlineStr">
@@ -70325,7 +70377,7 @@
       </c>
       <c r="E1550" t="inlineStr">
         <is>
-          <t>4. rechte Einschaltseite</t>
+          <t>2. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1550" t="inlineStr">
@@ -70363,7 +70415,7 @@
       </c>
       <c r="E1551" t="inlineStr">
         <is>
-          <t>5. rechte Einschaltseite</t>
+          <t>3. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1551" t="inlineStr">
@@ -70401,7 +70453,7 @@
       </c>
       <c r="E1552" t="inlineStr">
         <is>
-          <t>6. rechte Einschaltseite</t>
+          <t>4. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1552" t="inlineStr">
@@ -70439,7 +70491,7 @@
       </c>
       <c r="E1553" t="inlineStr">
         <is>
-          <t>7. rechte Einschaltseite</t>
+          <t>5. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1553" t="inlineStr">
@@ -70477,7 +70529,7 @@
       </c>
       <c r="E1554" t="inlineStr">
         <is>
-          <t>8. rechte Einschaltseite</t>
+          <t>6. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1554" t="inlineStr">
@@ -70515,7 +70567,7 @@
       </c>
       <c r="E1555" t="inlineStr">
         <is>
-          <t>9. rechte Einschaltseite</t>
+          <t>7. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1555" t="inlineStr">
@@ -70553,7 +70605,7 @@
       </c>
       <c r="E1556" t="inlineStr">
         <is>
-          <t>10. rechte Einschaltseite</t>
+          <t>8. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1556" t="inlineStr">
@@ -70586,12 +70638,12 @@
       </c>
       <c r="D1557" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1557" t="inlineStr">
         <is>
-          <t>EH/DH 1 Seite</t>
+          <t>9. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1557" t="inlineStr">
@@ -70624,12 +70676,12 @@
       </c>
       <c r="D1558" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1558" t="inlineStr">
         <is>
-          <t>EH/DH 2 Seiten</t>
+          <t>10. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1558" t="inlineStr">
@@ -70667,7 +70719,7 @@
       </c>
       <c r="E1559" t="inlineStr">
         <is>
-          <t>EH/DH 4 Seiten</t>
+          <t>EH/DH 1 Seite</t>
         </is>
       </c>
       <c r="H1559" t="inlineStr">
@@ -70705,7 +70757,7 @@
       </c>
       <c r="E1560" t="inlineStr">
         <is>
-          <t>V-Koop MWO/Wefra</t>
+          <t>EH/DH 2 Seiten</t>
         </is>
       </c>
       <c r="H1560" t="inlineStr">
@@ -70738,12 +70790,12 @@
       </c>
       <c r="D1561" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1561" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (pro 1.000)</t>
+          <t>EH/DH 4 Seiten</t>
         </is>
       </c>
       <c r="H1561" t="inlineStr">
@@ -70776,12 +70828,12 @@
       </c>
       <c r="D1562" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1562" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (gesamt)</t>
+          <t>V-Koop MWO/Wefra</t>
         </is>
       </c>
       <c r="H1562" t="inlineStr">
@@ -70819,7 +70871,7 @@
       </c>
       <c r="E1563" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 50g (gesamt)</t>
+          <t>Werbebeilage bis 25g (pro 1.000)</t>
         </is>
       </c>
       <c r="H1563" t="inlineStr">
@@ -70852,12 +70904,12 @@
       </c>
       <c r="D1564" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1564" t="inlineStr">
         <is>
-          <t>Titelseitenklappe</t>
+          <t>Werbebeilage bis 25g (gesamt)</t>
         </is>
       </c>
       <c r="H1564" t="inlineStr">
@@ -70890,12 +70942,12 @@
       </c>
       <c r="D1565" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1565" t="inlineStr">
         <is>
-          <t>French Cover</t>
+          <t>Werbebeilage bis 50g (gesamt)</t>
         </is>
       </c>
       <c r="H1565" t="inlineStr">
@@ -70933,7 +70985,7 @@
       </c>
       <c r="E1566" t="inlineStr">
         <is>
-          <t>ausklappbare 2. US</t>
+          <t>Titelseitenklappe</t>
         </is>
       </c>
       <c r="H1566" t="inlineStr">
@@ -70971,7 +71023,7 @@
       </c>
       <c r="E1567" t="inlineStr">
         <is>
-          <t>1/2 ausklappbare 2. US</t>
+          <t>French Cover</t>
         </is>
       </c>
       <c r="H1567" t="inlineStr">
@@ -71009,7 +71061,7 @@
       </c>
       <c r="E1568" t="inlineStr">
         <is>
-          <t>Banderole (umlaufend)</t>
+          <t>ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1568" t="inlineStr">
@@ -71047,7 +71099,7 @@
       </c>
       <c r="E1569" t="inlineStr">
         <is>
-          <t>Sogbanderole</t>
+          <t>1/2 ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1569" t="inlineStr">
@@ -71085,7 +71137,7 @@
       </c>
       <c r="E1570" t="inlineStr">
         <is>
-          <t>Zangenbanderole</t>
+          <t>Banderole (umlaufend)</t>
         </is>
       </c>
       <c r="H1570" t="inlineStr">
@@ -71123,7 +71175,7 @@
       </c>
       <c r="E1571" t="inlineStr">
         <is>
-          <t>Pfeilbanderole</t>
+          <t>Sogbanderole</t>
         </is>
       </c>
       <c r="H1571" t="inlineStr">
@@ -71161,7 +71213,7 @@
       </c>
       <c r="E1572" t="inlineStr">
         <is>
-          <t>Oversize-Beilage</t>
+          <t>Zangenbanderole</t>
         </is>
       </c>
       <c r="H1572" t="inlineStr">
@@ -71199,7 +71251,7 @@
       </c>
       <c r="E1573" t="inlineStr">
         <is>
-          <t>Lesezeichen (unbestimmte Stelle)</t>
+          <t>Pfeilbanderole</t>
         </is>
       </c>
       <c r="H1573" t="inlineStr">
@@ -71237,7 +71289,7 @@
       </c>
       <c r="E1574" t="inlineStr">
         <is>
-          <t>Lesezeichen (bestimmte Stelle)</t>
+          <t>Oversize-Beilage</t>
         </is>
       </c>
       <c r="H1574" t="inlineStr">
@@ -71275,7 +71327,7 @@
       </c>
       <c r="E1575" t="inlineStr">
         <is>
-          <t>Teaser-Anzeige im red. Text</t>
+          <t>Lesezeichen (unbestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1575" t="inlineStr">
@@ -71313,7 +71365,7 @@
       </c>
       <c r="E1576" t="inlineStr">
         <is>
-          <t>Griffecke im red. Text</t>
+          <t>Lesezeichen (bestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1576" t="inlineStr">
@@ -71346,12 +71398,12 @@
       </c>
       <c r="D1577" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1577" t="inlineStr">
         <is>
-          <t>Klappohr-Einhefter</t>
+          <t>Teaser-Anzeige im red. Text</t>
         </is>
       </c>
       <c r="H1577" t="inlineStr">
@@ -71384,12 +71436,12 @@
       </c>
       <c r="D1578" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1578" t="inlineStr">
         <is>
-          <t>gestanzter Einhefter</t>
+          <t>Griffecke im red. Text</t>
         </is>
       </c>
       <c r="H1578" t="inlineStr">
@@ -71427,7 +71479,7 @@
       </c>
       <c r="E1579" t="inlineStr">
         <is>
-          <t>perforierter Einhefter</t>
+          <t>Klappohr-Einhefter</t>
         </is>
       </c>
       <c r="H1579" t="inlineStr">
@@ -71465,7 +71517,7 @@
       </c>
       <c r="E1580" t="inlineStr">
         <is>
-          <t>Einhefter mit Klappe</t>
+          <t>gestanzter Einhefter</t>
         </is>
       </c>
       <c r="H1580" t="inlineStr">
@@ -71503,7 +71555,7 @@
       </c>
       <c r="E1581" t="inlineStr">
         <is>
-          <t>Flip-Einhefter</t>
+          <t>perforierter Einhefter</t>
         </is>
       </c>
       <c r="H1581" t="inlineStr">
@@ -71528,20 +71580,20 @@
       </c>
       <c r="B1582" t="inlineStr">
         <is>
-          <t>FORUM DKG</t>
+          <t>best practice onkologie</t>
         </is>
       </c>
       <c r="C1582" t="n">
-        <v>8700</v>
+        <v>10000</v>
       </c>
       <c r="D1582" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1582" t="inlineStr">
         <is>
-          <t>1/1 Seite 4c</t>
+          <t>Einhefter mit Klappe</t>
         </is>
       </c>
       <c r="H1582" t="inlineStr">
@@ -71566,20 +71618,20 @@
       </c>
       <c r="B1583" t="inlineStr">
         <is>
-          <t>FORUM DKG</t>
+          <t>best practice onkologie</t>
         </is>
       </c>
       <c r="C1583" t="n">
-        <v>8700</v>
+        <v>10000</v>
       </c>
       <c r="D1583" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1583" t="inlineStr">
         <is>
-          <t>1/2 Seite 4c</t>
+          <t>Flip-Einhefter</t>
         </is>
       </c>
       <c r="H1583" t="inlineStr">
@@ -71617,7 +71669,7 @@
       </c>
       <c r="E1584" t="inlineStr">
         <is>
-          <t>1/3 Seite 4c</t>
+          <t>1/1 Seite 4c</t>
         </is>
       </c>
       <c r="H1584" t="inlineStr">
@@ -71655,7 +71707,7 @@
       </c>
       <c r="E1585" t="inlineStr">
         <is>
-          <t>1/4 Seite 4c</t>
+          <t>1/2 Seite 4c</t>
         </is>
       </c>
       <c r="H1585" t="inlineStr">
@@ -71693,7 +71745,7 @@
       </c>
       <c r="E1586" t="inlineStr">
         <is>
-          <t>2/1 Doppelseite</t>
+          <t>1/3 Seite 4c</t>
         </is>
       </c>
       <c r="H1586" t="inlineStr">
@@ -71731,7 +71783,7 @@
       </c>
       <c r="E1587" t="inlineStr">
         <is>
-          <t>Advertorial (1/1 Seite 4c)</t>
+          <t>1/4 Seite 4c</t>
         </is>
       </c>
       <c r="H1587" t="inlineStr">
@@ -71764,12 +71816,12 @@
       </c>
       <c r="D1588" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1588" t="inlineStr">
         <is>
-          <t>4. Umschlagseite</t>
+          <t>2/1 Doppelseite</t>
         </is>
       </c>
       <c r="H1588" t="inlineStr">
@@ -71802,12 +71854,12 @@
       </c>
       <c r="D1589" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1589" t="inlineStr">
         <is>
-          <t>2. Umschlagseite</t>
+          <t>Advertorial (1/1 Seite 4c)</t>
         </is>
       </c>
       <c r="H1589" t="inlineStr">
@@ -71845,7 +71897,7 @@
       </c>
       <c r="E1590" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 1</t>
+          <t>4. Umschlagseite</t>
         </is>
       </c>
       <c r="H1590" t="inlineStr">
@@ -71883,7 +71935,7 @@
       </c>
       <c r="E1591" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 2</t>
+          <t>2. Umschlagseite</t>
         </is>
       </c>
       <c r="H1591" t="inlineStr">
@@ -71921,7 +71973,7 @@
       </c>
       <c r="E1592" t="inlineStr">
         <is>
-          <t>Seite ggü. Editorial 2</t>
+          <t>Seite ggü. Inhalt 1</t>
         </is>
       </c>
       <c r="H1592" t="inlineStr">
@@ -71959,7 +72011,7 @@
       </c>
       <c r="E1593" t="inlineStr">
         <is>
-          <t>Seite ggü. Textanfang</t>
+          <t>Seite ggü. Inhalt 2</t>
         </is>
       </c>
       <c r="H1593" t="inlineStr">
@@ -71997,7 +72049,7 @@
       </c>
       <c r="E1594" t="inlineStr">
         <is>
-          <t>1/1 Seite 4c Festplatzierung</t>
+          <t>Seite ggü. Editorial 2</t>
         </is>
       </c>
       <c r="H1594" t="inlineStr">
@@ -72035,7 +72087,7 @@
       </c>
       <c r="E1595" t="inlineStr">
         <is>
-          <t>1. rechte Einschaltseite</t>
+          <t>Seite ggü. Textanfang</t>
         </is>
       </c>
       <c r="H1595" t="inlineStr">
@@ -72073,7 +72125,7 @@
       </c>
       <c r="E1596" t="inlineStr">
         <is>
-          <t>2. rechte Einschaltseite</t>
+          <t>1/1 Seite 4c Festplatzierung</t>
         </is>
       </c>
       <c r="H1596" t="inlineStr">
@@ -72111,7 +72163,7 @@
       </c>
       <c r="E1597" t="inlineStr">
         <is>
-          <t>3. rechte Einschaltseite</t>
+          <t>1. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1597" t="inlineStr">
@@ -72149,7 +72201,7 @@
       </c>
       <c r="E1598" t="inlineStr">
         <is>
-          <t>4. rechte Einschaltseite</t>
+          <t>2. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1598" t="inlineStr">
@@ -72187,7 +72239,7 @@
       </c>
       <c r="E1599" t="inlineStr">
         <is>
-          <t>5. rechte Einschaltseite</t>
+          <t>3. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1599" t="inlineStr">
@@ -72225,7 +72277,7 @@
       </c>
       <c r="E1600" t="inlineStr">
         <is>
-          <t>6. rechte Einschaltseite</t>
+          <t>4. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1600" t="inlineStr">
@@ -72263,7 +72315,7 @@
       </c>
       <c r="E1601" t="inlineStr">
         <is>
-          <t>7. rechte Einschaltseite</t>
+          <t>5. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1601" t="inlineStr">
@@ -72301,7 +72353,7 @@
       </c>
       <c r="E1602" t="inlineStr">
         <is>
-          <t>8. rechte Einschaltseite</t>
+          <t>6. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1602" t="inlineStr">
@@ -72339,7 +72391,7 @@
       </c>
       <c r="E1603" t="inlineStr">
         <is>
-          <t>9. rechte Einschaltseite</t>
+          <t>7. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1603" t="inlineStr">
@@ -72377,7 +72429,7 @@
       </c>
       <c r="E1604" t="inlineStr">
         <is>
-          <t>10. rechte Einschaltseite</t>
+          <t>8. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1604" t="inlineStr">
@@ -72410,12 +72462,12 @@
       </c>
       <c r="D1605" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1605" t="inlineStr">
         <is>
-          <t>EH/DH 1 Seite</t>
+          <t>9. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1605" t="inlineStr">
@@ -72448,12 +72500,12 @@
       </c>
       <c r="D1606" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1606" t="inlineStr">
         <is>
-          <t>EH/DH 2 Seiten</t>
+          <t>10. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1606" t="inlineStr">
@@ -72491,7 +72543,7 @@
       </c>
       <c r="E1607" t="inlineStr">
         <is>
-          <t>EH/DH 4 Seiten</t>
+          <t>EH/DH 1 Seite</t>
         </is>
       </c>
       <c r="H1607" t="inlineStr">
@@ -72529,7 +72581,7 @@
       </c>
       <c r="E1608" t="inlineStr">
         <is>
-          <t>V-Koop MWO/Wefra</t>
+          <t>EH/DH 2 Seiten</t>
         </is>
       </c>
       <c r="H1608" t="inlineStr">
@@ -72562,12 +72614,12 @@
       </c>
       <c r="D1609" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1609" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (pro 1.000)</t>
+          <t>EH/DH 4 Seiten</t>
         </is>
       </c>
       <c r="H1609" t="inlineStr">
@@ -72600,12 +72652,12 @@
       </c>
       <c r="D1610" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1610" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (gesamt)</t>
+          <t>V-Koop MWO/Wefra</t>
         </is>
       </c>
       <c r="H1610" t="inlineStr">
@@ -72643,7 +72695,7 @@
       </c>
       <c r="E1611" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 50g (gesamt)</t>
+          <t>Werbebeilage bis 25g (pro 1.000)</t>
         </is>
       </c>
       <c r="H1611" t="inlineStr">
@@ -72676,12 +72728,12 @@
       </c>
       <c r="D1612" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1612" t="inlineStr">
         <is>
-          <t>Titelseitenklappe</t>
+          <t>Werbebeilage bis 25g (gesamt)</t>
         </is>
       </c>
       <c r="H1612" t="inlineStr">
@@ -72714,12 +72766,12 @@
       </c>
       <c r="D1613" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1613" t="inlineStr">
         <is>
-          <t>French Cover</t>
+          <t>Werbebeilage bis 50g (gesamt)</t>
         </is>
       </c>
       <c r="H1613" t="inlineStr">
@@ -72757,7 +72809,7 @@
       </c>
       <c r="E1614" t="inlineStr">
         <is>
-          <t>ausklappbare 2. US</t>
+          <t>Titelseitenklappe</t>
         </is>
       </c>
       <c r="H1614" t="inlineStr">
@@ -72795,7 +72847,7 @@
       </c>
       <c r="E1615" t="inlineStr">
         <is>
-          <t>1/2 ausklappbare 2. US</t>
+          <t>French Cover</t>
         </is>
       </c>
       <c r="H1615" t="inlineStr">
@@ -72833,7 +72885,7 @@
       </c>
       <c r="E1616" t="inlineStr">
         <is>
-          <t>Banderole (umlaufend)</t>
+          <t>ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1616" t="inlineStr">
@@ -72871,7 +72923,7 @@
       </c>
       <c r="E1617" t="inlineStr">
         <is>
-          <t>Sogbanderole</t>
+          <t>1/2 ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1617" t="inlineStr">
@@ -72909,7 +72961,7 @@
       </c>
       <c r="E1618" t="inlineStr">
         <is>
-          <t>Zangenbanderole</t>
+          <t>Banderole (umlaufend)</t>
         </is>
       </c>
       <c r="H1618" t="inlineStr">
@@ -72947,7 +72999,7 @@
       </c>
       <c r="E1619" t="inlineStr">
         <is>
-          <t>Pfeilbanderole</t>
+          <t>Sogbanderole</t>
         </is>
       </c>
       <c r="H1619" t="inlineStr">
@@ -72985,7 +73037,7 @@
       </c>
       <c r="E1620" t="inlineStr">
         <is>
-          <t>Oversize-Beilage</t>
+          <t>Zangenbanderole</t>
         </is>
       </c>
       <c r="H1620" t="inlineStr">
@@ -73023,7 +73075,7 @@
       </c>
       <c r="E1621" t="inlineStr">
         <is>
-          <t>Lesezeichen (unbestimmte Stelle)</t>
+          <t>Pfeilbanderole</t>
         </is>
       </c>
       <c r="H1621" t="inlineStr">
@@ -73061,7 +73113,7 @@
       </c>
       <c r="E1622" t="inlineStr">
         <is>
-          <t>Lesezeichen (bestimmte Stelle)</t>
+          <t>Oversize-Beilage</t>
         </is>
       </c>
       <c r="H1622" t="inlineStr">
@@ -73099,7 +73151,7 @@
       </c>
       <c r="E1623" t="inlineStr">
         <is>
-          <t>Teaser-Anzeige im red. Text</t>
+          <t>Lesezeichen (unbestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1623" t="inlineStr">
@@ -73137,7 +73189,7 @@
       </c>
       <c r="E1624" t="inlineStr">
         <is>
-          <t>Griffecke im red. Text</t>
+          <t>Lesezeichen (bestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1624" t="inlineStr">
@@ -73170,12 +73222,12 @@
       </c>
       <c r="D1625" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1625" t="inlineStr">
         <is>
-          <t>Klappohr-Einhefter</t>
+          <t>Teaser-Anzeige im red. Text</t>
         </is>
       </c>
       <c r="H1625" t="inlineStr">
@@ -73208,12 +73260,12 @@
       </c>
       <c r="D1626" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1626" t="inlineStr">
         <is>
-          <t>gestanzter Einhefter</t>
+          <t>Griffecke im red. Text</t>
         </is>
       </c>
       <c r="H1626" t="inlineStr">
@@ -73251,7 +73303,7 @@
       </c>
       <c r="E1627" t="inlineStr">
         <is>
-          <t>Einhefter mit Klappe</t>
+          <t>Klappohr-Einhefter</t>
         </is>
       </c>
       <c r="H1627" t="inlineStr">
@@ -73289,7 +73341,7 @@
       </c>
       <c r="E1628" t="inlineStr">
         <is>
-          <t>Flip-Einhefter</t>
+          <t>gestanzter Einhefter</t>
         </is>
       </c>
       <c r="H1628" t="inlineStr">
@@ -73314,20 +73366,20 @@
       </c>
       <c r="B1629" t="inlineStr">
         <is>
-          <t>Im Fokus Onkologie</t>
+          <t>FORUM DKG</t>
         </is>
       </c>
       <c r="C1629" t="n">
-        <v>8000</v>
+        <v>8700</v>
       </c>
       <c r="D1629" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1629" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
+          <t>Einhefter mit Klappe</t>
         </is>
       </c>
       <c r="H1629" t="inlineStr">
@@ -73352,20 +73404,20 @@
       </c>
       <c r="B1630" t="inlineStr">
         <is>
-          <t>Im Fokus Onkologie</t>
+          <t>FORUM DKG</t>
         </is>
       </c>
       <c r="C1630" t="n">
-        <v>8000</v>
+        <v>8700</v>
       </c>
       <c r="D1630" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1630" t="inlineStr">
         <is>
-          <t>1/2 Seite</t>
+          <t>Flip-Einhefter</t>
         </is>
       </c>
       <c r="H1630" t="inlineStr">
@@ -73403,7 +73455,7 @@
       </c>
       <c r="E1631" t="inlineStr">
         <is>
-          <t>1/3 Seite</t>
+          <t>1/1 Seite</t>
         </is>
       </c>
       <c r="H1631" t="inlineStr">
@@ -73441,7 +73493,7 @@
       </c>
       <c r="E1632" t="inlineStr">
         <is>
-          <t>1/4 Seite</t>
+          <t>1/2 Seite</t>
         </is>
       </c>
       <c r="H1632" t="inlineStr">
@@ -73479,7 +73531,7 @@
       </c>
       <c r="E1633" t="inlineStr">
         <is>
-          <t>2/1 Doppelseite</t>
+          <t>1/3 Seite</t>
         </is>
       </c>
       <c r="H1633" t="inlineStr">
@@ -73517,7 +73569,7 @@
       </c>
       <c r="E1634" t="inlineStr">
         <is>
-          <t>Advertorial (1/1 Seite)</t>
+          <t>1/4 Seite</t>
         </is>
       </c>
       <c r="H1634" t="inlineStr">
@@ -73550,12 +73602,12 @@
       </c>
       <c r="D1635" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1635" t="inlineStr">
         <is>
-          <t>4. Umschlagseite</t>
+          <t>2/1 Doppelseite</t>
         </is>
       </c>
       <c r="H1635" t="inlineStr">
@@ -73588,12 +73640,12 @@
       </c>
       <c r="D1636" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1636" t="inlineStr">
         <is>
-          <t>2. Umschlagseite</t>
+          <t>Advertorial (1/1 Seite)</t>
         </is>
       </c>
       <c r="H1636" t="inlineStr">
@@ -73631,7 +73683,7 @@
       </c>
       <c r="E1637" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 1</t>
+          <t>4. Umschlagseite</t>
         </is>
       </c>
       <c r="H1637" t="inlineStr">
@@ -73669,7 +73721,7 @@
       </c>
       <c r="E1638" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 2</t>
+          <t>2. Umschlagseite</t>
         </is>
       </c>
       <c r="H1638" t="inlineStr">
@@ -73707,7 +73759,7 @@
       </c>
       <c r="E1639" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 3</t>
+          <t>Seite ggü. Inhalt 1</t>
         </is>
       </c>
       <c r="H1639" t="inlineStr">
@@ -73745,7 +73797,7 @@
       </c>
       <c r="E1640" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 4</t>
+          <t>Seite ggü. Inhalt 2</t>
         </is>
       </c>
       <c r="H1640" t="inlineStr">
@@ -73783,7 +73835,7 @@
       </c>
       <c r="E1641" t="inlineStr">
         <is>
-          <t>Seite ggü. Textanfang</t>
+          <t>Seite ggü. Inhalt 3</t>
         </is>
       </c>
       <c r="H1641" t="inlineStr">
@@ -73821,7 +73873,7 @@
       </c>
       <c r="E1642" t="inlineStr">
         <is>
-          <t>1/1 Seite Festplatzierung</t>
+          <t>Seite ggü. Inhalt 4</t>
         </is>
       </c>
       <c r="H1642" t="inlineStr">
@@ -73859,7 +73911,7 @@
       </c>
       <c r="E1643" t="inlineStr">
         <is>
-          <t>1. rechte Einschaltseite</t>
+          <t>Seite ggü. Textanfang</t>
         </is>
       </c>
       <c r="H1643" t="inlineStr">
@@ -73897,7 +73949,7 @@
       </c>
       <c r="E1644" t="inlineStr">
         <is>
-          <t>2. rechte Einschaltseite</t>
+          <t>1/1 Seite Festplatzierung</t>
         </is>
       </c>
       <c r="H1644" t="inlineStr">
@@ -73935,7 +73987,7 @@
       </c>
       <c r="E1645" t="inlineStr">
         <is>
-          <t>3. rechte Einschaltseite</t>
+          <t>1. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1645" t="inlineStr">
@@ -73973,7 +74025,7 @@
       </c>
       <c r="E1646" t="inlineStr">
         <is>
-          <t>4. rechte Einschaltseite</t>
+          <t>2. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1646" t="inlineStr">
@@ -74011,7 +74063,7 @@
       </c>
       <c r="E1647" t="inlineStr">
         <is>
-          <t>5. rechte Einschaltseite</t>
+          <t>3. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1647" t="inlineStr">
@@ -74049,7 +74101,7 @@
       </c>
       <c r="E1648" t="inlineStr">
         <is>
-          <t>6. rechte Einschaltseite</t>
+          <t>4. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1648" t="inlineStr">
@@ -74087,7 +74139,7 @@
       </c>
       <c r="E1649" t="inlineStr">
         <is>
-          <t>7. rechte Einschaltseite</t>
+          <t>5. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1649" t="inlineStr">
@@ -74125,7 +74177,7 @@
       </c>
       <c r="E1650" t="inlineStr">
         <is>
-          <t>8. rechte Einschaltseite</t>
+          <t>6. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1650" t="inlineStr">
@@ -74163,7 +74215,7 @@
       </c>
       <c r="E1651" t="inlineStr">
         <is>
-          <t>9. rechte Einschaltseite</t>
+          <t>7. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1651" t="inlineStr">
@@ -74201,7 +74253,7 @@
       </c>
       <c r="E1652" t="inlineStr">
         <is>
-          <t>10. rechte Einschaltseite</t>
+          <t>8. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1652" t="inlineStr">
@@ -74234,12 +74286,12 @@
       </c>
       <c r="D1653" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1653" t="inlineStr">
         <is>
-          <t>EH/DH 1 Seite</t>
+          <t>9. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1653" t="inlineStr">
@@ -74272,12 +74324,12 @@
       </c>
       <c r="D1654" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1654" t="inlineStr">
         <is>
-          <t>EH/DH 2 Seiten</t>
+          <t>10. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1654" t="inlineStr">
@@ -74315,7 +74367,7 @@
       </c>
       <c r="E1655" t="inlineStr">
         <is>
-          <t>EH/DH 4 Seiten</t>
+          <t>EH/DH 1 Seite</t>
         </is>
       </c>
       <c r="H1655" t="inlineStr">
@@ -74353,7 +74405,7 @@
       </c>
       <c r="E1656" t="inlineStr">
         <is>
-          <t>V-Koop MWO/Wefra</t>
+          <t>EH/DH 2 Seiten</t>
         </is>
       </c>
       <c r="H1656" t="inlineStr">
@@ -74386,12 +74438,12 @@
       </c>
       <c r="D1657" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1657" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (pro 1.000)</t>
+          <t>EH/DH 4 Seiten</t>
         </is>
       </c>
       <c r="H1657" t="inlineStr">
@@ -74424,12 +74476,12 @@
       </c>
       <c r="D1658" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1658" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (gesamt)</t>
+          <t>V-Koop MWO/Wefra</t>
         </is>
       </c>
       <c r="H1658" t="inlineStr">
@@ -74467,7 +74519,7 @@
       </c>
       <c r="E1659" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 50g (gesamt)</t>
+          <t>Werbebeilage bis 25g (pro 1.000)</t>
         </is>
       </c>
       <c r="H1659" t="inlineStr">
@@ -74500,12 +74552,12 @@
       </c>
       <c r="D1660" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1660" t="inlineStr">
         <is>
-          <t>Titelseitenklappe</t>
+          <t>Werbebeilage bis 25g (gesamt)</t>
         </is>
       </c>
       <c r="H1660" t="inlineStr">
@@ -74538,12 +74590,12 @@
       </c>
       <c r="D1661" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1661" t="inlineStr">
         <is>
-          <t>French Cover</t>
+          <t>Werbebeilage bis 50g (gesamt)</t>
         </is>
       </c>
       <c r="H1661" t="inlineStr">
@@ -74581,7 +74633,7 @@
       </c>
       <c r="E1662" t="inlineStr">
         <is>
-          <t>ausklappbare 2. US</t>
+          <t>Titelseitenklappe</t>
         </is>
       </c>
       <c r="H1662" t="inlineStr">
@@ -74619,7 +74671,7 @@
       </c>
       <c r="E1663" t="inlineStr">
         <is>
-          <t>1/2 ausklappbare 2. US</t>
+          <t>French Cover</t>
         </is>
       </c>
       <c r="H1663" t="inlineStr">
@@ -74657,7 +74709,7 @@
       </c>
       <c r="E1664" t="inlineStr">
         <is>
-          <t>Banderole (umlaufend)</t>
+          <t>ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1664" t="inlineStr">
@@ -74695,7 +74747,7 @@
       </c>
       <c r="E1665" t="inlineStr">
         <is>
-          <t>Sogbanderole</t>
+          <t>1/2 ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1665" t="inlineStr">
@@ -74733,7 +74785,7 @@
       </c>
       <c r="E1666" t="inlineStr">
         <is>
-          <t>Zangenbanderole</t>
+          <t>Banderole (umlaufend)</t>
         </is>
       </c>
       <c r="H1666" t="inlineStr">
@@ -74771,7 +74823,7 @@
       </c>
       <c r="E1667" t="inlineStr">
         <is>
-          <t>Pfeilbanderole</t>
+          <t>Sogbanderole</t>
         </is>
       </c>
       <c r="H1667" t="inlineStr">
@@ -74809,7 +74861,7 @@
       </c>
       <c r="E1668" t="inlineStr">
         <is>
-          <t>Oversize-Beilage</t>
+          <t>Zangenbanderole</t>
         </is>
       </c>
       <c r="H1668" t="inlineStr">
@@ -74847,7 +74899,7 @@
       </c>
       <c r="E1669" t="inlineStr">
         <is>
-          <t>Lesezeichen (unbestimmte Stelle)</t>
+          <t>Pfeilbanderole</t>
         </is>
       </c>
       <c r="H1669" t="inlineStr">
@@ -74885,7 +74937,7 @@
       </c>
       <c r="E1670" t="inlineStr">
         <is>
-          <t>Lesezeichen (bestimmte Stelle)</t>
+          <t>Oversize-Beilage</t>
         </is>
       </c>
       <c r="H1670" t="inlineStr">
@@ -74923,7 +74975,7 @@
       </c>
       <c r="E1671" t="inlineStr">
         <is>
-          <t>Teaser-Anzeige auf Inhalt-Seite</t>
+          <t>Lesezeichen (unbestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1671" t="inlineStr">
@@ -74961,7 +75013,7 @@
       </c>
       <c r="E1672" t="inlineStr">
         <is>
-          <t>Teaser-Anzeige im red. Text</t>
+          <t>Lesezeichen (bestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1672" t="inlineStr">
@@ -74999,7 +75051,7 @@
       </c>
       <c r="E1673" t="inlineStr">
         <is>
-          <t>Griffecke auf Inhalt-Seite</t>
+          <t>Teaser-Anzeige auf Inhalt-Seite</t>
         </is>
       </c>
       <c r="H1673" t="inlineStr">
@@ -75037,7 +75089,7 @@
       </c>
       <c r="E1674" t="inlineStr">
         <is>
-          <t>Griffecke im red. Text</t>
+          <t>Teaser-Anzeige im red. Text</t>
         </is>
       </c>
       <c r="H1674" t="inlineStr">
@@ -75070,12 +75122,12 @@
       </c>
       <c r="D1675" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1675" t="inlineStr">
         <is>
-          <t>Klappohr-Einhefter</t>
+          <t>Griffecke auf Inhalt-Seite</t>
         </is>
       </c>
       <c r="H1675" t="inlineStr">
@@ -75108,12 +75160,12 @@
       </c>
       <c r="D1676" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1676" t="inlineStr">
         <is>
-          <t>gestanzter Einhefter</t>
+          <t>Griffecke im red. Text</t>
         </is>
       </c>
       <c r="H1676" t="inlineStr">
@@ -75151,7 +75203,7 @@
       </c>
       <c r="E1677" t="inlineStr">
         <is>
-          <t>Einhefter mit Klappe</t>
+          <t>Klappohr-Einhefter</t>
         </is>
       </c>
       <c r="H1677" t="inlineStr">
@@ -75189,7 +75241,7 @@
       </c>
       <c r="E1678" t="inlineStr">
         <is>
-          <t>Flip-Einhefter</t>
+          <t>gestanzter Einhefter</t>
         </is>
       </c>
       <c r="H1678" t="inlineStr">
@@ -75214,20 +75266,20 @@
       </c>
       <c r="B1679" t="inlineStr">
         <is>
-          <t>InFo Hämatologie + Onkologie</t>
+          <t>Im Fokus Onkologie</t>
         </is>
       </c>
       <c r="C1679" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="D1679" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1679" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
+          <t>Einhefter mit Klappe</t>
         </is>
       </c>
       <c r="H1679" t="inlineStr">
@@ -75252,20 +75304,20 @@
       </c>
       <c r="B1680" t="inlineStr">
         <is>
-          <t>InFo Hämatologie + Onkologie</t>
+          <t>Im Fokus Onkologie</t>
         </is>
       </c>
       <c r="C1680" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="D1680" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1680" t="inlineStr">
         <is>
-          <t>1/2 Seite</t>
+          <t>Flip-Einhefter</t>
         </is>
       </c>
       <c r="H1680" t="inlineStr">
@@ -75303,7 +75355,7 @@
       </c>
       <c r="E1681" t="inlineStr">
         <is>
-          <t>1/3 Seite</t>
+          <t>1/1 Seite</t>
         </is>
       </c>
       <c r="H1681" t="inlineStr">
@@ -75341,7 +75393,7 @@
       </c>
       <c r="E1682" t="inlineStr">
         <is>
-          <t>1/4 Seite</t>
+          <t>1/2 Seite</t>
         </is>
       </c>
       <c r="H1682" t="inlineStr">
@@ -75379,7 +75431,7 @@
       </c>
       <c r="E1683" t="inlineStr">
         <is>
-          <t>2/1 Doppelseite</t>
+          <t>1/3 Seite</t>
         </is>
       </c>
       <c r="H1683" t="inlineStr">
@@ -75417,7 +75469,7 @@
       </c>
       <c r="E1684" t="inlineStr">
         <is>
-          <t>Advertorial (1/1 Seite)</t>
+          <t>1/4 Seite</t>
         </is>
       </c>
       <c r="H1684" t="inlineStr">
@@ -75450,12 +75502,12 @@
       </c>
       <c r="D1685" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1685" t="inlineStr">
         <is>
-          <t>4. Umschlagseite</t>
+          <t>2/1 Doppelseite</t>
         </is>
       </c>
       <c r="H1685" t="inlineStr">
@@ -75488,12 +75540,12 @@
       </c>
       <c r="D1686" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1686" t="inlineStr">
         <is>
-          <t>2. Umschlagseite</t>
+          <t>Advertorial (1/1 Seite)</t>
         </is>
       </c>
       <c r="H1686" t="inlineStr">
@@ -75531,7 +75583,7 @@
       </c>
       <c r="E1687" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 1</t>
+          <t>4. Umschlagseite</t>
         </is>
       </c>
       <c r="H1687" t="inlineStr">
@@ -75569,7 +75621,7 @@
       </c>
       <c r="E1688" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 2</t>
+          <t>2. Umschlagseite</t>
         </is>
       </c>
       <c r="H1688" t="inlineStr">
@@ -75607,7 +75659,7 @@
       </c>
       <c r="E1689" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 3</t>
+          <t>Seite ggü. Inhalt 1</t>
         </is>
       </c>
       <c r="H1689" t="inlineStr">
@@ -75645,7 +75697,7 @@
       </c>
       <c r="E1690" t="inlineStr">
         <is>
-          <t>Seite ggü. Textanfang</t>
+          <t>Seite ggü. Inhalt 2</t>
         </is>
       </c>
       <c r="H1690" t="inlineStr">
@@ -75683,7 +75735,7 @@
       </c>
       <c r="E1691" t="inlineStr">
         <is>
-          <t>1/1 Seite Festplatzierung</t>
+          <t>Seite ggü. Inhalt 3</t>
         </is>
       </c>
       <c r="H1691" t="inlineStr">
@@ -75721,7 +75773,7 @@
       </c>
       <c r="E1692" t="inlineStr">
         <is>
-          <t>1. rechte Einschaltseite</t>
+          <t>Seite ggü. Textanfang</t>
         </is>
       </c>
       <c r="H1692" t="inlineStr">
@@ -75759,7 +75811,7 @@
       </c>
       <c r="E1693" t="inlineStr">
         <is>
-          <t>2. rechte Einschaltseite</t>
+          <t>1/1 Seite Festplatzierung</t>
         </is>
       </c>
       <c r="H1693" t="inlineStr">
@@ -75797,7 +75849,7 @@
       </c>
       <c r="E1694" t="inlineStr">
         <is>
-          <t>3. rechte Einschaltseite</t>
+          <t>1. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1694" t="inlineStr">
@@ -75835,7 +75887,7 @@
       </c>
       <c r="E1695" t="inlineStr">
         <is>
-          <t>4. rechte Einschaltseite</t>
+          <t>2. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1695" t="inlineStr">
@@ -75873,7 +75925,7 @@
       </c>
       <c r="E1696" t="inlineStr">
         <is>
-          <t>5. rechte Einschaltseite</t>
+          <t>3. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1696" t="inlineStr">
@@ -75911,7 +75963,7 @@
       </c>
       <c r="E1697" t="inlineStr">
         <is>
-          <t>6. rechte Einschaltseite</t>
+          <t>4. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1697" t="inlineStr">
@@ -75949,7 +76001,7 @@
       </c>
       <c r="E1698" t="inlineStr">
         <is>
-          <t>7. rechte Einschaltseite</t>
+          <t>5. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1698" t="inlineStr">
@@ -75987,7 +76039,7 @@
       </c>
       <c r="E1699" t="inlineStr">
         <is>
-          <t>8. rechte Einschaltseite</t>
+          <t>6. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1699" t="inlineStr">
@@ -76025,7 +76077,7 @@
       </c>
       <c r="E1700" t="inlineStr">
         <is>
-          <t>9. rechte Einschaltseite</t>
+          <t>7. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1700" t="inlineStr">
@@ -76063,7 +76115,7 @@
       </c>
       <c r="E1701" t="inlineStr">
         <is>
-          <t>10. rechte Einschaltseite</t>
+          <t>8. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1701" t="inlineStr">
@@ -76096,12 +76148,12 @@
       </c>
       <c r="D1702" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1702" t="inlineStr">
         <is>
-          <t>EH/DH 1 Seite</t>
+          <t>9. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1702" t="inlineStr">
@@ -76134,12 +76186,12 @@
       </c>
       <c r="D1703" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1703" t="inlineStr">
         <is>
-          <t>EH/DH 2 Seiten</t>
+          <t>10. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1703" t="inlineStr">
@@ -76177,7 +76229,7 @@
       </c>
       <c r="E1704" t="inlineStr">
         <is>
-          <t>EH/DH 4 Seiten</t>
+          <t>EH/DH 1 Seite</t>
         </is>
       </c>
       <c r="H1704" t="inlineStr">
@@ -76210,12 +76262,12 @@
       </c>
       <c r="D1705" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1705" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (pro 1.000)</t>
+          <t>EH/DH 2 Seiten</t>
         </is>
       </c>
       <c r="H1705" t="inlineStr">
@@ -76248,12 +76300,12 @@
       </c>
       <c r="D1706" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1706" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (gesamt)</t>
+          <t>EH/DH 4 Seiten</t>
         </is>
       </c>
       <c r="H1706" t="inlineStr">
@@ -76291,7 +76343,7 @@
       </c>
       <c r="E1707" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 50g (gesamt)</t>
+          <t>Werbebeilage bis 25g (pro 1.000)</t>
         </is>
       </c>
       <c r="H1707" t="inlineStr">
@@ -76324,12 +76376,12 @@
       </c>
       <c r="D1708" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1708" t="inlineStr">
         <is>
-          <t>Titelseitenklappe</t>
+          <t>Werbebeilage bis 25g (gesamt)</t>
         </is>
       </c>
       <c r="H1708" t="inlineStr">
@@ -76362,12 +76414,12 @@
       </c>
       <c r="D1709" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1709" t="inlineStr">
         <is>
-          <t>French Cover</t>
+          <t>Werbebeilage bis 50g (gesamt)</t>
         </is>
       </c>
       <c r="H1709" t="inlineStr">
@@ -76405,7 +76457,7 @@
       </c>
       <c r="E1710" t="inlineStr">
         <is>
-          <t>ausklappbare 2. US</t>
+          <t>Titelseitenklappe</t>
         </is>
       </c>
       <c r="H1710" t="inlineStr">
@@ -76443,7 +76495,7 @@
       </c>
       <c r="E1711" t="inlineStr">
         <is>
-          <t>1/2 ausklappbare 2. US</t>
+          <t>French Cover</t>
         </is>
       </c>
       <c r="H1711" t="inlineStr">
@@ -76481,7 +76533,7 @@
       </c>
       <c r="E1712" t="inlineStr">
         <is>
-          <t>Banderole (umlaufend)</t>
+          <t>ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1712" t="inlineStr">
@@ -76519,7 +76571,7 @@
       </c>
       <c r="E1713" t="inlineStr">
         <is>
-          <t>Sogbanderole</t>
+          <t>1/2 ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1713" t="inlineStr">
@@ -76557,7 +76609,7 @@
       </c>
       <c r="E1714" t="inlineStr">
         <is>
-          <t>Zangenbanderole</t>
+          <t>Banderole (umlaufend)</t>
         </is>
       </c>
       <c r="H1714" t="inlineStr">
@@ -76595,7 +76647,7 @@
       </c>
       <c r="E1715" t="inlineStr">
         <is>
-          <t>Pfeilbanderole</t>
+          <t>Sogbanderole</t>
         </is>
       </c>
       <c r="H1715" t="inlineStr">
@@ -76633,7 +76685,7 @@
       </c>
       <c r="E1716" t="inlineStr">
         <is>
-          <t>Oversize-Beilage</t>
+          <t>Zangenbanderole</t>
         </is>
       </c>
       <c r="H1716" t="inlineStr">
@@ -76671,7 +76723,7 @@
       </c>
       <c r="E1717" t="inlineStr">
         <is>
-          <t>Lesezeichen (unbestimmte Stelle)</t>
+          <t>Pfeilbanderole</t>
         </is>
       </c>
       <c r="H1717" t="inlineStr">
@@ -76709,7 +76761,7 @@
       </c>
       <c r="E1718" t="inlineStr">
         <is>
-          <t>Lesezeichen (bestimmte Stelle)</t>
+          <t>Oversize-Beilage</t>
         </is>
       </c>
       <c r="H1718" t="inlineStr">
@@ -76747,7 +76799,7 @@
       </c>
       <c r="E1719" t="inlineStr">
         <is>
-          <t>Teaser-Anzeige auf Inhalt-Seite</t>
+          <t>Lesezeichen (unbestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1719" t="inlineStr">
@@ -76785,7 +76837,7 @@
       </c>
       <c r="E1720" t="inlineStr">
         <is>
-          <t>Teaser-Anzeige im red. Text</t>
+          <t>Lesezeichen (bestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1720" t="inlineStr">
@@ -76823,7 +76875,7 @@
       </c>
       <c r="E1721" t="inlineStr">
         <is>
-          <t>Griffecke auf Inhalt-Seite</t>
+          <t>Teaser-Anzeige auf Inhalt-Seite</t>
         </is>
       </c>
       <c r="H1721" t="inlineStr">
@@ -76861,7 +76913,7 @@
       </c>
       <c r="E1722" t="inlineStr">
         <is>
-          <t>Griffecke im red. Text</t>
+          <t>Teaser-Anzeige im red. Text</t>
         </is>
       </c>
       <c r="H1722" t="inlineStr">
@@ -76894,12 +76946,12 @@
       </c>
       <c r="D1723" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1723" t="inlineStr">
         <is>
-          <t>Klappohr-Einhefter</t>
+          <t>Griffecke auf Inhalt-Seite</t>
         </is>
       </c>
       <c r="H1723" t="inlineStr">
@@ -76932,12 +76984,12 @@
       </c>
       <c r="D1724" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1724" t="inlineStr">
         <is>
-          <t>gestanzter Einhefter</t>
+          <t>Griffecke im red. Text</t>
         </is>
       </c>
       <c r="H1724" t="inlineStr">
@@ -76975,7 +77027,7 @@
       </c>
       <c r="E1725" t="inlineStr">
         <is>
-          <t>Einhefter mit Klappe</t>
+          <t>Klappohr-Einhefter</t>
         </is>
       </c>
       <c r="H1725" t="inlineStr">
@@ -77013,7 +77065,7 @@
       </c>
       <c r="E1726" t="inlineStr">
         <is>
-          <t>Flip-Einhefter</t>
+          <t>gestanzter Einhefter</t>
         </is>
       </c>
       <c r="H1726" t="inlineStr">
@@ -77038,20 +77090,20 @@
       </c>
       <c r="B1727" t="inlineStr">
         <is>
-          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+          <t>InFo Hämatologie + Onkologie</t>
         </is>
       </c>
       <c r="C1727" t="n">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="D1727" t="inlineStr">
         <is>
-          <t>Anzeigenformate</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1727" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
+          <t>Einhefter mit Klappe</t>
         </is>
       </c>
       <c r="H1727" t="inlineStr">
@@ -77076,20 +77128,20 @@
       </c>
       <c r="B1728" t="inlineStr">
         <is>
-          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+          <t>InFo Hämatologie + Onkologie</t>
         </is>
       </c>
       <c r="C1728" t="n">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="D1728" t="inlineStr">
         <is>
-          <t>Anzeigenformate</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1728" t="inlineStr">
         <is>
-          <t>A4 Seite hoch</t>
+          <t>Flip-Einhefter</t>
         </is>
       </c>
       <c r="H1728" t="inlineStr">
@@ -77127,7 +77179,7 @@
       </c>
       <c r="E1729" t="inlineStr">
         <is>
-          <t>A5 Seite hoch</t>
+          <t>1/1 Seite</t>
         </is>
       </c>
       <c r="H1729" t="inlineStr">
@@ -77165,7 +77217,7 @@
       </c>
       <c r="E1730" t="inlineStr">
         <is>
-          <t>3/4 Seite quer</t>
+          <t>A4 Seite hoch</t>
         </is>
       </c>
       <c r="H1730" t="inlineStr">
@@ -77203,7 +77255,7 @@
       </c>
       <c r="E1731" t="inlineStr">
         <is>
-          <t>1/2 Seite quer</t>
+          <t>A5 Seite hoch</t>
         </is>
       </c>
       <c r="H1731" t="inlineStr">
@@ -77241,7 +77293,7 @@
       </c>
       <c r="E1732" t="inlineStr">
         <is>
-          <t>1/3 Seite quer</t>
+          <t>3/4 Seite quer</t>
         </is>
       </c>
       <c r="H1732" t="inlineStr">
@@ -77279,7 +77331,7 @@
       </c>
       <c r="E1733" t="inlineStr">
         <is>
-          <t>1/4 Seite quer</t>
+          <t>1/2 Seite quer</t>
         </is>
       </c>
       <c r="H1733" t="inlineStr">
@@ -77317,7 +77369,7 @@
       </c>
       <c r="E1734" t="inlineStr">
         <is>
-          <t>Advertorial (A4 hoch)</t>
+          <t>1/3 Seite quer</t>
         </is>
       </c>
       <c r="H1734" t="inlineStr">
@@ -77350,12 +77402,12 @@
       </c>
       <c r="D1735" t="inlineStr">
         <is>
-          <t>Sonder- und Festplatzierungen</t>
+          <t>Anzeigenformate</t>
         </is>
       </c>
       <c r="E1735" t="inlineStr">
         <is>
-          <t>Titelseitenfuß</t>
+          <t>1/4 Seite quer</t>
         </is>
       </c>
       <c r="H1735" t="inlineStr">
@@ -77388,12 +77440,12 @@
       </c>
       <c r="D1736" t="inlineStr">
         <is>
-          <t>Sonder- und Festplatzierungen</t>
+          <t>Anzeigenformate</t>
         </is>
       </c>
       <c r="E1736" t="inlineStr">
         <is>
-          <t>Insel</t>
+          <t>Advertorial (A4 hoch)</t>
         </is>
       </c>
       <c r="H1736" t="inlineStr">
@@ -77431,7 +77483,7 @@
       </c>
       <c r="E1737" t="inlineStr">
         <is>
-          <t>Insel maxi</t>
+          <t>Titelseitenfuß</t>
         </is>
       </c>
       <c r="H1737" t="inlineStr">
@@ -77469,7 +77521,7 @@
       </c>
       <c r="E1738" t="inlineStr">
         <is>
-          <t>Tunnel klein</t>
+          <t>Insel</t>
         </is>
       </c>
       <c r="H1738" t="inlineStr">
@@ -77507,7 +77559,7 @@
       </c>
       <c r="E1739" t="inlineStr">
         <is>
-          <t>Tunnel groß</t>
+          <t>Insel maxi</t>
         </is>
       </c>
       <c r="H1739" t="inlineStr">
@@ -77545,7 +77597,7 @@
       </c>
       <c r="E1740" t="inlineStr">
         <is>
-          <t>Seite 3, 1/1 Seite</t>
+          <t>Tunnel klein</t>
         </is>
       </c>
       <c r="H1740" t="inlineStr">
@@ -77583,7 +77635,7 @@
       </c>
       <c r="E1741" t="inlineStr">
         <is>
-          <t>Seite 5, 1/1 Seite</t>
+          <t>Tunnel groß</t>
         </is>
       </c>
       <c r="H1741" t="inlineStr">
@@ -77621,7 +77673,7 @@
       </c>
       <c r="E1742" t="inlineStr">
         <is>
-          <t>Seite 7, 1/1 Seite</t>
+          <t>Seite 3, 1/1 Seite</t>
         </is>
       </c>
       <c r="H1742" t="inlineStr">
@@ -77659,7 +77711,7 @@
       </c>
       <c r="E1743" t="inlineStr">
         <is>
-          <t>Seite 9, 1/1 Seite</t>
+          <t>Seite 5, 1/1 Seite</t>
         </is>
       </c>
       <c r="H1743" t="inlineStr">
@@ -77697,7 +77749,7 @@
       </c>
       <c r="E1744" t="inlineStr">
         <is>
-          <t>Seite 11, 1/1 Seite</t>
+          <t>Seite 7, 1/1 Seite</t>
         </is>
       </c>
       <c r="H1744" t="inlineStr">
@@ -77735,7 +77787,7 @@
       </c>
       <c r="E1745" t="inlineStr">
         <is>
-          <t>Seite 3, A4 hoch</t>
+          <t>Seite 9, 1/1 Seite</t>
         </is>
       </c>
       <c r="H1745" t="inlineStr">
@@ -77773,7 +77825,7 @@
       </c>
       <c r="E1746" t="inlineStr">
         <is>
-          <t>Seite 5, A4 hoch</t>
+          <t>Seite 11, 1/1 Seite</t>
         </is>
       </c>
       <c r="H1746" t="inlineStr">
@@ -77811,7 +77863,7 @@
       </c>
       <c r="E1747" t="inlineStr">
         <is>
-          <t>Seite 7, A4 hoch</t>
+          <t>Seite 3, A4 hoch</t>
         </is>
       </c>
       <c r="H1747" t="inlineStr">
@@ -77849,7 +77901,7 @@
       </c>
       <c r="E1748" t="inlineStr">
         <is>
-          <t>Seite 9, A4 hoch</t>
+          <t>Seite 5, A4 hoch</t>
         </is>
       </c>
       <c r="H1748" t="inlineStr">
@@ -77887,7 +77939,7 @@
       </c>
       <c r="E1749" t="inlineStr">
         <is>
-          <t>Seite 11, A4 hoch</t>
+          <t>Seite 7, A4 hoch</t>
         </is>
       </c>
       <c r="H1749" t="inlineStr">
@@ -77920,12 +77972,12 @@
       </c>
       <c r="D1750" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Sonder- und Festplatzierungen</t>
         </is>
       </c>
       <c r="E1750" t="inlineStr">
         <is>
-          <t>Flex-Tarif – 1/1 Seite 4c</t>
+          <t>Seite 9, A4 hoch</t>
         </is>
       </c>
       <c r="H1750" t="inlineStr">
@@ -77958,12 +78010,12 @@
       </c>
       <c r="D1751" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Sonder- und Festplatzierungen</t>
         </is>
       </c>
       <c r="E1751" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (pro 1.000)</t>
+          <t>Seite 11, A4 hoch</t>
         </is>
       </c>
       <c r="H1751" t="inlineStr">
@@ -77996,12 +78048,12 @@
       </c>
       <c r="D1752" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1752" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (gesamt)</t>
+          <t>Flex-Tarif – 1/1 Seite 4c</t>
         </is>
       </c>
       <c r="H1752" t="inlineStr">
@@ -78039,7 +78091,7 @@
       </c>
       <c r="E1753" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 50g (gesamt)</t>
+          <t>Werbebeilage bis 25g (pro 1.000)</t>
         </is>
       </c>
       <c r="H1753" t="inlineStr">
@@ -78072,12 +78124,12 @@
       </c>
       <c r="D1754" t="inlineStr">
         <is>
-          <t>AdSpecials</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1754" t="inlineStr">
         <is>
-          <t>Großumleger 4-seitig</t>
+          <t>Werbebeilage bis 25g (gesamt)</t>
         </is>
       </c>
       <c r="H1754" t="inlineStr">
@@ -78110,12 +78162,12 @@
       </c>
       <c r="D1755" t="inlineStr">
         <is>
-          <t>AdSpecials</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1755" t="inlineStr">
         <is>
-          <t>Titelseite + 2. Seite</t>
+          <t>Werbebeilage bis 50g (gesamt)</t>
         </is>
       </c>
       <c r="H1755" t="inlineStr">
@@ -78153,7 +78205,7 @@
       </c>
       <c r="E1756" t="inlineStr">
         <is>
-          <t>Transparenzumleger 4-seitig</t>
+          <t>Großumleger 4-seitig</t>
         </is>
       </c>
       <c r="H1756" t="inlineStr">
@@ -78191,7 +78243,7 @@
       </c>
       <c r="E1757" t="inlineStr">
         <is>
-          <t>HalfCover TSK (voll)</t>
+          <t>Titelseite + 2. Seite</t>
         </is>
       </c>
       <c r="H1757" t="inlineStr">
@@ -78229,7 +78281,7 @@
       </c>
       <c r="E1758" t="inlineStr">
         <is>
-          <t>HalfCover TSK (1/2 Vorder-/Rückseite)</t>
+          <t>Transparenzumleger 4-seitig</t>
         </is>
       </c>
       <c r="H1758" t="inlineStr">
@@ -78267,7 +78319,7 @@
       </c>
       <c r="E1759" t="inlineStr">
         <is>
-          <t>Banderole</t>
+          <t>HalfCover TSK (voll)</t>
         </is>
       </c>
       <c r="H1759" t="inlineStr">
@@ -78305,7 +78357,7 @@
       </c>
       <c r="E1760" t="inlineStr">
         <is>
-          <t>Transparent-Flieger</t>
+          <t>HalfCover TSK (1/2 Vorder-/Rückseite)</t>
         </is>
       </c>
       <c r="H1760" t="inlineStr">
@@ -78343,32 +78395,108 @@
       </c>
       <c r="E1761" t="inlineStr">
         <is>
+          <t>Banderole</t>
+        </is>
+      </c>
+      <c r="H1761" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="I1761" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="K1761" t="inlineStr">
+        <is>
+          <t>Onkologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B1762" t="inlineStr">
+        <is>
+          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+        </is>
+      </c>
+      <c r="C1762" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D1762" t="inlineStr">
+        <is>
+          <t>AdSpecials</t>
+        </is>
+      </c>
+      <c r="E1762" t="inlineStr">
+        <is>
+          <t>Transparent-Flieger</t>
+        </is>
+      </c>
+      <c r="H1762" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="I1762" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="K1762" t="inlineStr">
+        <is>
+          <t>Onkologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B1763" t="inlineStr">
+        <is>
+          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+        </is>
+      </c>
+      <c r="C1763" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D1763" t="inlineStr">
+        <is>
+          <t>AdSpecials</t>
+        </is>
+      </c>
+      <c r="E1763" t="inlineStr">
+        <is>
           <t>Aufkleber maschinell</t>
         </is>
       </c>
-      <c r="H1761" t="inlineStr">
-        <is>
-          <t>nein</t>
-        </is>
-      </c>
-      <c r="I1761" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="K1761" t="inlineStr">
+      <c r="H1763" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="I1763" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="K1763" t="inlineStr">
         <is>
           <t>Onkologie</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1761"/>
+  <autoFilter ref="A1:L1763"/>
   <dataValidations count="2">
-    <dataValidation sqref="H2:I1761" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:I1763" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J1761" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J1763" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"DU,EH"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Angebotsdaten.xlsx
+++ b/Angebotsdaten.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Preise'!$A$1:$L$1846</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Termine'!$A$1:$J$408</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Staffeln'!$A$1:$E$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Staffeln'!$A$1:$E$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -90680,6 +90680,11 @@
           <t>Kardiologie</t>
         </is>
       </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>DGK-Kardiologen-Kongressausgabe</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -90725,6 +90730,11 @@
           <t>Innere Medizin</t>
         </is>
       </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>DGIM-Kongressausgabe</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -90815,6 +90825,11 @@
           <t>Diabetes</t>
         </is>
       </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>DDG-Diabetes-Kongressausgabe</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -91398,6 +91413,11 @@
       <c r="I202" t="inlineStr">
         <is>
           <t>Hochdruck</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Deutsche Hochdruckliga-Tagung-Kongressausgabe</t>
         </is>
       </c>
     </row>
@@ -99643,7 +99663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -99810,7 +99830,12 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2027</v>
+        <v>2026</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Allgemeinmedizin</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -99821,12 +99846,17 @@
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2027</v>
+        <v>2026</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Allgemeinmedizin</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -99837,12 +99867,17 @@
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2027</v>
+        <v>2026</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Allgemeinmedizin</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -99853,12 +99888,17 @@
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2027</v>
+        <v>2026</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Allgemeinmedizin</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -99866,10 +99906,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -99878,14 +99918,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mengenstaffel</t>
+          <t>Malstaffel</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -99894,14 +99934,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mengenstaffel</t>
+          <t>Malstaffel</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -99910,14 +99950,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mengenstaffel</t>
+          <t>Malstaffel</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -99926,18 +99966,82 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mengenstaffel</t>
+          <t>Malstaffel</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>18</v>
       </c>
       <c r="E17" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Mengenstaffel</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Mengenstaffel</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Mengenstaffel</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12</v>
+      </c>
+      <c r="E20" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Mengenstaffel</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>18</v>
+      </c>
+      <c r="E21" t="n">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E17"/>
+  <autoFilter ref="A1:E21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Angebotsdaten.xlsx
+++ b/Angebotsdaten.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Staffeln" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Preise'!$A$1:$L$1846</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Preise'!$A$1:$L$1856</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Termine'!$A$1:$J$408</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Staffeln'!$A$1:$E$21</definedName>
   </definedNames>
@@ -636,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1846"/>
+  <dimension ref="A1:L1856"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22406,7 +22406,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>1/1 Seite Festplatzierung</t>
+          <t>Seite ggü. Inhalt Journal Club</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -49048,7 +49048,7 @@
         </is>
       </c>
       <c r="C1066" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         </is>
       </c>
       <c r="C1067" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -49140,7 +49140,7 @@
         </is>
       </c>
       <c r="C1068" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -49186,7 +49186,7 @@
         </is>
       </c>
       <c r="C1069" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         </is>
       </c>
       <c r="C1070" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -49278,7 +49278,7 @@
         </is>
       </c>
       <c r="C1071" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -49324,7 +49324,7 @@
         </is>
       </c>
       <c r="C1072" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -49370,7 +49370,7 @@
         </is>
       </c>
       <c r="C1073" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -49416,7 +49416,7 @@
         </is>
       </c>
       <c r="C1074" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -49462,7 +49462,7 @@
         </is>
       </c>
       <c r="C1075" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -49508,7 +49508,7 @@
         </is>
       </c>
       <c r="C1076" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         </is>
       </c>
       <c r="C1077" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -49600,7 +49600,7 @@
         </is>
       </c>
       <c r="C1078" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -49646,7 +49646,7 @@
         </is>
       </c>
       <c r="C1079" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -49692,7 +49692,7 @@
         </is>
       </c>
       <c r="C1080" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -49738,7 +49738,7 @@
         </is>
       </c>
       <c r="C1081" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -49784,7 +49784,7 @@
         </is>
       </c>
       <c r="C1082" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -49830,7 +49830,7 @@
         </is>
       </c>
       <c r="C1083" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -49876,7 +49876,7 @@
         </is>
       </c>
       <c r="C1084" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         </is>
       </c>
       <c r="C1085" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -49968,7 +49968,7 @@
         </is>
       </c>
       <c r="C1086" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         </is>
       </c>
       <c r="C1087" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -50060,7 +50060,7 @@
         </is>
       </c>
       <c r="C1088" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -50106,7 +50106,7 @@
         </is>
       </c>
       <c r="C1089" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -50152,7 +50152,7 @@
         </is>
       </c>
       <c r="C1090" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -50198,7 +50198,7 @@
         </is>
       </c>
       <c r="C1091" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -50244,7 +50244,7 @@
         </is>
       </c>
       <c r="C1092" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -50290,7 +50290,7 @@
         </is>
       </c>
       <c r="C1093" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         </is>
       </c>
       <c r="C1094" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         </is>
       </c>
       <c r="C1095" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -50428,7 +50428,7 @@
         </is>
       </c>
       <c r="C1096" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -50469,7 +50469,7 @@
         </is>
       </c>
       <c r="C1097" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -50510,7 +50510,7 @@
         </is>
       </c>
       <c r="C1098" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         </is>
       </c>
       <c r="C1099" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         </is>
       </c>
       <c r="C1100" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -50633,7 +50633,7 @@
         </is>
       </c>
       <c r="C1101" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
@@ -50674,7 +50674,7 @@
         </is>
       </c>
       <c r="C1102" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1102" t="inlineStr">
         <is>
@@ -50720,7 +50720,7 @@
         </is>
       </c>
       <c r="C1103" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1103" t="inlineStr">
         <is>
@@ -50761,7 +50761,7 @@
         </is>
       </c>
       <c r="C1104" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1104" t="inlineStr">
         <is>
@@ -50802,7 +50802,7 @@
         </is>
       </c>
       <c r="C1105" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1105" t="inlineStr">
         <is>
@@ -50843,7 +50843,7 @@
         </is>
       </c>
       <c r="C1106" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1106" t="inlineStr">
         <is>
@@ -50884,7 +50884,7 @@
         </is>
       </c>
       <c r="C1107" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1107" t="inlineStr">
         <is>
@@ -50925,7 +50925,7 @@
         </is>
       </c>
       <c r="C1108" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1108" t="inlineStr">
         <is>
@@ -50966,7 +50966,7 @@
         </is>
       </c>
       <c r="C1109" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1109" t="inlineStr">
         <is>
@@ -51007,7 +51007,7 @@
         </is>
       </c>
       <c r="C1110" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1110" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         </is>
       </c>
       <c r="C1111" t="n">
-        <v>8800</v>
+        <v>8930</v>
       </c>
       <c r="D1111" t="inlineStr">
         <is>
@@ -69998,7 +69998,7 @@
       </c>
       <c r="E1534" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt Journal Screen</t>
+          <t>Seite ggü. Inhalt Journal Club</t>
         </is>
       </c>
       <c r="F1534" t="n">
@@ -70175,24 +70175,24 @@
       </c>
       <c r="B1538" t="inlineStr">
         <is>
-          <t>Cardio News</t>
+          <t>PNEUMONEWS</t>
         </is>
       </c>
       <c r="C1538" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1538" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1538" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
+          <t>1. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="F1538" t="n">
-        <v>7760</v>
+        <v>4100</v>
       </c>
       <c r="H1538" t="inlineStr">
         <is>
@@ -70211,7 +70211,7 @@
       </c>
       <c r="K1538" t="inlineStr">
         <is>
-          <t>Kardiologie</t>
+          <t>Pneumologie</t>
         </is>
       </c>
     </row>
@@ -70221,24 +70221,24 @@
       </c>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>Cardio News</t>
+          <t>PNEUMONEWS</t>
         </is>
       </c>
       <c r="C1539" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1539" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1539" t="inlineStr">
         <is>
-          <t>A4 hoch</t>
+          <t>2. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="F1539" t="n">
-        <v>6720</v>
+        <v>4100</v>
       </c>
       <c r="H1539" t="inlineStr">
         <is>
@@ -70257,7 +70257,7 @@
       </c>
       <c r="K1539" t="inlineStr">
         <is>
-          <t>Kardiologie</t>
+          <t>Pneumologie</t>
         </is>
       </c>
     </row>
@@ -70267,24 +70267,24 @@
       </c>
       <c r="B1540" t="inlineStr">
         <is>
-          <t>Cardio News</t>
+          <t>PNEUMONEWS</t>
         </is>
       </c>
       <c r="C1540" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1540" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1540" t="inlineStr">
         <is>
-          <t>3/4 Seite</t>
+          <t>3. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="F1540" t="n">
-        <v>7400</v>
+        <v>4100</v>
       </c>
       <c r="H1540" t="inlineStr">
         <is>
@@ -70303,7 +70303,7 @@
       </c>
       <c r="K1540" t="inlineStr">
         <is>
-          <t>Kardiologie</t>
+          <t>Pneumologie</t>
         </is>
       </c>
     </row>
@@ -70313,24 +70313,24 @@
       </c>
       <c r="B1541" t="inlineStr">
         <is>
-          <t>Cardio News</t>
+          <t>PNEUMONEWS</t>
         </is>
       </c>
       <c r="C1541" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1541" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1541" t="inlineStr">
         <is>
-          <t>3/5 Seite</t>
+          <t>4. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="F1541" t="n">
-        <v>6100</v>
+        <v>4100</v>
       </c>
       <c r="H1541" t="inlineStr">
         <is>
@@ -70349,7 +70349,7 @@
       </c>
       <c r="K1541" t="inlineStr">
         <is>
-          <t>Kardiologie</t>
+          <t>Pneumologie</t>
         </is>
       </c>
     </row>
@@ -70359,24 +70359,24 @@
       </c>
       <c r="B1542" t="inlineStr">
         <is>
-          <t>Cardio News</t>
+          <t>PNEUMONEWS</t>
         </is>
       </c>
       <c r="C1542" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1542" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1542" t="inlineStr">
         <is>
-          <t>2/3 Seite</t>
+          <t>5. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="F1542" t="n">
-        <v>6000</v>
+        <v>4100</v>
       </c>
       <c r="H1542" t="inlineStr">
         <is>
@@ -70395,7 +70395,7 @@
       </c>
       <c r="K1542" t="inlineStr">
         <is>
-          <t>Kardiologie</t>
+          <t>Pneumologie</t>
         </is>
       </c>
     </row>
@@ -70405,24 +70405,24 @@
       </c>
       <c r="B1543" t="inlineStr">
         <is>
-          <t>Cardio News</t>
+          <t>PNEUMONEWS</t>
         </is>
       </c>
       <c r="C1543" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1543" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1543" t="inlineStr">
         <is>
-          <t>1/2 Seite</t>
+          <t>6. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="F1543" t="n">
-        <v>4900</v>
+        <v>4100</v>
       </c>
       <c r="H1543" t="inlineStr">
         <is>
@@ -70441,7 +70441,7 @@
       </c>
       <c r="K1543" t="inlineStr">
         <is>
-          <t>Kardiologie</t>
+          <t>Pneumologie</t>
         </is>
       </c>
     </row>
@@ -70451,24 +70451,24 @@
       </c>
       <c r="B1544" t="inlineStr">
         <is>
-          <t>Cardio News</t>
+          <t>PNEUMONEWS</t>
         </is>
       </c>
       <c r="C1544" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1544" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1544" t="inlineStr">
         <is>
-          <t>2/5 Seite</t>
+          <t>7. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="F1544" t="n">
-        <v>4380</v>
+        <v>4100</v>
       </c>
       <c r="H1544" t="inlineStr">
         <is>
@@ -70487,7 +70487,7 @@
       </c>
       <c r="K1544" t="inlineStr">
         <is>
-          <t>Kardiologie</t>
+          <t>Pneumologie</t>
         </is>
       </c>
     </row>
@@ -70497,24 +70497,24 @@
       </c>
       <c r="B1545" t="inlineStr">
         <is>
-          <t>Cardio News</t>
+          <t>PNEUMONEWS</t>
         </is>
       </c>
       <c r="C1545" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1545" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1545" t="inlineStr">
         <is>
-          <t>1/3 Seite</t>
+          <t>8. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="F1545" t="n">
-        <v>3700</v>
+        <v>4100</v>
       </c>
       <c r="H1545" t="inlineStr">
         <is>
@@ -70533,7 +70533,7 @@
       </c>
       <c r="K1545" t="inlineStr">
         <is>
-          <t>Kardiologie</t>
+          <t>Pneumologie</t>
         </is>
       </c>
     </row>
@@ -70543,24 +70543,24 @@
       </c>
       <c r="B1546" t="inlineStr">
         <is>
-          <t>Cardio News</t>
+          <t>PNEUMONEWS</t>
         </is>
       </c>
       <c r="C1546" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1546" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1546" t="inlineStr">
         <is>
-          <t>1/4 Seite</t>
+          <t>9. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="F1546" t="n">
-        <v>3690</v>
+        <v>4100</v>
       </c>
       <c r="H1546" t="inlineStr">
         <is>
@@ -70579,7 +70579,7 @@
       </c>
       <c r="K1546" t="inlineStr">
         <is>
-          <t>Kardiologie</t>
+          <t>Pneumologie</t>
         </is>
       </c>
     </row>
@@ -70589,24 +70589,24 @@
       </c>
       <c r="B1547" t="inlineStr">
         <is>
-          <t>Cardio News</t>
+          <t>PNEUMONEWS</t>
         </is>
       </c>
       <c r="C1547" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="D1547" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1547" t="inlineStr">
         <is>
-          <t>2/10 Seite</t>
+          <t>10. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="F1547" t="n">
-        <v>3590</v>
+        <v>4100</v>
       </c>
       <c r="H1547" t="inlineStr">
         <is>
@@ -70625,7 +70625,7 @@
       </c>
       <c r="K1547" t="inlineStr">
         <is>
-          <t>Kardiologie</t>
+          <t>Pneumologie</t>
         </is>
       </c>
     </row>
@@ -70648,11 +70648,11 @@
       </c>
       <c r="E1548" t="inlineStr">
         <is>
-          <t>Tunnel groß</t>
+          <t>1/1 Seite</t>
         </is>
       </c>
       <c r="F1548" t="n">
-        <v>4690</v>
+        <v>7760</v>
       </c>
       <c r="H1548" t="inlineStr">
         <is>
@@ -70694,11 +70694,11 @@
       </c>
       <c r="E1549" t="inlineStr">
         <is>
-          <t>Insel maxi</t>
+          <t>A4 hoch</t>
         </is>
       </c>
       <c r="F1549" t="n">
-        <v>4990</v>
+        <v>6720</v>
       </c>
       <c r="H1549" t="inlineStr">
         <is>
@@ -70735,16 +70735,16 @@
       </c>
       <c r="D1550" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1550" t="inlineStr">
         <is>
-          <t>Seite 2 A4</t>
+          <t>3/4 Seite</t>
         </is>
       </c>
       <c r="F1550" t="n">
-        <v>8170</v>
+        <v>7400</v>
       </c>
       <c r="H1550" t="inlineStr">
         <is>
@@ -70781,16 +70781,16 @@
       </c>
       <c r="D1551" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1551" t="inlineStr">
         <is>
-          <t>Seite 5 1/1</t>
+          <t>3/5 Seite</t>
         </is>
       </c>
       <c r="F1551" t="n">
-        <v>8650</v>
+        <v>6100</v>
       </c>
       <c r="H1551" t="inlineStr">
         <is>
@@ -70827,16 +70827,16 @@
       </c>
       <c r="D1552" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1552" t="inlineStr">
         <is>
-          <t>Seite 5 A4</t>
+          <t>2/3 Seite</t>
         </is>
       </c>
       <c r="F1552" t="n">
-        <v>7400</v>
+        <v>6000</v>
       </c>
       <c r="H1552" t="inlineStr">
         <is>
@@ -70873,16 +70873,16 @@
       </c>
       <c r="D1553" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1553" t="inlineStr">
         <is>
-          <t>Letzte Seite 1/1</t>
+          <t>1/2 Seite</t>
         </is>
       </c>
       <c r="F1553" t="n">
-        <v>8200</v>
+        <v>4900</v>
       </c>
       <c r="H1553" t="inlineStr">
         <is>
@@ -70919,16 +70919,16 @@
       </c>
       <c r="D1554" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1554" t="inlineStr">
         <is>
-          <t>Letzte Seite A4</t>
+          <t>2/5 Seite</t>
         </is>
       </c>
       <c r="F1554" t="n">
-        <v>7080</v>
+        <v>4380</v>
       </c>
       <c r="H1554" t="inlineStr">
         <is>
@@ -70965,25 +70965,30 @@
       </c>
       <c r="D1555" t="inlineStr">
         <is>
-          <t>AdSpecials</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1555" t="inlineStr">
         <is>
-          <t>Banderole</t>
+          <t>1/3 Seite</t>
         </is>
       </c>
       <c r="F1555" t="n">
-        <v>9990</v>
+        <v>3700</v>
       </c>
       <c r="H1555" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="I1555" t="inlineStr">
         <is>
           <t>ja</t>
+        </is>
+      </c>
+      <c r="J1555" t="inlineStr">
+        <is>
+          <t>DU</t>
         </is>
       </c>
       <c r="K1555" t="inlineStr">
@@ -70998,11 +71003,11 @@
       </c>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>DGU Kongresszeitung</t>
+          <t>Cardio News</t>
         </is>
       </c>
       <c r="C1556" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D1556" t="inlineStr">
         <is>
@@ -71011,11 +71016,11 @@
       </c>
       <c r="E1556" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
+          <t>1/4 Seite</t>
         </is>
       </c>
       <c r="F1556" t="n">
-        <v>6100</v>
+        <v>3690</v>
       </c>
       <c r="H1556" t="inlineStr">
         <is>
@@ -71034,7 +71039,7 @@
       </c>
       <c r="K1556" t="inlineStr">
         <is>
-          <t>Urologie</t>
+          <t>Kardiologie</t>
         </is>
       </c>
     </row>
@@ -71044,11 +71049,11 @@
       </c>
       <c r="B1557" t="inlineStr">
         <is>
-          <t>DGU Kongresszeitung</t>
+          <t>Cardio News</t>
         </is>
       </c>
       <c r="C1557" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D1557" t="inlineStr">
         <is>
@@ -71057,11 +71062,11 @@
       </c>
       <c r="E1557" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>2/10 Seite</t>
         </is>
       </c>
       <c r="F1557" t="n">
-        <v>5540</v>
+        <v>3590</v>
       </c>
       <c r="H1557" t="inlineStr">
         <is>
@@ -71080,7 +71085,7 @@
       </c>
       <c r="K1557" t="inlineStr">
         <is>
-          <t>Urologie</t>
+          <t>Kardiologie</t>
         </is>
       </c>
     </row>
@@ -71090,11 +71095,11 @@
       </c>
       <c r="B1558" t="inlineStr">
         <is>
-          <t>DGU Kongresszeitung</t>
+          <t>Cardio News</t>
         </is>
       </c>
       <c r="C1558" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D1558" t="inlineStr">
         <is>
@@ -71103,11 +71108,11 @@
       </c>
       <c r="E1558" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>Tunnel groß</t>
         </is>
       </c>
       <c r="F1558" t="n">
-        <v>4150</v>
+        <v>4690</v>
       </c>
       <c r="H1558" t="inlineStr">
         <is>
@@ -71126,7 +71131,7 @@
       </c>
       <c r="K1558" t="inlineStr">
         <is>
-          <t>Urologie</t>
+          <t>Kardiologie</t>
         </is>
       </c>
     </row>
@@ -71136,11 +71141,11 @@
       </c>
       <c r="B1559" t="inlineStr">
         <is>
-          <t>DGU Kongresszeitung</t>
+          <t>Cardio News</t>
         </is>
       </c>
       <c r="C1559" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D1559" t="inlineStr">
         <is>
@@ -71149,11 +71154,11 @@
       </c>
       <c r="E1559" t="inlineStr">
         <is>
-          <t>3/4 Seite quer</t>
+          <t>Insel maxi</t>
         </is>
       </c>
       <c r="F1559" t="n">
-        <v>5630</v>
+        <v>4990</v>
       </c>
       <c r="H1559" t="inlineStr">
         <is>
@@ -71172,7 +71177,7 @@
       </c>
       <c r="K1559" t="inlineStr">
         <is>
-          <t>Urologie</t>
+          <t>Kardiologie</t>
         </is>
       </c>
     </row>
@@ -71182,24 +71187,24 @@
       </c>
       <c r="B1560" t="inlineStr">
         <is>
-          <t>DGU Kongresszeitung</t>
+          <t>Cardio News</t>
         </is>
       </c>
       <c r="C1560" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D1560" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1560" t="inlineStr">
         <is>
-          <t>1/2 Seite</t>
+          <t>Seite 2 A4</t>
         </is>
       </c>
       <c r="F1560" t="n">
-        <v>5250</v>
+        <v>8170</v>
       </c>
       <c r="H1560" t="inlineStr">
         <is>
@@ -71218,7 +71223,7 @@
       </c>
       <c r="K1560" t="inlineStr">
         <is>
-          <t>Urologie</t>
+          <t>Kardiologie</t>
         </is>
       </c>
     </row>
@@ -71228,24 +71233,24 @@
       </c>
       <c r="B1561" t="inlineStr">
         <is>
-          <t>DGU Kongresszeitung</t>
+          <t>Cardio News</t>
         </is>
       </c>
       <c r="C1561" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D1561" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1561" t="inlineStr">
         <is>
-          <t>1/4 seite</t>
+          <t>Seite 5 1/1</t>
         </is>
       </c>
       <c r="F1561" t="n">
-        <v>2850</v>
+        <v>8650</v>
       </c>
       <c r="H1561" t="inlineStr">
         <is>
@@ -71264,7 +71269,7 @@
       </c>
       <c r="K1561" t="inlineStr">
         <is>
-          <t>Urologie</t>
+          <t>Kardiologie</t>
         </is>
       </c>
     </row>
@@ -71274,24 +71279,24 @@
       </c>
       <c r="B1562" t="inlineStr">
         <is>
-          <t>DGU Kongresszeitung</t>
+          <t>Cardio News</t>
         </is>
       </c>
       <c r="C1562" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D1562" t="inlineStr">
         <is>
-          <t>Sonderplatzierungen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1562" t="inlineStr">
         <is>
-          <t>Titelseitenfuß</t>
+          <t>Seite 5 A4</t>
         </is>
       </c>
       <c r="F1562" t="n">
-        <v>5300</v>
+        <v>7400</v>
       </c>
       <c r="H1562" t="inlineStr">
         <is>
@@ -71310,7 +71315,7 @@
       </c>
       <c r="K1562" t="inlineStr">
         <is>
-          <t>Urologie</t>
+          <t>Kardiologie</t>
         </is>
       </c>
     </row>
@@ -71320,28 +71325,28 @@
       </c>
       <c r="B1563" t="inlineStr">
         <is>
-          <t>DGU Kongresszeitung</t>
+          <t>Cardio News</t>
         </is>
       </c>
       <c r="C1563" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D1563" t="inlineStr">
         <is>
-          <t>Sonderplatzierungen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1563" t="inlineStr">
         <is>
-          <t>Insel</t>
+          <t>Letzte Seite 1/1</t>
         </is>
       </c>
       <c r="F1563" t="n">
-        <v>3260</v>
+        <v>8200</v>
       </c>
       <c r="H1563" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="I1563" t="inlineStr">
@@ -71356,7 +71361,7 @@
       </c>
       <c r="K1563" t="inlineStr">
         <is>
-          <t>Urologie</t>
+          <t>Kardiologie</t>
         </is>
       </c>
     </row>
@@ -71366,28 +71371,28 @@
       </c>
       <c r="B1564" t="inlineStr">
         <is>
-          <t>DGU Kongresszeitung</t>
+          <t>Cardio News</t>
         </is>
       </c>
       <c r="C1564" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D1564" t="inlineStr">
         <is>
-          <t>Sonderplatzierungen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1564" t="inlineStr">
         <is>
-          <t>Insel maxi</t>
+          <t>Letzte Seite A4</t>
         </is>
       </c>
       <c r="F1564" t="n">
-        <v>5300</v>
+        <v>7080</v>
       </c>
       <c r="H1564" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="I1564" t="inlineStr">
@@ -71402,7 +71407,7 @@
       </c>
       <c r="K1564" t="inlineStr">
         <is>
-          <t>Urologie</t>
+          <t>Kardiologie</t>
         </is>
       </c>
     </row>
@@ -71412,24 +71417,24 @@
       </c>
       <c r="B1565" t="inlineStr">
         <is>
-          <t>DGU Kongresszeitung</t>
+          <t>Cardio News</t>
         </is>
       </c>
       <c r="C1565" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D1565" t="inlineStr">
         <is>
-          <t>Sonderplatzierungen</t>
+          <t>AdSpecials</t>
         </is>
       </c>
       <c r="E1565" t="inlineStr">
         <is>
-          <t>Tunnel klein</t>
+          <t>Banderole</t>
         </is>
       </c>
       <c r="F1565" t="n">
-        <v>2930</v>
+        <v>9990</v>
       </c>
       <c r="H1565" t="inlineStr">
         <is>
@@ -71441,14 +71446,9 @@
           <t>ja</t>
         </is>
       </c>
-      <c r="J1565" t="inlineStr">
-        <is>
-          <t>DU</t>
-        </is>
-      </c>
       <c r="K1565" t="inlineStr">
         <is>
-          <t>Urologie</t>
+          <t>Kardiologie</t>
         </is>
       </c>
     </row>
@@ -71466,20 +71466,20 @@
       </c>
       <c r="D1566" t="inlineStr">
         <is>
-          <t>Sonderplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1566" t="inlineStr">
         <is>
-          <t>Tunnel groß</t>
+          <t>1/1 Seite</t>
         </is>
       </c>
       <c r="F1566" t="n">
-        <v>4160</v>
+        <v>6100</v>
       </c>
       <c r="H1566" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="I1566" t="inlineStr">
@@ -71512,20 +71512,20 @@
       </c>
       <c r="D1567" t="inlineStr">
         <is>
-          <t>Sonderplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1567" t="inlineStr">
         <is>
-          <t>Großumleger</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="F1567" t="n">
-        <v>18500</v>
+        <v>5540</v>
       </c>
       <c r="H1567" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="I1567" t="inlineStr">
@@ -71558,20 +71558,20 @@
       </c>
       <c r="D1568" t="inlineStr">
         <is>
-          <t>Sonderplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1568" t="inlineStr">
         <is>
-          <t>Titelseite + 2.Seite</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="F1568" t="n">
-        <v>14900</v>
+        <v>4150</v>
       </c>
       <c r="H1568" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="I1568" t="inlineStr">
@@ -71604,20 +71604,20 @@
       </c>
       <c r="D1569" t="inlineStr">
         <is>
-          <t>Sonderplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1569" t="inlineStr">
         <is>
-          <t>Transparenzumleger</t>
+          <t>3/4 Seite quer</t>
         </is>
       </c>
       <c r="F1569" t="n">
-        <v>14900</v>
+        <v>5630</v>
       </c>
       <c r="H1569" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="I1569" t="inlineStr">
@@ -71650,20 +71650,20 @@
       </c>
       <c r="D1570" t="inlineStr">
         <is>
-          <t>Sonderplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1570" t="inlineStr">
         <is>
-          <t>Banderole</t>
+          <t>1/2 Seite</t>
         </is>
       </c>
       <c r="F1570" t="n">
-        <v>5100</v>
+        <v>5250</v>
       </c>
       <c r="H1570" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="I1570" t="inlineStr">
@@ -71673,7 +71673,7 @@
       </c>
       <c r="J1570" t="inlineStr">
         <is>
-          <t>EH</t>
+          <t>DU</t>
         </is>
       </c>
       <c r="K1570" t="inlineStr">
@@ -71696,20 +71696,20 @@
       </c>
       <c r="D1571" t="inlineStr">
         <is>
-          <t>Sonderplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1571" t="inlineStr">
         <is>
-          <t>Aufkleber + Trägeranzeige</t>
+          <t>1/4 seite</t>
         </is>
       </c>
       <c r="F1571" t="n">
-        <v>2300</v>
+        <v>2850</v>
       </c>
       <c r="H1571" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="I1571" t="inlineStr">
@@ -71719,7 +71719,7 @@
       </c>
       <c r="J1571" t="inlineStr">
         <is>
-          <t>EH</t>
+          <t>DU</t>
         </is>
       </c>
       <c r="K1571" t="inlineStr">
@@ -71742,20 +71742,20 @@
       </c>
       <c r="D1572" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Sonderplatzierungen</t>
         </is>
       </c>
       <c r="E1572" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (pro 1.000)</t>
+          <t>Titelseitenfuß</t>
         </is>
       </c>
       <c r="F1572" t="n">
-        <v>580</v>
+        <v>5300</v>
       </c>
       <c r="H1572" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="I1572" t="inlineStr">
@@ -71765,7 +71765,7 @@
       </c>
       <c r="J1572" t="inlineStr">
         <is>
-          <t>EH</t>
+          <t>DU</t>
         </is>
       </c>
       <c r="K1572" t="inlineStr">
@@ -71776,25 +71776,28 @@
     </row>
     <row r="1573">
       <c r="A1573" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B1573" t="inlineStr">
         <is>
-          <t>Die Onkologie</t>
+          <t>DGU Kongresszeitung</t>
         </is>
       </c>
       <c r="C1573" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="D1573" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderplatzierungen</t>
         </is>
       </c>
       <c r="E1573" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
-        </is>
+          <t>Insel</t>
+        </is>
+      </c>
+      <c r="F1573" t="n">
+        <v>3260</v>
       </c>
       <c r="H1573" t="inlineStr">
         <is>
@@ -71806,33 +71809,41 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J1573" t="inlineStr">
+        <is>
+          <t>DU</t>
+        </is>
+      </c>
       <c r="K1573" t="inlineStr">
         <is>
-          <t>Onkologie</t>
+          <t>Urologie</t>
         </is>
       </c>
     </row>
     <row r="1574">
       <c r="A1574" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B1574" t="inlineStr">
         <is>
-          <t>Die Onkologie</t>
+          <t>DGU Kongresszeitung</t>
         </is>
       </c>
       <c r="C1574" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="D1574" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderplatzierungen</t>
         </is>
       </c>
       <c r="E1574" t="inlineStr">
         <is>
-          <t>1/2 Seite</t>
-        </is>
+          <t>Insel maxi</t>
+        </is>
+      </c>
+      <c r="F1574" t="n">
+        <v>5300</v>
       </c>
       <c r="H1574" t="inlineStr">
         <is>
@@ -71844,33 +71855,41 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J1574" t="inlineStr">
+        <is>
+          <t>DU</t>
+        </is>
+      </c>
       <c r="K1574" t="inlineStr">
         <is>
-          <t>Onkologie</t>
+          <t>Urologie</t>
         </is>
       </c>
     </row>
     <row r="1575">
       <c r="A1575" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B1575" t="inlineStr">
         <is>
-          <t>Die Onkologie</t>
+          <t>DGU Kongresszeitung</t>
         </is>
       </c>
       <c r="C1575" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="D1575" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderplatzierungen</t>
         </is>
       </c>
       <c r="E1575" t="inlineStr">
         <is>
-          <t>1/3 Seite</t>
-        </is>
+          <t>Tunnel klein</t>
+        </is>
+      </c>
+      <c r="F1575" t="n">
+        <v>2930</v>
       </c>
       <c r="H1575" t="inlineStr">
         <is>
@@ -71882,33 +71901,41 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J1575" t="inlineStr">
+        <is>
+          <t>DU</t>
+        </is>
+      </c>
       <c r="K1575" t="inlineStr">
         <is>
-          <t>Onkologie</t>
+          <t>Urologie</t>
         </is>
       </c>
     </row>
     <row r="1576">
       <c r="A1576" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B1576" t="inlineStr">
         <is>
-          <t>Die Onkologie</t>
+          <t>DGU Kongresszeitung</t>
         </is>
       </c>
       <c r="C1576" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="D1576" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderplatzierungen</t>
         </is>
       </c>
       <c r="E1576" t="inlineStr">
         <is>
-          <t>1/4 Seite</t>
-        </is>
+          <t>Tunnel groß</t>
+        </is>
+      </c>
+      <c r="F1576" t="n">
+        <v>4160</v>
       </c>
       <c r="H1576" t="inlineStr">
         <is>
@@ -71920,33 +71947,41 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J1576" t="inlineStr">
+        <is>
+          <t>DU</t>
+        </is>
+      </c>
       <c r="K1576" t="inlineStr">
         <is>
-          <t>Onkologie</t>
+          <t>Urologie</t>
         </is>
       </c>
     </row>
     <row r="1577">
       <c r="A1577" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B1577" t="inlineStr">
         <is>
-          <t>Die Onkologie</t>
+          <t>DGU Kongresszeitung</t>
         </is>
       </c>
       <c r="C1577" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="D1577" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderplatzierungen</t>
         </is>
       </c>
       <c r="E1577" t="inlineStr">
         <is>
-          <t>2/1 Doppelseite</t>
-        </is>
+          <t>Großumleger</t>
+        </is>
+      </c>
+      <c r="F1577" t="n">
+        <v>18500</v>
       </c>
       <c r="H1577" t="inlineStr">
         <is>
@@ -71958,33 +71993,41 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J1577" t="inlineStr">
+        <is>
+          <t>DU</t>
+        </is>
+      </c>
       <c r="K1577" t="inlineStr">
         <is>
-          <t>Onkologie</t>
+          <t>Urologie</t>
         </is>
       </c>
     </row>
     <row r="1578">
       <c r="A1578" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B1578" t="inlineStr">
         <is>
-          <t>Die Onkologie</t>
+          <t>DGU Kongresszeitung</t>
         </is>
       </c>
       <c r="C1578" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="D1578" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderplatzierungen</t>
         </is>
       </c>
       <c r="E1578" t="inlineStr">
         <is>
-          <t>Advertorial (1/1 Seite)</t>
-        </is>
+          <t>Titelseite + 2.Seite</t>
+        </is>
+      </c>
+      <c r="F1578" t="n">
+        <v>14900</v>
       </c>
       <c r="H1578" t="inlineStr">
         <is>
@@ -71996,33 +72039,41 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J1578" t="inlineStr">
+        <is>
+          <t>DU</t>
+        </is>
+      </c>
       <c r="K1578" t="inlineStr">
         <is>
-          <t>Onkologie</t>
+          <t>Urologie</t>
         </is>
       </c>
     </row>
     <row r="1579">
       <c r="A1579" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B1579" t="inlineStr">
         <is>
-          <t>Die Onkologie</t>
+          <t>DGU Kongresszeitung</t>
         </is>
       </c>
       <c r="C1579" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="D1579" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Sonderplatzierungen</t>
         </is>
       </c>
       <c r="E1579" t="inlineStr">
         <is>
-          <t>4. Umschlagseite</t>
-        </is>
+          <t>Transparenzumleger</t>
+        </is>
+      </c>
+      <c r="F1579" t="n">
+        <v>14900</v>
       </c>
       <c r="H1579" t="inlineStr">
         <is>
@@ -72034,33 +72085,41 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J1579" t="inlineStr">
+        <is>
+          <t>DU</t>
+        </is>
+      </c>
       <c r="K1579" t="inlineStr">
         <is>
-          <t>Onkologie</t>
+          <t>Urologie</t>
         </is>
       </c>
     </row>
     <row r="1580">
       <c r="A1580" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B1580" t="inlineStr">
         <is>
-          <t>Die Onkologie</t>
+          <t>DGU Kongresszeitung</t>
         </is>
       </c>
       <c r="C1580" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="D1580" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Sonderplatzierungen</t>
         </is>
       </c>
       <c r="E1580" t="inlineStr">
         <is>
-          <t>2. Umschlagseite</t>
-        </is>
+          <t>Banderole</t>
+        </is>
+      </c>
+      <c r="F1580" t="n">
+        <v>5100</v>
       </c>
       <c r="H1580" t="inlineStr">
         <is>
@@ -72072,33 +72131,41 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J1580" t="inlineStr">
+        <is>
+          <t>EH</t>
+        </is>
+      </c>
       <c r="K1580" t="inlineStr">
         <is>
-          <t>Onkologie</t>
+          <t>Urologie</t>
         </is>
       </c>
     </row>
     <row r="1581">
       <c r="A1581" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B1581" t="inlineStr">
         <is>
-          <t>Die Onkologie</t>
+          <t>DGU Kongresszeitung</t>
         </is>
       </c>
       <c r="C1581" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="D1581" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Sonderplatzierungen</t>
         </is>
       </c>
       <c r="E1581" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt / red. Info</t>
-        </is>
+          <t>Aufkleber + Trägeranzeige</t>
+        </is>
+      </c>
+      <c r="F1581" t="n">
+        <v>2300</v>
       </c>
       <c r="H1581" t="inlineStr">
         <is>
@@ -72110,33 +72177,41 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J1581" t="inlineStr">
+        <is>
+          <t>EH</t>
+        </is>
+      </c>
       <c r="K1581" t="inlineStr">
         <is>
-          <t>Onkologie</t>
+          <t>Urologie</t>
         </is>
       </c>
     </row>
     <row r="1582">
       <c r="A1582" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B1582" t="inlineStr">
         <is>
-          <t>Die Onkologie</t>
+          <t>DGU Kongresszeitung</t>
         </is>
       </c>
       <c r="C1582" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="D1582" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1582" t="inlineStr">
         <is>
-          <t>Seite ggü. Hrsg. 1</t>
-        </is>
+          <t>Werbebeilage bis 25g (pro 1.000)</t>
+        </is>
+      </c>
+      <c r="F1582" t="n">
+        <v>580</v>
       </c>
       <c r="H1582" t="inlineStr">
         <is>
@@ -72148,9 +72223,14 @@
           <t>ja</t>
         </is>
       </c>
+      <c r="J1582" t="inlineStr">
+        <is>
+          <t>EH</t>
+        </is>
+      </c>
       <c r="K1582" t="inlineStr">
         <is>
-          <t>Onkologie</t>
+          <t>Urologie</t>
         </is>
       </c>
     </row>
@@ -72168,12 +72248,12 @@
       </c>
       <c r="D1583" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1583" t="inlineStr">
         <is>
-          <t>Seite ggü. Hrsg. 2</t>
+          <t>1/1 Seite</t>
         </is>
       </c>
       <c r="H1583" t="inlineStr">
@@ -72206,12 +72286,12 @@
       </c>
       <c r="D1584" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1584" t="inlineStr">
         <is>
-          <t>Seite ggü. Textanfang</t>
+          <t>1/2 Seite</t>
         </is>
       </c>
       <c r="H1584" t="inlineStr">
@@ -72244,12 +72324,12 @@
       </c>
       <c r="D1585" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1585" t="inlineStr">
         <is>
-          <t>1/1 Seite Festplatzierung</t>
+          <t>1/3 Seite</t>
         </is>
       </c>
       <c r="H1585" t="inlineStr">
@@ -72282,12 +72362,12 @@
       </c>
       <c r="D1586" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1586" t="inlineStr">
         <is>
-          <t>1. rechte Einschaltseite</t>
+          <t>1/4 Seite</t>
         </is>
       </c>
       <c r="H1586" t="inlineStr">
@@ -72320,12 +72400,12 @@
       </c>
       <c r="D1587" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1587" t="inlineStr">
         <is>
-          <t>2. rechte Einschaltseite</t>
+          <t>2/1 Doppelseite</t>
         </is>
       </c>
       <c r="H1587" t="inlineStr">
@@ -72358,12 +72438,12 @@
       </c>
       <c r="D1588" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1588" t="inlineStr">
         <is>
-          <t>3. rechte Einschaltseite</t>
+          <t>Advertorial (1/1 Seite)</t>
         </is>
       </c>
       <c r="H1588" t="inlineStr">
@@ -72401,7 +72481,7 @@
       </c>
       <c r="E1589" t="inlineStr">
         <is>
-          <t>4. rechte Einschaltseite</t>
+          <t>4. Umschlagseite</t>
         </is>
       </c>
       <c r="H1589" t="inlineStr">
@@ -72439,7 +72519,7 @@
       </c>
       <c r="E1590" t="inlineStr">
         <is>
-          <t>5. rechte Einschaltseite</t>
+          <t>2. Umschlagseite</t>
         </is>
       </c>
       <c r="H1590" t="inlineStr">
@@ -72477,7 +72557,7 @@
       </c>
       <c r="E1591" t="inlineStr">
         <is>
-          <t>6. rechte Einschaltseite</t>
+          <t>Seite ggü. Inhalt / red. Info</t>
         </is>
       </c>
       <c r="H1591" t="inlineStr">
@@ -72515,7 +72595,7 @@
       </c>
       <c r="E1592" t="inlineStr">
         <is>
-          <t>7. rechte Einschaltseite</t>
+          <t>Seite ggü. Hrsg. 1</t>
         </is>
       </c>
       <c r="H1592" t="inlineStr">
@@ -72553,7 +72633,7 @@
       </c>
       <c r="E1593" t="inlineStr">
         <is>
-          <t>8. rechte Einschaltseite</t>
+          <t>Seite ggü. Hrsg. 2</t>
         </is>
       </c>
       <c r="H1593" t="inlineStr">
@@ -72591,7 +72671,7 @@
       </c>
       <c r="E1594" t="inlineStr">
         <is>
-          <t>9. rechte Einschaltseite</t>
+          <t>Seite ggü. Textanfang</t>
         </is>
       </c>
       <c r="H1594" t="inlineStr">
@@ -72629,7 +72709,7 @@
       </c>
       <c r="E1595" t="inlineStr">
         <is>
-          <t>10. rechte Einschaltseite</t>
+          <t>1/1 Seite Festplatzierung</t>
         </is>
       </c>
       <c r="H1595" t="inlineStr">
@@ -72662,12 +72742,12 @@
       </c>
       <c r="D1596" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1596" t="inlineStr">
         <is>
-          <t>EH/DH 1 Seite</t>
+          <t>1. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1596" t="inlineStr">
@@ -72700,12 +72780,12 @@
       </c>
       <c r="D1597" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1597" t="inlineStr">
         <is>
-          <t>EH/DH 2 Seiten</t>
+          <t>2. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1597" t="inlineStr">
@@ -72738,12 +72818,12 @@
       </c>
       <c r="D1598" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1598" t="inlineStr">
         <is>
-          <t>EH/DH 4 Seiten</t>
+          <t>3. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1598" t="inlineStr">
@@ -72776,12 +72856,12 @@
       </c>
       <c r="D1599" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1599" t="inlineStr">
         <is>
-          <t>V-Koop MWO/Wefra</t>
+          <t>4. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1599" t="inlineStr">
@@ -72814,12 +72894,12 @@
       </c>
       <c r="D1600" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1600" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (pro 1.000)</t>
+          <t>5. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1600" t="inlineStr">
@@ -72852,12 +72932,12 @@
       </c>
       <c r="D1601" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1601" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (gesamt)</t>
+          <t>6. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1601" t="inlineStr">
@@ -72890,12 +72970,12 @@
       </c>
       <c r="D1602" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1602" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 50g (gesamt)</t>
+          <t>7. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1602" t="inlineStr">
@@ -72928,12 +73008,12 @@
       </c>
       <c r="D1603" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1603" t="inlineStr">
         <is>
-          <t>Titelseitenklappe</t>
+          <t>8. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1603" t="inlineStr">
@@ -72966,12 +73046,12 @@
       </c>
       <c r="D1604" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1604" t="inlineStr">
         <is>
-          <t>French Cover</t>
+          <t>9. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1604" t="inlineStr">
@@ -73004,12 +73084,12 @@
       </c>
       <c r="D1605" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1605" t="inlineStr">
         <is>
-          <t>ausklappbare 2. US</t>
+          <t>10. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1605" t="inlineStr">
@@ -73042,12 +73122,12 @@
       </c>
       <c r="D1606" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1606" t="inlineStr">
         <is>
-          <t>1/2 ausklappbare 2. US</t>
+          <t>EH/DH 1 Seite</t>
         </is>
       </c>
       <c r="H1606" t="inlineStr">
@@ -73080,12 +73160,12 @@
       </c>
       <c r="D1607" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1607" t="inlineStr">
         <is>
-          <t>Banderole (umlaufend)</t>
+          <t>EH/DH 2 Seiten</t>
         </is>
       </c>
       <c r="H1607" t="inlineStr">
@@ -73118,12 +73198,12 @@
       </c>
       <c r="D1608" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1608" t="inlineStr">
         <is>
-          <t>Sogbanderole</t>
+          <t>EH/DH 4 Seiten</t>
         </is>
       </c>
       <c r="H1608" t="inlineStr">
@@ -73156,12 +73236,12 @@
       </c>
       <c r="D1609" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1609" t="inlineStr">
         <is>
-          <t>Zangenbanderole</t>
+          <t>V-Koop MWO/Wefra</t>
         </is>
       </c>
       <c r="H1609" t="inlineStr">
@@ -73194,12 +73274,12 @@
       </c>
       <c r="D1610" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1610" t="inlineStr">
         <is>
-          <t>Pfeilbanderole</t>
+          <t>Werbebeilage bis 25g (pro 1.000)</t>
         </is>
       </c>
       <c r="H1610" t="inlineStr">
@@ -73232,12 +73312,12 @@
       </c>
       <c r="D1611" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1611" t="inlineStr">
         <is>
-          <t>Oversize-Beilage</t>
+          <t>Werbebeilage bis 25g (gesamt)</t>
         </is>
       </c>
       <c r="H1611" t="inlineStr">
@@ -73270,12 +73350,12 @@
       </c>
       <c r="D1612" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1612" t="inlineStr">
         <is>
-          <t>Lesezeichen (unbestimmte Stelle)</t>
+          <t>Werbebeilage bis 50g (gesamt)</t>
         </is>
       </c>
       <c r="H1612" t="inlineStr">
@@ -73313,7 +73393,7 @@
       </c>
       <c r="E1613" t="inlineStr">
         <is>
-          <t>Lesezeichen (bestimmte Stelle)</t>
+          <t>Titelseitenklappe</t>
         </is>
       </c>
       <c r="H1613" t="inlineStr">
@@ -73346,12 +73426,12 @@
       </c>
       <c r="D1614" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1614" t="inlineStr">
         <is>
-          <t>Klappohr-Einhefter</t>
+          <t>French Cover</t>
         </is>
       </c>
       <c r="H1614" t="inlineStr">
@@ -73384,12 +73464,12 @@
       </c>
       <c r="D1615" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1615" t="inlineStr">
         <is>
-          <t>gestanzter Einhefter</t>
+          <t>ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1615" t="inlineStr">
@@ -73422,12 +73502,12 @@
       </c>
       <c r="D1616" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1616" t="inlineStr">
         <is>
-          <t>perforierter Einhefter</t>
+          <t>1/2 ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1616" t="inlineStr">
@@ -73460,12 +73540,12 @@
       </c>
       <c r="D1617" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1617" t="inlineStr">
         <is>
-          <t>Einhefter mit Klappe</t>
+          <t>Banderole (umlaufend)</t>
         </is>
       </c>
       <c r="H1617" t="inlineStr">
@@ -73498,12 +73578,12 @@
       </c>
       <c r="D1618" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1618" t="inlineStr">
         <is>
-          <t>Flip-Einhefter</t>
+          <t>Sogbanderole</t>
         </is>
       </c>
       <c r="H1618" t="inlineStr">
@@ -73528,20 +73608,20 @@
       </c>
       <c r="B1619" t="inlineStr">
         <is>
-          <t>best practice onkologie</t>
+          <t>Die Onkologie</t>
         </is>
       </c>
       <c r="C1619" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="D1619" t="inlineStr">
         <is>
-          <t>Normalplatzierungen (4c inkl.)</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1619" t="inlineStr">
         <is>
-          <t>1/1 Seite 4c</t>
+          <t>Zangenbanderole</t>
         </is>
       </c>
       <c r="H1619" t="inlineStr">
@@ -73566,20 +73646,20 @@
       </c>
       <c r="B1620" t="inlineStr">
         <is>
-          <t>best practice onkologie</t>
+          <t>Die Onkologie</t>
         </is>
       </c>
       <c r="C1620" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="D1620" t="inlineStr">
         <is>
-          <t>Normalplatzierungen (4c inkl.)</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1620" t="inlineStr">
         <is>
-          <t>1/2 Seite 4c</t>
+          <t>Pfeilbanderole</t>
         </is>
       </c>
       <c r="H1620" t="inlineStr">
@@ -73604,20 +73684,20 @@
       </c>
       <c r="B1621" t="inlineStr">
         <is>
-          <t>best practice onkologie</t>
+          <t>Die Onkologie</t>
         </is>
       </c>
       <c r="C1621" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="D1621" t="inlineStr">
         <is>
-          <t>Normalplatzierungen (4c inkl.)</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1621" t="inlineStr">
         <is>
-          <t>1/3 Seite 4c</t>
+          <t>Oversize-Beilage</t>
         </is>
       </c>
       <c r="H1621" t="inlineStr">
@@ -73642,20 +73722,20 @@
       </c>
       <c r="B1622" t="inlineStr">
         <is>
-          <t>best practice onkologie</t>
+          <t>Die Onkologie</t>
         </is>
       </c>
       <c r="C1622" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="D1622" t="inlineStr">
         <is>
-          <t>Normalplatzierungen (4c inkl.)</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1622" t="inlineStr">
         <is>
-          <t>1/4 Seite 4c</t>
+          <t>Lesezeichen (unbestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1622" t="inlineStr">
@@ -73680,20 +73760,20 @@
       </c>
       <c r="B1623" t="inlineStr">
         <is>
-          <t>best practice onkologie</t>
+          <t>Die Onkologie</t>
         </is>
       </c>
       <c r="C1623" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="D1623" t="inlineStr">
         <is>
-          <t>Normalplatzierungen (4c inkl.)</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1623" t="inlineStr">
         <is>
-          <t>2/1 Doppelseite</t>
+          <t>Lesezeichen (bestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1623" t="inlineStr">
@@ -73718,20 +73798,20 @@
       </c>
       <c r="B1624" t="inlineStr">
         <is>
-          <t>best practice onkologie</t>
+          <t>Die Onkologie</t>
         </is>
       </c>
       <c r="C1624" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="D1624" t="inlineStr">
         <is>
-          <t>Normalplatzierungen (4c inkl.)</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1624" t="inlineStr">
         <is>
-          <t>Advertorial (1/1 Seite 4c)</t>
+          <t>Klappohr-Einhefter</t>
         </is>
       </c>
       <c r="H1624" t="inlineStr">
@@ -73756,20 +73836,20 @@
       </c>
       <c r="B1625" t="inlineStr">
         <is>
-          <t>best practice onkologie</t>
+          <t>Die Onkologie</t>
         </is>
       </c>
       <c r="C1625" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="D1625" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen (4c inkl.)</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1625" t="inlineStr">
         <is>
-          <t>4. Umschlagseite</t>
+          <t>gestanzter Einhefter</t>
         </is>
       </c>
       <c r="H1625" t="inlineStr">
@@ -73794,20 +73874,20 @@
       </c>
       <c r="B1626" t="inlineStr">
         <is>
-          <t>best practice onkologie</t>
+          <t>Die Onkologie</t>
         </is>
       </c>
       <c r="C1626" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="D1626" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen (4c inkl.)</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1626" t="inlineStr">
         <is>
-          <t>2. Umschlagseite</t>
+          <t>perforierter Einhefter</t>
         </is>
       </c>
       <c r="H1626" t="inlineStr">
@@ -73832,20 +73912,20 @@
       </c>
       <c r="B1627" t="inlineStr">
         <is>
-          <t>best practice onkologie</t>
+          <t>Die Onkologie</t>
         </is>
       </c>
       <c r="C1627" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="D1627" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen (4c inkl.)</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1627" t="inlineStr">
         <is>
-          <t>Seite ggü. red. Info / Inhalt</t>
+          <t>Einhefter mit Klappe</t>
         </is>
       </c>
       <c r="H1627" t="inlineStr">
@@ -73870,20 +73950,20 @@
       </c>
       <c r="B1628" t="inlineStr">
         <is>
-          <t>best practice onkologie</t>
+          <t>Die Onkologie</t>
         </is>
       </c>
       <c r="C1628" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="D1628" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen (4c inkl.)</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1628" t="inlineStr">
         <is>
-          <t>Seite ggü. Hrsg.</t>
+          <t>Flip-Einhefter</t>
         </is>
       </c>
       <c r="H1628" t="inlineStr">
@@ -73916,12 +73996,12 @@
       </c>
       <c r="D1629" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen (4c inkl.)</t>
+          <t>Normalplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1629" t="inlineStr">
         <is>
-          <t>Seite ggü. Editorial</t>
+          <t>1/1 Seite 4c</t>
         </is>
       </c>
       <c r="H1629" t="inlineStr">
@@ -73954,12 +74034,12 @@
       </c>
       <c r="D1630" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen (4c inkl.)</t>
+          <t>Normalplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1630" t="inlineStr">
         <is>
-          <t>Seite ggü. Textanfang</t>
+          <t>1/2 Seite 4c</t>
         </is>
       </c>
       <c r="H1630" t="inlineStr">
@@ -73992,12 +74072,12 @@
       </c>
       <c r="D1631" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen (4c inkl.)</t>
+          <t>Normalplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1631" t="inlineStr">
         <is>
-          <t>1/1 Seite 4c Festplatzierung</t>
+          <t>1/3 Seite 4c</t>
         </is>
       </c>
       <c r="H1631" t="inlineStr">
@@ -74030,12 +74110,12 @@
       </c>
       <c r="D1632" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen (4c inkl.)</t>
+          <t>Normalplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1632" t="inlineStr">
         <is>
-          <t>1. rechte Einschaltseite</t>
+          <t>1/4 Seite 4c</t>
         </is>
       </c>
       <c r="H1632" t="inlineStr">
@@ -74068,12 +74148,12 @@
       </c>
       <c r="D1633" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen (4c inkl.)</t>
+          <t>Normalplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1633" t="inlineStr">
         <is>
-          <t>2. rechte Einschaltseite</t>
+          <t>2/1 Doppelseite</t>
         </is>
       </c>
       <c r="H1633" t="inlineStr">
@@ -74106,12 +74186,12 @@
       </c>
       <c r="D1634" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen (4c inkl.)</t>
+          <t>Normalplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1634" t="inlineStr">
         <is>
-          <t>3. rechte Einschaltseite</t>
+          <t>Advertorial (1/1 Seite 4c)</t>
         </is>
       </c>
       <c r="H1634" t="inlineStr">
@@ -74149,7 +74229,7 @@
       </c>
       <c r="E1635" t="inlineStr">
         <is>
-          <t>4. rechte Einschaltseite</t>
+          <t>4. Umschlagseite</t>
         </is>
       </c>
       <c r="H1635" t="inlineStr">
@@ -74187,7 +74267,7 @@
       </c>
       <c r="E1636" t="inlineStr">
         <is>
-          <t>5. rechte Einschaltseite</t>
+          <t>2. Umschlagseite</t>
         </is>
       </c>
       <c r="H1636" t="inlineStr">
@@ -74225,7 +74305,7 @@
       </c>
       <c r="E1637" t="inlineStr">
         <is>
-          <t>6. rechte Einschaltseite</t>
+          <t>Seite ggü. red. Info / Inhalt</t>
         </is>
       </c>
       <c r="H1637" t="inlineStr">
@@ -74263,7 +74343,7 @@
       </c>
       <c r="E1638" t="inlineStr">
         <is>
-          <t>7. rechte Einschaltseite</t>
+          <t>Seite ggü. Hrsg.</t>
         </is>
       </c>
       <c r="H1638" t="inlineStr">
@@ -74301,7 +74381,7 @@
       </c>
       <c r="E1639" t="inlineStr">
         <is>
-          <t>8. rechte Einschaltseite</t>
+          <t>Seite ggü. Editorial</t>
         </is>
       </c>
       <c r="H1639" t="inlineStr">
@@ -74339,7 +74419,7 @@
       </c>
       <c r="E1640" t="inlineStr">
         <is>
-          <t>9. rechte Einschaltseite</t>
+          <t>Seite ggü. Textanfang</t>
         </is>
       </c>
       <c r="H1640" t="inlineStr">
@@ -74377,7 +74457,7 @@
       </c>
       <c r="E1641" t="inlineStr">
         <is>
-          <t>10. rechte Einschaltseite</t>
+          <t>1/1 Seite 4c Festplatzierung</t>
         </is>
       </c>
       <c r="H1641" t="inlineStr">
@@ -74410,12 +74490,12 @@
       </c>
       <c r="D1642" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1642" t="inlineStr">
         <is>
-          <t>EH/DH 1 Seite</t>
+          <t>1. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1642" t="inlineStr">
@@ -74448,12 +74528,12 @@
       </c>
       <c r="D1643" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1643" t="inlineStr">
         <is>
-          <t>EH/DH 2 Seiten</t>
+          <t>2. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1643" t="inlineStr">
@@ -74486,12 +74566,12 @@
       </c>
       <c r="D1644" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1644" t="inlineStr">
         <is>
-          <t>EH/DH 4 Seiten</t>
+          <t>3. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1644" t="inlineStr">
@@ -74524,12 +74604,12 @@
       </c>
       <c r="D1645" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1645" t="inlineStr">
         <is>
-          <t>V-Koop MWO/Wefra</t>
+          <t>4. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1645" t="inlineStr">
@@ -74562,12 +74642,12 @@
       </c>
       <c r="D1646" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Vorzugsplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1646" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (pro 1.000)</t>
+          <t>5. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1646" t="inlineStr">
@@ -74600,12 +74680,12 @@
       </c>
       <c r="D1647" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Vorzugsplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1647" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (gesamt)</t>
+          <t>6. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1647" t="inlineStr">
@@ -74638,12 +74718,12 @@
       </c>
       <c r="D1648" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Vorzugsplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1648" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 50g (gesamt)</t>
+          <t>7. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1648" t="inlineStr">
@@ -74676,12 +74756,12 @@
       </c>
       <c r="D1649" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Vorzugsplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1649" t="inlineStr">
         <is>
-          <t>Titelseitenklappe</t>
+          <t>8. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1649" t="inlineStr">
@@ -74714,12 +74794,12 @@
       </c>
       <c r="D1650" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Vorzugsplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1650" t="inlineStr">
         <is>
-          <t>French Cover</t>
+          <t>9. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1650" t="inlineStr">
@@ -74752,12 +74832,12 @@
       </c>
       <c r="D1651" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Vorzugsplatzierungen (4c inkl.)</t>
         </is>
       </c>
       <c r="E1651" t="inlineStr">
         <is>
-          <t>ausklappbare 2. US</t>
+          <t>10. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1651" t="inlineStr">
@@ -74790,12 +74870,12 @@
       </c>
       <c r="D1652" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1652" t="inlineStr">
         <is>
-          <t>1/2 ausklappbare 2. US</t>
+          <t>EH/DH 1 Seite</t>
         </is>
       </c>
       <c r="H1652" t="inlineStr">
@@ -74828,12 +74908,12 @@
       </c>
       <c r="D1653" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1653" t="inlineStr">
         <is>
-          <t>Banderole (umlaufend)</t>
+          <t>EH/DH 2 Seiten</t>
         </is>
       </c>
       <c r="H1653" t="inlineStr">
@@ -74866,12 +74946,12 @@
       </c>
       <c r="D1654" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1654" t="inlineStr">
         <is>
-          <t>Sogbanderole</t>
+          <t>EH/DH 4 Seiten</t>
         </is>
       </c>
       <c r="H1654" t="inlineStr">
@@ -74904,12 +74984,12 @@
       </c>
       <c r="D1655" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1655" t="inlineStr">
         <is>
-          <t>Zangenbanderole</t>
+          <t>V-Koop MWO/Wefra</t>
         </is>
       </c>
       <c r="H1655" t="inlineStr">
@@ -74942,12 +75022,12 @@
       </c>
       <c r="D1656" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1656" t="inlineStr">
         <is>
-          <t>Pfeilbanderole</t>
+          <t>Werbebeilage bis 25g (pro 1.000)</t>
         </is>
       </c>
       <c r="H1656" t="inlineStr">
@@ -74980,12 +75060,12 @@
       </c>
       <c r="D1657" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1657" t="inlineStr">
         <is>
-          <t>Oversize-Beilage</t>
+          <t>Werbebeilage bis 25g (gesamt)</t>
         </is>
       </c>
       <c r="H1657" t="inlineStr">
@@ -75018,12 +75098,12 @@
       </c>
       <c r="D1658" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1658" t="inlineStr">
         <is>
-          <t>Lesezeichen (unbestimmte Stelle)</t>
+          <t>Werbebeilage bis 50g (gesamt)</t>
         </is>
       </c>
       <c r="H1658" t="inlineStr">
@@ -75061,7 +75141,7 @@
       </c>
       <c r="E1659" t="inlineStr">
         <is>
-          <t>Lesezeichen (bestimmte Stelle)</t>
+          <t>Titelseitenklappe</t>
         </is>
       </c>
       <c r="H1659" t="inlineStr">
@@ -75099,7 +75179,7 @@
       </c>
       <c r="E1660" t="inlineStr">
         <is>
-          <t>Teaser-Anzeige im red. Text</t>
+          <t>French Cover</t>
         </is>
       </c>
       <c r="H1660" t="inlineStr">
@@ -75137,7 +75217,7 @@
       </c>
       <c r="E1661" t="inlineStr">
         <is>
-          <t>Griffecke im red. Text</t>
+          <t>ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1661" t="inlineStr">
@@ -75170,12 +75250,12 @@
       </c>
       <c r="D1662" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1662" t="inlineStr">
         <is>
-          <t>Klappohr-Einhefter</t>
+          <t>1/2 ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1662" t="inlineStr">
@@ -75208,12 +75288,12 @@
       </c>
       <c r="D1663" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1663" t="inlineStr">
         <is>
-          <t>gestanzter Einhefter</t>
+          <t>Banderole (umlaufend)</t>
         </is>
       </c>
       <c r="H1663" t="inlineStr">
@@ -75246,12 +75326,12 @@
       </c>
       <c r="D1664" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1664" t="inlineStr">
         <is>
-          <t>perforierter Einhefter</t>
+          <t>Sogbanderole</t>
         </is>
       </c>
       <c r="H1664" t="inlineStr">
@@ -75284,12 +75364,12 @@
       </c>
       <c r="D1665" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1665" t="inlineStr">
         <is>
-          <t>Einhefter mit Klappe</t>
+          <t>Zangenbanderole</t>
         </is>
       </c>
       <c r="H1665" t="inlineStr">
@@ -75322,12 +75402,12 @@
       </c>
       <c r="D1666" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1666" t="inlineStr">
         <is>
-          <t>Flip-Einhefter</t>
+          <t>Pfeilbanderole</t>
         </is>
       </c>
       <c r="H1666" t="inlineStr">
@@ -75352,20 +75432,20 @@
       </c>
       <c r="B1667" t="inlineStr">
         <is>
-          <t>FORUM DKG</t>
+          <t>best practice onkologie</t>
         </is>
       </c>
       <c r="C1667" t="n">
-        <v>8700</v>
+        <v>10000</v>
       </c>
       <c r="D1667" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1667" t="inlineStr">
         <is>
-          <t>1/1 Seite 4c</t>
+          <t>Oversize-Beilage</t>
         </is>
       </c>
       <c r="H1667" t="inlineStr">
@@ -75390,20 +75470,20 @@
       </c>
       <c r="B1668" t="inlineStr">
         <is>
-          <t>FORUM DKG</t>
+          <t>best practice onkologie</t>
         </is>
       </c>
       <c r="C1668" t="n">
-        <v>8700</v>
+        <v>10000</v>
       </c>
       <c r="D1668" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1668" t="inlineStr">
         <is>
-          <t>1/2 Seite 4c</t>
+          <t>Lesezeichen (unbestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1668" t="inlineStr">
@@ -75428,20 +75508,20 @@
       </c>
       <c r="B1669" t="inlineStr">
         <is>
-          <t>FORUM DKG</t>
+          <t>best practice onkologie</t>
         </is>
       </c>
       <c r="C1669" t="n">
-        <v>8700</v>
+        <v>10000</v>
       </c>
       <c r="D1669" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1669" t="inlineStr">
         <is>
-          <t>1/3 Seite 4c</t>
+          <t>Lesezeichen (bestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1669" t="inlineStr">
@@ -75466,20 +75546,20 @@
       </c>
       <c r="B1670" t="inlineStr">
         <is>
-          <t>FORUM DKG</t>
+          <t>best practice onkologie</t>
         </is>
       </c>
       <c r="C1670" t="n">
-        <v>8700</v>
+        <v>10000</v>
       </c>
       <c r="D1670" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1670" t="inlineStr">
         <is>
-          <t>1/4 Seite 4c</t>
+          <t>Teaser-Anzeige im red. Text</t>
         </is>
       </c>
       <c r="H1670" t="inlineStr">
@@ -75504,20 +75584,20 @@
       </c>
       <c r="B1671" t="inlineStr">
         <is>
-          <t>FORUM DKG</t>
+          <t>best practice onkologie</t>
         </is>
       </c>
       <c r="C1671" t="n">
-        <v>8700</v>
+        <v>10000</v>
       </c>
       <c r="D1671" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1671" t="inlineStr">
         <is>
-          <t>2/1 Doppelseite</t>
+          <t>Griffecke im red. Text</t>
         </is>
       </c>
       <c r="H1671" t="inlineStr">
@@ -75542,20 +75622,20 @@
       </c>
       <c r="B1672" t="inlineStr">
         <is>
-          <t>FORUM DKG</t>
+          <t>best practice onkologie</t>
         </is>
       </c>
       <c r="C1672" t="n">
-        <v>8700</v>
+        <v>10000</v>
       </c>
       <c r="D1672" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1672" t="inlineStr">
         <is>
-          <t>Advertorial (1/1 Seite 4c)</t>
+          <t>Klappohr-Einhefter</t>
         </is>
       </c>
       <c r="H1672" t="inlineStr">
@@ -75580,20 +75660,20 @@
       </c>
       <c r="B1673" t="inlineStr">
         <is>
-          <t>FORUM DKG</t>
+          <t>best practice onkologie</t>
         </is>
       </c>
       <c r="C1673" t="n">
-        <v>8700</v>
+        <v>10000</v>
       </c>
       <c r="D1673" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1673" t="inlineStr">
         <is>
-          <t>4. Umschlagseite</t>
+          <t>gestanzter Einhefter</t>
         </is>
       </c>
       <c r="H1673" t="inlineStr">
@@ -75618,20 +75698,20 @@
       </c>
       <c r="B1674" t="inlineStr">
         <is>
-          <t>FORUM DKG</t>
+          <t>best practice onkologie</t>
         </is>
       </c>
       <c r="C1674" t="n">
-        <v>8700</v>
+        <v>10000</v>
       </c>
       <c r="D1674" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1674" t="inlineStr">
         <is>
-          <t>2. Umschlagseite</t>
+          <t>perforierter Einhefter</t>
         </is>
       </c>
       <c r="H1674" t="inlineStr">
@@ -75656,20 +75736,20 @@
       </c>
       <c r="B1675" t="inlineStr">
         <is>
-          <t>FORUM DKG</t>
+          <t>best practice onkologie</t>
         </is>
       </c>
       <c r="C1675" t="n">
-        <v>8700</v>
+        <v>10000</v>
       </c>
       <c r="D1675" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1675" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 1</t>
+          <t>Einhefter mit Klappe</t>
         </is>
       </c>
       <c r="H1675" t="inlineStr">
@@ -75694,20 +75774,20 @@
       </c>
       <c r="B1676" t="inlineStr">
         <is>
-          <t>FORUM DKG</t>
+          <t>best practice onkologie</t>
         </is>
       </c>
       <c r="C1676" t="n">
-        <v>8700</v>
+        <v>10000</v>
       </c>
       <c r="D1676" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1676" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 2</t>
+          <t>Flip-Einhefter</t>
         </is>
       </c>
       <c r="H1676" t="inlineStr">
@@ -75740,12 +75820,12 @@
       </c>
       <c r="D1677" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1677" t="inlineStr">
         <is>
-          <t>Seite ggü. Editorial 2</t>
+          <t>1/1 Seite 4c</t>
         </is>
       </c>
       <c r="H1677" t="inlineStr">
@@ -75778,12 +75858,12 @@
       </c>
       <c r="D1678" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1678" t="inlineStr">
         <is>
-          <t>Seite ggü. Textanfang</t>
+          <t>1/2 Seite 4c</t>
         </is>
       </c>
       <c r="H1678" t="inlineStr">
@@ -75816,12 +75896,12 @@
       </c>
       <c r="D1679" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1679" t="inlineStr">
         <is>
-          <t>1/1 Seite 4c Festplatzierung</t>
+          <t>1/3 Seite 4c</t>
         </is>
       </c>
       <c r="H1679" t="inlineStr">
@@ -75854,12 +75934,12 @@
       </c>
       <c r="D1680" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1680" t="inlineStr">
         <is>
-          <t>1. rechte Einschaltseite</t>
+          <t>1/4 Seite 4c</t>
         </is>
       </c>
       <c r="H1680" t="inlineStr">
@@ -75892,12 +75972,12 @@
       </c>
       <c r="D1681" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1681" t="inlineStr">
         <is>
-          <t>2. rechte Einschaltseite</t>
+          <t>2/1 Doppelseite</t>
         </is>
       </c>
       <c r="H1681" t="inlineStr">
@@ -75930,12 +76010,12 @@
       </c>
       <c r="D1682" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1682" t="inlineStr">
         <is>
-          <t>3. rechte Einschaltseite</t>
+          <t>Advertorial (1/1 Seite 4c)</t>
         </is>
       </c>
       <c r="H1682" t="inlineStr">
@@ -75973,7 +76053,7 @@
       </c>
       <c r="E1683" t="inlineStr">
         <is>
-          <t>4. rechte Einschaltseite</t>
+          <t>4. Umschlagseite</t>
         </is>
       </c>
       <c r="H1683" t="inlineStr">
@@ -76011,7 +76091,7 @@
       </c>
       <c r="E1684" t="inlineStr">
         <is>
-          <t>5. rechte Einschaltseite</t>
+          <t>2. Umschlagseite</t>
         </is>
       </c>
       <c r="H1684" t="inlineStr">
@@ -76049,7 +76129,7 @@
       </c>
       <c r="E1685" t="inlineStr">
         <is>
-          <t>6. rechte Einschaltseite</t>
+          <t>Seite ggü. Inhalt 1</t>
         </is>
       </c>
       <c r="H1685" t="inlineStr">
@@ -76087,7 +76167,7 @@
       </c>
       <c r="E1686" t="inlineStr">
         <is>
-          <t>7. rechte Einschaltseite</t>
+          <t>Seite ggü. Inhalt 2</t>
         </is>
       </c>
       <c r="H1686" t="inlineStr">
@@ -76125,7 +76205,7 @@
       </c>
       <c r="E1687" t="inlineStr">
         <is>
-          <t>8. rechte Einschaltseite</t>
+          <t>Seite ggü. Editorial 2</t>
         </is>
       </c>
       <c r="H1687" t="inlineStr">
@@ -76163,7 +76243,7 @@
       </c>
       <c r="E1688" t="inlineStr">
         <is>
-          <t>9. rechte Einschaltseite</t>
+          <t>Seite ggü. Textanfang</t>
         </is>
       </c>
       <c r="H1688" t="inlineStr">
@@ -76201,7 +76281,7 @@
       </c>
       <c r="E1689" t="inlineStr">
         <is>
-          <t>10. rechte Einschaltseite</t>
+          <t>1/1 Seite 4c Festplatzierung</t>
         </is>
       </c>
       <c r="H1689" t="inlineStr">
@@ -76234,12 +76314,12 @@
       </c>
       <c r="D1690" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1690" t="inlineStr">
         <is>
-          <t>EH/DH 1 Seite</t>
+          <t>1. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1690" t="inlineStr">
@@ -76272,12 +76352,12 @@
       </c>
       <c r="D1691" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1691" t="inlineStr">
         <is>
-          <t>EH/DH 2 Seiten</t>
+          <t>2. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1691" t="inlineStr">
@@ -76310,12 +76390,12 @@
       </c>
       <c r="D1692" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1692" t="inlineStr">
         <is>
-          <t>EH/DH 4 Seiten</t>
+          <t>3. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1692" t="inlineStr">
@@ -76348,12 +76428,12 @@
       </c>
       <c r="D1693" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1693" t="inlineStr">
         <is>
-          <t>V-Koop MWO/Wefra</t>
+          <t>4. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1693" t="inlineStr">
@@ -76386,12 +76466,12 @@
       </c>
       <c r="D1694" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1694" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (pro 1.000)</t>
+          <t>5. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1694" t="inlineStr">
@@ -76424,12 +76504,12 @@
       </c>
       <c r="D1695" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1695" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (gesamt)</t>
+          <t>6. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1695" t="inlineStr">
@@ -76462,12 +76542,12 @@
       </c>
       <c r="D1696" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1696" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 50g (gesamt)</t>
+          <t>7. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1696" t="inlineStr">
@@ -76500,12 +76580,12 @@
       </c>
       <c r="D1697" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1697" t="inlineStr">
         <is>
-          <t>Titelseitenklappe</t>
+          <t>8. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1697" t="inlineStr">
@@ -76538,12 +76618,12 @@
       </c>
       <c r="D1698" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1698" t="inlineStr">
         <is>
-          <t>French Cover</t>
+          <t>9. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1698" t="inlineStr">
@@ -76576,12 +76656,12 @@
       </c>
       <c r="D1699" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1699" t="inlineStr">
         <is>
-          <t>ausklappbare 2. US</t>
+          <t>10. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1699" t="inlineStr">
@@ -76614,12 +76694,12 @@
       </c>
       <c r="D1700" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1700" t="inlineStr">
         <is>
-          <t>1/2 ausklappbare 2. US</t>
+          <t>EH/DH 1 Seite</t>
         </is>
       </c>
       <c r="H1700" t="inlineStr">
@@ -76652,12 +76732,12 @@
       </c>
       <c r="D1701" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1701" t="inlineStr">
         <is>
-          <t>Banderole (umlaufend)</t>
+          <t>EH/DH 2 Seiten</t>
         </is>
       </c>
       <c r="H1701" t="inlineStr">
@@ -76690,12 +76770,12 @@
       </c>
       <c r="D1702" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1702" t="inlineStr">
         <is>
-          <t>Sogbanderole</t>
+          <t>EH/DH 4 Seiten</t>
         </is>
       </c>
       <c r="H1702" t="inlineStr">
@@ -76728,12 +76808,12 @@
       </c>
       <c r="D1703" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1703" t="inlineStr">
         <is>
-          <t>Zangenbanderole</t>
+          <t>V-Koop MWO/Wefra</t>
         </is>
       </c>
       <c r="H1703" t="inlineStr">
@@ -76766,12 +76846,12 @@
       </c>
       <c r="D1704" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1704" t="inlineStr">
         <is>
-          <t>Pfeilbanderole</t>
+          <t>Werbebeilage bis 25g (pro 1.000)</t>
         </is>
       </c>
       <c r="H1704" t="inlineStr">
@@ -76804,12 +76884,12 @@
       </c>
       <c r="D1705" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1705" t="inlineStr">
         <is>
-          <t>Oversize-Beilage</t>
+          <t>Werbebeilage bis 25g (gesamt)</t>
         </is>
       </c>
       <c r="H1705" t="inlineStr">
@@ -76842,12 +76922,12 @@
       </c>
       <c r="D1706" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1706" t="inlineStr">
         <is>
-          <t>Lesezeichen (unbestimmte Stelle)</t>
+          <t>Werbebeilage bis 50g (gesamt)</t>
         </is>
       </c>
       <c r="H1706" t="inlineStr">
@@ -76885,7 +76965,7 @@
       </c>
       <c r="E1707" t="inlineStr">
         <is>
-          <t>Lesezeichen (bestimmte Stelle)</t>
+          <t>Titelseitenklappe</t>
         </is>
       </c>
       <c r="H1707" t="inlineStr">
@@ -76923,7 +77003,7 @@
       </c>
       <c r="E1708" t="inlineStr">
         <is>
-          <t>Teaser-Anzeige im red. Text</t>
+          <t>French Cover</t>
         </is>
       </c>
       <c r="H1708" t="inlineStr">
@@ -76961,7 +77041,7 @@
       </c>
       <c r="E1709" t="inlineStr">
         <is>
-          <t>Griffecke im red. Text</t>
+          <t>ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1709" t="inlineStr">
@@ -76994,12 +77074,12 @@
       </c>
       <c r="D1710" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1710" t="inlineStr">
         <is>
-          <t>Klappohr-Einhefter</t>
+          <t>1/2 ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1710" t="inlineStr">
@@ -77032,12 +77112,12 @@
       </c>
       <c r="D1711" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1711" t="inlineStr">
         <is>
-          <t>gestanzter Einhefter</t>
+          <t>Banderole (umlaufend)</t>
         </is>
       </c>
       <c r="H1711" t="inlineStr">
@@ -77070,12 +77150,12 @@
       </c>
       <c r="D1712" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1712" t="inlineStr">
         <is>
-          <t>Einhefter mit Klappe</t>
+          <t>Sogbanderole</t>
         </is>
       </c>
       <c r="H1712" t="inlineStr">
@@ -77108,12 +77188,12 @@
       </c>
       <c r="D1713" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1713" t="inlineStr">
         <is>
-          <t>Flip-Einhefter</t>
+          <t>Zangenbanderole</t>
         </is>
       </c>
       <c r="H1713" t="inlineStr">
@@ -77138,20 +77218,20 @@
       </c>
       <c r="B1714" t="inlineStr">
         <is>
-          <t>Im Fokus Onkologie</t>
+          <t>FORUM DKG</t>
         </is>
       </c>
       <c r="C1714" t="n">
-        <v>8000</v>
+        <v>8700</v>
       </c>
       <c r="D1714" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1714" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
+          <t>Pfeilbanderole</t>
         </is>
       </c>
       <c r="H1714" t="inlineStr">
@@ -77176,20 +77256,20 @@
       </c>
       <c r="B1715" t="inlineStr">
         <is>
-          <t>Im Fokus Onkologie</t>
+          <t>FORUM DKG</t>
         </is>
       </c>
       <c r="C1715" t="n">
-        <v>8000</v>
+        <v>8700</v>
       </c>
       <c r="D1715" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1715" t="inlineStr">
         <is>
-          <t>1/2 Seite</t>
+          <t>Oversize-Beilage</t>
         </is>
       </c>
       <c r="H1715" t="inlineStr">
@@ -77214,20 +77294,20 @@
       </c>
       <c r="B1716" t="inlineStr">
         <is>
-          <t>Im Fokus Onkologie</t>
+          <t>FORUM DKG</t>
         </is>
       </c>
       <c r="C1716" t="n">
-        <v>8000</v>
+        <v>8700</v>
       </c>
       <c r="D1716" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1716" t="inlineStr">
         <is>
-          <t>1/3 Seite</t>
+          <t>Lesezeichen (unbestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1716" t="inlineStr">
@@ -77252,20 +77332,20 @@
       </c>
       <c r="B1717" t="inlineStr">
         <is>
-          <t>Im Fokus Onkologie</t>
+          <t>FORUM DKG</t>
         </is>
       </c>
       <c r="C1717" t="n">
-        <v>8000</v>
+        <v>8700</v>
       </c>
       <c r="D1717" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1717" t="inlineStr">
         <is>
-          <t>1/4 Seite</t>
+          <t>Lesezeichen (bestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1717" t="inlineStr">
@@ -77290,20 +77370,20 @@
       </c>
       <c r="B1718" t="inlineStr">
         <is>
-          <t>Im Fokus Onkologie</t>
+          <t>FORUM DKG</t>
         </is>
       </c>
       <c r="C1718" t="n">
-        <v>8000</v>
+        <v>8700</v>
       </c>
       <c r="D1718" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1718" t="inlineStr">
         <is>
-          <t>2/1 Doppelseite</t>
+          <t>Teaser-Anzeige im red. Text</t>
         </is>
       </c>
       <c r="H1718" t="inlineStr">
@@ -77328,20 +77408,20 @@
       </c>
       <c r="B1719" t="inlineStr">
         <is>
-          <t>Im Fokus Onkologie</t>
+          <t>FORUM DKG</t>
         </is>
       </c>
       <c r="C1719" t="n">
-        <v>8000</v>
+        <v>8700</v>
       </c>
       <c r="D1719" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1719" t="inlineStr">
         <is>
-          <t>Advertorial (1/1 Seite)</t>
+          <t>Griffecke im red. Text</t>
         </is>
       </c>
       <c r="H1719" t="inlineStr">
@@ -77366,20 +77446,20 @@
       </c>
       <c r="B1720" t="inlineStr">
         <is>
-          <t>Im Fokus Onkologie</t>
+          <t>FORUM DKG</t>
         </is>
       </c>
       <c r="C1720" t="n">
-        <v>8000</v>
+        <v>8700</v>
       </c>
       <c r="D1720" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1720" t="inlineStr">
         <is>
-          <t>4. Umschlagseite</t>
+          <t>Klappohr-Einhefter</t>
         </is>
       </c>
       <c r="H1720" t="inlineStr">
@@ -77404,20 +77484,20 @@
       </c>
       <c r="B1721" t="inlineStr">
         <is>
-          <t>Im Fokus Onkologie</t>
+          <t>FORUM DKG</t>
         </is>
       </c>
       <c r="C1721" t="n">
-        <v>8000</v>
+        <v>8700</v>
       </c>
       <c r="D1721" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1721" t="inlineStr">
         <is>
-          <t>2. Umschlagseite</t>
+          <t>gestanzter Einhefter</t>
         </is>
       </c>
       <c r="H1721" t="inlineStr">
@@ -77442,20 +77522,20 @@
       </c>
       <c r="B1722" t="inlineStr">
         <is>
-          <t>Im Fokus Onkologie</t>
+          <t>FORUM DKG</t>
         </is>
       </c>
       <c r="C1722" t="n">
-        <v>8000</v>
+        <v>8700</v>
       </c>
       <c r="D1722" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1722" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 1</t>
+          <t>Einhefter mit Klappe</t>
         </is>
       </c>
       <c r="H1722" t="inlineStr">
@@ -77480,20 +77560,20 @@
       </c>
       <c r="B1723" t="inlineStr">
         <is>
-          <t>Im Fokus Onkologie</t>
+          <t>FORUM DKG</t>
         </is>
       </c>
       <c r="C1723" t="n">
-        <v>8000</v>
+        <v>8700</v>
       </c>
       <c r="D1723" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1723" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 2</t>
+          <t>Flip-Einhefter</t>
         </is>
       </c>
       <c r="H1723" t="inlineStr">
@@ -77526,12 +77606,12 @@
       </c>
       <c r="D1724" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1724" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 3</t>
+          <t>1/1 Seite</t>
         </is>
       </c>
       <c r="H1724" t="inlineStr">
@@ -77564,12 +77644,12 @@
       </c>
       <c r="D1725" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1725" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 4</t>
+          <t>1/2 Seite</t>
         </is>
       </c>
       <c r="H1725" t="inlineStr">
@@ -77602,12 +77682,12 @@
       </c>
       <c r="D1726" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1726" t="inlineStr">
         <is>
-          <t>Seite ggü. Textanfang</t>
+          <t>1/3 Seite</t>
         </is>
       </c>
       <c r="H1726" t="inlineStr">
@@ -77640,12 +77720,12 @@
       </c>
       <c r="D1727" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1727" t="inlineStr">
         <is>
-          <t>1/1 Seite Festplatzierung</t>
+          <t>1/4 Seite</t>
         </is>
       </c>
       <c r="H1727" t="inlineStr">
@@ -77678,12 +77758,12 @@
       </c>
       <c r="D1728" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1728" t="inlineStr">
         <is>
-          <t>1. rechte Einschaltseite</t>
+          <t>2/1 Doppelseite</t>
         </is>
       </c>
       <c r="H1728" t="inlineStr">
@@ -77716,12 +77796,12 @@
       </c>
       <c r="D1729" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1729" t="inlineStr">
         <is>
-          <t>2. rechte Einschaltseite</t>
+          <t>Advertorial (1/1 Seite)</t>
         </is>
       </c>
       <c r="H1729" t="inlineStr">
@@ -77759,7 +77839,7 @@
       </c>
       <c r="E1730" t="inlineStr">
         <is>
-          <t>3. rechte Einschaltseite</t>
+          <t>4. Umschlagseite</t>
         </is>
       </c>
       <c r="H1730" t="inlineStr">
@@ -77797,7 +77877,7 @@
       </c>
       <c r="E1731" t="inlineStr">
         <is>
-          <t>4. rechte Einschaltseite</t>
+          <t>2. Umschlagseite</t>
         </is>
       </c>
       <c r="H1731" t="inlineStr">
@@ -77835,7 +77915,7 @@
       </c>
       <c r="E1732" t="inlineStr">
         <is>
-          <t>5. rechte Einschaltseite</t>
+          <t>Seite ggü. Inhalt 1</t>
         </is>
       </c>
       <c r="H1732" t="inlineStr">
@@ -77873,7 +77953,7 @@
       </c>
       <c r="E1733" t="inlineStr">
         <is>
-          <t>6. rechte Einschaltseite</t>
+          <t>Seite ggü. Inhalt 2</t>
         </is>
       </c>
       <c r="H1733" t="inlineStr">
@@ -77911,7 +77991,7 @@
       </c>
       <c r="E1734" t="inlineStr">
         <is>
-          <t>7. rechte Einschaltseite</t>
+          <t>Seite ggü. Inhalt 3</t>
         </is>
       </c>
       <c r="H1734" t="inlineStr">
@@ -77949,7 +78029,7 @@
       </c>
       <c r="E1735" t="inlineStr">
         <is>
-          <t>8. rechte Einschaltseite</t>
+          <t>Seite ggü. Inhalt 4</t>
         </is>
       </c>
       <c r="H1735" t="inlineStr">
@@ -77987,7 +78067,7 @@
       </c>
       <c r="E1736" t="inlineStr">
         <is>
-          <t>9. rechte Einschaltseite</t>
+          <t>Seite ggü. Textanfang</t>
         </is>
       </c>
       <c r="H1736" t="inlineStr">
@@ -78025,7 +78105,7 @@
       </c>
       <c r="E1737" t="inlineStr">
         <is>
-          <t>10. rechte Einschaltseite</t>
+          <t>1/1 Seite Festplatzierung</t>
         </is>
       </c>
       <c r="H1737" t="inlineStr">
@@ -78058,12 +78138,12 @@
       </c>
       <c r="D1738" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1738" t="inlineStr">
         <is>
-          <t>EH/DH 1 Seite</t>
+          <t>1. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1738" t="inlineStr">
@@ -78096,12 +78176,12 @@
       </c>
       <c r="D1739" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1739" t="inlineStr">
         <is>
-          <t>EH/DH 2 Seiten</t>
+          <t>2. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1739" t="inlineStr">
@@ -78134,12 +78214,12 @@
       </c>
       <c r="D1740" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1740" t="inlineStr">
         <is>
-          <t>EH/DH 4 Seiten</t>
+          <t>3. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1740" t="inlineStr">
@@ -78172,12 +78252,12 @@
       </c>
       <c r="D1741" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1741" t="inlineStr">
         <is>
-          <t>V-Koop MWO/Wefra</t>
+          <t>4. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1741" t="inlineStr">
@@ -78210,12 +78290,12 @@
       </c>
       <c r="D1742" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1742" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (pro 1.000)</t>
+          <t>5. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1742" t="inlineStr">
@@ -78248,12 +78328,12 @@
       </c>
       <c r="D1743" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1743" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (gesamt)</t>
+          <t>6. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1743" t="inlineStr">
@@ -78286,12 +78366,12 @@
       </c>
       <c r="D1744" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1744" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 50g (gesamt)</t>
+          <t>7. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1744" t="inlineStr">
@@ -78324,12 +78404,12 @@
       </c>
       <c r="D1745" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1745" t="inlineStr">
         <is>
-          <t>Titelseitenklappe</t>
+          <t>8. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1745" t="inlineStr">
@@ -78362,12 +78442,12 @@
       </c>
       <c r="D1746" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1746" t="inlineStr">
         <is>
-          <t>French Cover</t>
+          <t>9. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1746" t="inlineStr">
@@ -78400,12 +78480,12 @@
       </c>
       <c r="D1747" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1747" t="inlineStr">
         <is>
-          <t>ausklappbare 2. US</t>
+          <t>10. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1747" t="inlineStr">
@@ -78438,12 +78518,12 @@
       </c>
       <c r="D1748" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1748" t="inlineStr">
         <is>
-          <t>1/2 ausklappbare 2. US</t>
+          <t>EH/DH 1 Seite</t>
         </is>
       </c>
       <c r="H1748" t="inlineStr">
@@ -78476,12 +78556,12 @@
       </c>
       <c r="D1749" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1749" t="inlineStr">
         <is>
-          <t>Banderole (umlaufend)</t>
+          <t>EH/DH 2 Seiten</t>
         </is>
       </c>
       <c r="H1749" t="inlineStr">
@@ -78514,12 +78594,12 @@
       </c>
       <c r="D1750" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1750" t="inlineStr">
         <is>
-          <t>Sogbanderole</t>
+          <t>EH/DH 4 Seiten</t>
         </is>
       </c>
       <c r="H1750" t="inlineStr">
@@ -78552,12 +78632,12 @@
       </c>
       <c r="D1751" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1751" t="inlineStr">
         <is>
-          <t>Zangenbanderole</t>
+          <t>V-Koop MWO/Wefra</t>
         </is>
       </c>
       <c r="H1751" t="inlineStr">
@@ -78590,12 +78670,12 @@
       </c>
       <c r="D1752" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1752" t="inlineStr">
         <is>
-          <t>Pfeilbanderole</t>
+          <t>Werbebeilage bis 25g (pro 1.000)</t>
         </is>
       </c>
       <c r="H1752" t="inlineStr">
@@ -78628,12 +78708,12 @@
       </c>
       <c r="D1753" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1753" t="inlineStr">
         <is>
-          <t>Oversize-Beilage</t>
+          <t>Werbebeilage bis 25g (gesamt)</t>
         </is>
       </c>
       <c r="H1753" t="inlineStr">
@@ -78666,12 +78746,12 @@
       </c>
       <c r="D1754" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1754" t="inlineStr">
         <is>
-          <t>Lesezeichen (unbestimmte Stelle)</t>
+          <t>Werbebeilage bis 50g (gesamt)</t>
         </is>
       </c>
       <c r="H1754" t="inlineStr">
@@ -78709,7 +78789,7 @@
       </c>
       <c r="E1755" t="inlineStr">
         <is>
-          <t>Lesezeichen (bestimmte Stelle)</t>
+          <t>Titelseitenklappe</t>
         </is>
       </c>
       <c r="H1755" t="inlineStr">
@@ -78747,7 +78827,7 @@
       </c>
       <c r="E1756" t="inlineStr">
         <is>
-          <t>Teaser-Anzeige auf Inhalt-Seite</t>
+          <t>French Cover</t>
         </is>
       </c>
       <c r="H1756" t="inlineStr">
@@ -78785,7 +78865,7 @@
       </c>
       <c r="E1757" t="inlineStr">
         <is>
-          <t>Teaser-Anzeige im red. Text</t>
+          <t>ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1757" t="inlineStr">
@@ -78823,7 +78903,7 @@
       </c>
       <c r="E1758" t="inlineStr">
         <is>
-          <t>Griffecke auf Inhalt-Seite</t>
+          <t>1/2 ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1758" t="inlineStr">
@@ -78861,7 +78941,7 @@
       </c>
       <c r="E1759" t="inlineStr">
         <is>
-          <t>Griffecke im red. Text</t>
+          <t>Banderole (umlaufend)</t>
         </is>
       </c>
       <c r="H1759" t="inlineStr">
@@ -78894,12 +78974,12 @@
       </c>
       <c r="D1760" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1760" t="inlineStr">
         <is>
-          <t>Klappohr-Einhefter</t>
+          <t>Sogbanderole</t>
         </is>
       </c>
       <c r="H1760" t="inlineStr">
@@ -78932,12 +79012,12 @@
       </c>
       <c r="D1761" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1761" t="inlineStr">
         <is>
-          <t>gestanzter Einhefter</t>
+          <t>Zangenbanderole</t>
         </is>
       </c>
       <c r="H1761" t="inlineStr">
@@ -78970,12 +79050,12 @@
       </c>
       <c r="D1762" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1762" t="inlineStr">
         <is>
-          <t>Einhefter mit Klappe</t>
+          <t>Pfeilbanderole</t>
         </is>
       </c>
       <c r="H1762" t="inlineStr">
@@ -79008,12 +79088,12 @@
       </c>
       <c r="D1763" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1763" t="inlineStr">
         <is>
-          <t>Flip-Einhefter</t>
+          <t>Oversize-Beilage</t>
         </is>
       </c>
       <c r="H1763" t="inlineStr">
@@ -79038,20 +79118,20 @@
       </c>
       <c r="B1764" t="inlineStr">
         <is>
-          <t>InFo Hämatologie + Onkologie</t>
+          <t>Im Fokus Onkologie</t>
         </is>
       </c>
       <c r="C1764" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="D1764" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1764" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
+          <t>Lesezeichen (unbestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1764" t="inlineStr">
@@ -79076,20 +79156,20 @@
       </c>
       <c r="B1765" t="inlineStr">
         <is>
-          <t>InFo Hämatologie + Onkologie</t>
+          <t>Im Fokus Onkologie</t>
         </is>
       </c>
       <c r="C1765" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="D1765" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1765" t="inlineStr">
         <is>
-          <t>1/2 Seite</t>
+          <t>Lesezeichen (bestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1765" t="inlineStr">
@@ -79114,20 +79194,20 @@
       </c>
       <c r="B1766" t="inlineStr">
         <is>
-          <t>InFo Hämatologie + Onkologie</t>
+          <t>Im Fokus Onkologie</t>
         </is>
       </c>
       <c r="C1766" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="D1766" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1766" t="inlineStr">
         <is>
-          <t>1/3 Seite</t>
+          <t>Teaser-Anzeige auf Inhalt-Seite</t>
         </is>
       </c>
       <c r="H1766" t="inlineStr">
@@ -79152,20 +79232,20 @@
       </c>
       <c r="B1767" t="inlineStr">
         <is>
-          <t>InFo Hämatologie + Onkologie</t>
+          <t>Im Fokus Onkologie</t>
         </is>
       </c>
       <c r="C1767" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="D1767" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1767" t="inlineStr">
         <is>
-          <t>1/4 Seite</t>
+          <t>Teaser-Anzeige im red. Text</t>
         </is>
       </c>
       <c r="H1767" t="inlineStr">
@@ -79190,20 +79270,20 @@
       </c>
       <c r="B1768" t="inlineStr">
         <is>
-          <t>InFo Hämatologie + Onkologie</t>
+          <t>Im Fokus Onkologie</t>
         </is>
       </c>
       <c r="C1768" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="D1768" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1768" t="inlineStr">
         <is>
-          <t>2/1 Doppelseite</t>
+          <t>Griffecke auf Inhalt-Seite</t>
         </is>
       </c>
       <c r="H1768" t="inlineStr">
@@ -79228,20 +79308,20 @@
       </c>
       <c r="B1769" t="inlineStr">
         <is>
-          <t>InFo Hämatologie + Onkologie</t>
+          <t>Im Fokus Onkologie</t>
         </is>
       </c>
       <c r="C1769" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="D1769" t="inlineStr">
         <is>
-          <t>Normalplatzierungen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1769" t="inlineStr">
         <is>
-          <t>Advertorial (1/1 Seite)</t>
+          <t>Griffecke im red. Text</t>
         </is>
       </c>
       <c r="H1769" t="inlineStr">
@@ -79266,20 +79346,20 @@
       </c>
       <c r="B1770" t="inlineStr">
         <is>
-          <t>InFo Hämatologie + Onkologie</t>
+          <t>Im Fokus Onkologie</t>
         </is>
       </c>
       <c r="C1770" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="D1770" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1770" t="inlineStr">
         <is>
-          <t>4. Umschlagseite</t>
+          <t>Klappohr-Einhefter</t>
         </is>
       </c>
       <c r="H1770" t="inlineStr">
@@ -79304,20 +79384,20 @@
       </c>
       <c r="B1771" t="inlineStr">
         <is>
-          <t>InFo Hämatologie + Onkologie</t>
+          <t>Im Fokus Onkologie</t>
         </is>
       </c>
       <c r="C1771" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="D1771" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1771" t="inlineStr">
         <is>
-          <t>2. Umschlagseite</t>
+          <t>gestanzter Einhefter</t>
         </is>
       </c>
       <c r="H1771" t="inlineStr">
@@ -79342,20 +79422,20 @@
       </c>
       <c r="B1772" t="inlineStr">
         <is>
-          <t>InFo Hämatologie + Onkologie</t>
+          <t>Im Fokus Onkologie</t>
         </is>
       </c>
       <c r="C1772" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="D1772" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1772" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 1</t>
+          <t>Einhefter mit Klappe</t>
         </is>
       </c>
       <c r="H1772" t="inlineStr">
@@ -79380,20 +79460,20 @@
       </c>
       <c r="B1773" t="inlineStr">
         <is>
-          <t>InFo Hämatologie + Onkologie</t>
+          <t>Im Fokus Onkologie</t>
         </is>
       </c>
       <c r="C1773" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="D1773" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1773" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 2</t>
+          <t>Flip-Einhefter</t>
         </is>
       </c>
       <c r="H1773" t="inlineStr">
@@ -79426,12 +79506,12 @@
       </c>
       <c r="D1774" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1774" t="inlineStr">
         <is>
-          <t>Seite ggü. Inhalt 3</t>
+          <t>1/1 Seite</t>
         </is>
       </c>
       <c r="H1774" t="inlineStr">
@@ -79464,12 +79544,12 @@
       </c>
       <c r="D1775" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1775" t="inlineStr">
         <is>
-          <t>Seite ggü. Textanfang</t>
+          <t>1/2 Seite</t>
         </is>
       </c>
       <c r="H1775" t="inlineStr">
@@ -79502,12 +79582,12 @@
       </c>
       <c r="D1776" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1776" t="inlineStr">
         <is>
-          <t>1/1 Seite Festplatzierung</t>
+          <t>1/3 Seite</t>
         </is>
       </c>
       <c r="H1776" t="inlineStr">
@@ -79540,12 +79620,12 @@
       </c>
       <c r="D1777" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1777" t="inlineStr">
         <is>
-          <t>1. rechte Einschaltseite</t>
+          <t>1/4 Seite</t>
         </is>
       </c>
       <c r="H1777" t="inlineStr">
@@ -79578,12 +79658,12 @@
       </c>
       <c r="D1778" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1778" t="inlineStr">
         <is>
-          <t>2. rechte Einschaltseite</t>
+          <t>2/1 Doppelseite</t>
         </is>
       </c>
       <c r="H1778" t="inlineStr">
@@ -79616,12 +79696,12 @@
       </c>
       <c r="D1779" t="inlineStr">
         <is>
-          <t>Vorzugsplatzierungen</t>
+          <t>Normalplatzierungen</t>
         </is>
       </c>
       <c r="E1779" t="inlineStr">
         <is>
-          <t>3. rechte Einschaltseite</t>
+          <t>Advertorial (1/1 Seite)</t>
         </is>
       </c>
       <c r="H1779" t="inlineStr">
@@ -79659,7 +79739,7 @@
       </c>
       <c r="E1780" t="inlineStr">
         <is>
-          <t>4. rechte Einschaltseite</t>
+          <t>4. Umschlagseite</t>
         </is>
       </c>
       <c r="H1780" t="inlineStr">
@@ -79697,7 +79777,7 @@
       </c>
       <c r="E1781" t="inlineStr">
         <is>
-          <t>5. rechte Einschaltseite</t>
+          <t>2. Umschlagseite</t>
         </is>
       </c>
       <c r="H1781" t="inlineStr">
@@ -79735,7 +79815,7 @@
       </c>
       <c r="E1782" t="inlineStr">
         <is>
-          <t>6. rechte Einschaltseite</t>
+          <t>Seite ggü. Inhalt 1</t>
         </is>
       </c>
       <c r="H1782" t="inlineStr">
@@ -79773,7 +79853,7 @@
       </c>
       <c r="E1783" t="inlineStr">
         <is>
-          <t>7. rechte Einschaltseite</t>
+          <t>Seite ggü. Inhalt 2</t>
         </is>
       </c>
       <c r="H1783" t="inlineStr">
@@ -79811,7 +79891,7 @@
       </c>
       <c r="E1784" t="inlineStr">
         <is>
-          <t>8. rechte Einschaltseite</t>
+          <t>Seite ggü. Inhalt 3</t>
         </is>
       </c>
       <c r="H1784" t="inlineStr">
@@ -79849,7 +79929,7 @@
       </c>
       <c r="E1785" t="inlineStr">
         <is>
-          <t>9. rechte Einschaltseite</t>
+          <t>Seite ggü. Textanfang</t>
         </is>
       </c>
       <c r="H1785" t="inlineStr">
@@ -79887,7 +79967,7 @@
       </c>
       <c r="E1786" t="inlineStr">
         <is>
-          <t>10. rechte Einschaltseite</t>
+          <t>1/1 Seite Festplatzierung</t>
         </is>
       </c>
       <c r="H1786" t="inlineStr">
@@ -79920,12 +80000,12 @@
       </c>
       <c r="D1787" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1787" t="inlineStr">
         <is>
-          <t>EH/DH 1 Seite</t>
+          <t>1. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1787" t="inlineStr">
@@ -79958,12 +80038,12 @@
       </c>
       <c r="D1788" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1788" t="inlineStr">
         <is>
-          <t>EH/DH 2 Seiten</t>
+          <t>2. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1788" t="inlineStr">
@@ -79996,12 +80076,12 @@
       </c>
       <c r="D1789" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1789" t="inlineStr">
         <is>
-          <t>EH/DH 4 Seiten</t>
+          <t>3. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1789" t="inlineStr">
@@ -80034,12 +80114,12 @@
       </c>
       <c r="D1790" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1790" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (pro 1.000)</t>
+          <t>4. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1790" t="inlineStr">
@@ -80072,12 +80152,12 @@
       </c>
       <c r="D1791" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1791" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (gesamt)</t>
+          <t>5. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1791" t="inlineStr">
@@ -80110,12 +80190,12 @@
       </c>
       <c r="D1792" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1792" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 50g (gesamt)</t>
+          <t>6. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1792" t="inlineStr">
@@ -80148,12 +80228,12 @@
       </c>
       <c r="D1793" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1793" t="inlineStr">
         <is>
-          <t>Titelseitenklappe</t>
+          <t>7. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1793" t="inlineStr">
@@ -80186,12 +80266,12 @@
       </c>
       <c r="D1794" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1794" t="inlineStr">
         <is>
-          <t>French Cover</t>
+          <t>8. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1794" t="inlineStr">
@@ -80224,12 +80304,12 @@
       </c>
       <c r="D1795" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1795" t="inlineStr">
         <is>
-          <t>ausklappbare 2. US</t>
+          <t>9. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1795" t="inlineStr">
@@ -80262,12 +80342,12 @@
       </c>
       <c r="D1796" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Vorzugsplatzierungen</t>
         </is>
       </c>
       <c r="E1796" t="inlineStr">
         <is>
-          <t>1/2 ausklappbare 2. US</t>
+          <t>10. rechte Einschaltseite</t>
         </is>
       </c>
       <c r="H1796" t="inlineStr">
@@ -80300,12 +80380,12 @@
       </c>
       <c r="D1797" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1797" t="inlineStr">
         <is>
-          <t>Banderole (umlaufend)</t>
+          <t>EH/DH 1 Seite</t>
         </is>
       </c>
       <c r="H1797" t="inlineStr">
@@ -80338,12 +80418,12 @@
       </c>
       <c r="D1798" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1798" t="inlineStr">
         <is>
-          <t>Sogbanderole</t>
+          <t>EH/DH 2 Seiten</t>
         </is>
       </c>
       <c r="H1798" t="inlineStr">
@@ -80376,12 +80456,12 @@
       </c>
       <c r="D1799" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1799" t="inlineStr">
         <is>
-          <t>Zangenbanderole</t>
+          <t>EH/DH 4 Seiten</t>
         </is>
       </c>
       <c r="H1799" t="inlineStr">
@@ -80414,12 +80494,12 @@
       </c>
       <c r="D1800" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1800" t="inlineStr">
         <is>
-          <t>Pfeilbanderole</t>
+          <t>Werbebeilage bis 25g (pro 1.000)</t>
         </is>
       </c>
       <c r="H1800" t="inlineStr">
@@ -80452,12 +80532,12 @@
       </c>
       <c r="D1801" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1801" t="inlineStr">
         <is>
-          <t>Oversize-Beilage</t>
+          <t>Werbebeilage bis 25g (gesamt)</t>
         </is>
       </c>
       <c r="H1801" t="inlineStr">
@@ -80490,12 +80570,12 @@
       </c>
       <c r="D1802" t="inlineStr">
         <is>
-          <t>Sonderwerbeformen</t>
+          <t>Beilagen</t>
         </is>
       </c>
       <c r="E1802" t="inlineStr">
         <is>
-          <t>Lesezeichen (unbestimmte Stelle)</t>
+          <t>Werbebeilage bis 50g (gesamt)</t>
         </is>
       </c>
       <c r="H1802" t="inlineStr">
@@ -80533,7 +80613,7 @@
       </c>
       <c r="E1803" t="inlineStr">
         <is>
-          <t>Lesezeichen (bestimmte Stelle)</t>
+          <t>Titelseitenklappe</t>
         </is>
       </c>
       <c r="H1803" t="inlineStr">
@@ -80571,7 +80651,7 @@
       </c>
       <c r="E1804" t="inlineStr">
         <is>
-          <t>Teaser-Anzeige auf Inhalt-Seite</t>
+          <t>French Cover</t>
         </is>
       </c>
       <c r="H1804" t="inlineStr">
@@ -80609,7 +80689,7 @@
       </c>
       <c r="E1805" t="inlineStr">
         <is>
-          <t>Teaser-Anzeige im red. Text</t>
+          <t>ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1805" t="inlineStr">
@@ -80647,7 +80727,7 @@
       </c>
       <c r="E1806" t="inlineStr">
         <is>
-          <t>Griffecke auf Inhalt-Seite</t>
+          <t>1/2 ausklappbare 2. US</t>
         </is>
       </c>
       <c r="H1806" t="inlineStr">
@@ -80685,7 +80765,7 @@
       </c>
       <c r="E1807" t="inlineStr">
         <is>
-          <t>Griffecke im red. Text</t>
+          <t>Banderole (umlaufend)</t>
         </is>
       </c>
       <c r="H1807" t="inlineStr">
@@ -80718,12 +80798,12 @@
       </c>
       <c r="D1808" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1808" t="inlineStr">
         <is>
-          <t>Klappohr-Einhefter</t>
+          <t>Sogbanderole</t>
         </is>
       </c>
       <c r="H1808" t="inlineStr">
@@ -80756,12 +80836,12 @@
       </c>
       <c r="D1809" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1809" t="inlineStr">
         <is>
-          <t>gestanzter Einhefter</t>
+          <t>Zangenbanderole</t>
         </is>
       </c>
       <c r="H1809" t="inlineStr">
@@ -80794,12 +80874,12 @@
       </c>
       <c r="D1810" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1810" t="inlineStr">
         <is>
-          <t>Einhefter mit Klappe</t>
+          <t>Pfeilbanderole</t>
         </is>
       </c>
       <c r="H1810" t="inlineStr">
@@ -80832,12 +80912,12 @@
       </c>
       <c r="D1811" t="inlineStr">
         <is>
-          <t>Einhefter-Sonderwerbeformen</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1811" t="inlineStr">
         <is>
-          <t>Flip-Einhefter</t>
+          <t>Oversize-Beilage</t>
         </is>
       </c>
       <c r="H1811" t="inlineStr">
@@ -80862,20 +80942,20 @@
       </c>
       <c r="B1812" t="inlineStr">
         <is>
-          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+          <t>InFo Hämatologie + Onkologie</t>
         </is>
       </c>
       <c r="C1812" t="n">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="D1812" t="inlineStr">
         <is>
-          <t>Anzeigenformate</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1812" t="inlineStr">
         <is>
-          <t>1/1 Seite</t>
+          <t>Lesezeichen (unbestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1812" t="inlineStr">
@@ -80900,20 +80980,20 @@
       </c>
       <c r="B1813" t="inlineStr">
         <is>
-          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+          <t>InFo Hämatologie + Onkologie</t>
         </is>
       </c>
       <c r="C1813" t="n">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="D1813" t="inlineStr">
         <is>
-          <t>Anzeigenformate</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1813" t="inlineStr">
         <is>
-          <t>A4 Seite hoch</t>
+          <t>Lesezeichen (bestimmte Stelle)</t>
         </is>
       </c>
       <c r="H1813" t="inlineStr">
@@ -80938,20 +81018,20 @@
       </c>
       <c r="B1814" t="inlineStr">
         <is>
-          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+          <t>InFo Hämatologie + Onkologie</t>
         </is>
       </c>
       <c r="C1814" t="n">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="D1814" t="inlineStr">
         <is>
-          <t>Anzeigenformate</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1814" t="inlineStr">
         <is>
-          <t>A5 Seite hoch</t>
+          <t>Teaser-Anzeige auf Inhalt-Seite</t>
         </is>
       </c>
       <c r="H1814" t="inlineStr">
@@ -80976,20 +81056,20 @@
       </c>
       <c r="B1815" t="inlineStr">
         <is>
-          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+          <t>InFo Hämatologie + Onkologie</t>
         </is>
       </c>
       <c r="C1815" t="n">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="D1815" t="inlineStr">
         <is>
-          <t>Anzeigenformate</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1815" t="inlineStr">
         <is>
-          <t>3/4 Seite quer</t>
+          <t>Teaser-Anzeige im red. Text</t>
         </is>
       </c>
       <c r="H1815" t="inlineStr">
@@ -81014,20 +81094,20 @@
       </c>
       <c r="B1816" t="inlineStr">
         <is>
-          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+          <t>InFo Hämatologie + Onkologie</t>
         </is>
       </c>
       <c r="C1816" t="n">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="D1816" t="inlineStr">
         <is>
-          <t>Anzeigenformate</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1816" t="inlineStr">
         <is>
-          <t>1/2 Seite quer</t>
+          <t>Griffecke auf Inhalt-Seite</t>
         </is>
       </c>
       <c r="H1816" t="inlineStr">
@@ -81052,20 +81132,20 @@
       </c>
       <c r="B1817" t="inlineStr">
         <is>
-          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+          <t>InFo Hämatologie + Onkologie</t>
         </is>
       </c>
       <c r="C1817" t="n">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="D1817" t="inlineStr">
         <is>
-          <t>Anzeigenformate</t>
+          <t>Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1817" t="inlineStr">
         <is>
-          <t>1/3 Seite quer</t>
+          <t>Griffecke im red. Text</t>
         </is>
       </c>
       <c r="H1817" t="inlineStr">
@@ -81090,20 +81170,20 @@
       </c>
       <c r="B1818" t="inlineStr">
         <is>
-          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+          <t>InFo Hämatologie + Onkologie</t>
         </is>
       </c>
       <c r="C1818" t="n">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="D1818" t="inlineStr">
         <is>
-          <t>Anzeigenformate</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1818" t="inlineStr">
         <is>
-          <t>1/4 Seite quer</t>
+          <t>Klappohr-Einhefter</t>
         </is>
       </c>
       <c r="H1818" t="inlineStr">
@@ -81128,20 +81208,20 @@
       </c>
       <c r="B1819" t="inlineStr">
         <is>
-          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+          <t>InFo Hämatologie + Onkologie</t>
         </is>
       </c>
       <c r="C1819" t="n">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="D1819" t="inlineStr">
         <is>
-          <t>Anzeigenformate</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1819" t="inlineStr">
         <is>
-          <t>Advertorial (A4 hoch)</t>
+          <t>gestanzter Einhefter</t>
         </is>
       </c>
       <c r="H1819" t="inlineStr">
@@ -81166,20 +81246,20 @@
       </c>
       <c r="B1820" t="inlineStr">
         <is>
-          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+          <t>InFo Hämatologie + Onkologie</t>
         </is>
       </c>
       <c r="C1820" t="n">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="D1820" t="inlineStr">
         <is>
-          <t>Sonder- und Festplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1820" t="inlineStr">
         <is>
-          <t>Titelseitenfuß</t>
+          <t>Einhefter mit Klappe</t>
         </is>
       </c>
       <c r="H1820" t="inlineStr">
@@ -81204,20 +81284,20 @@
       </c>
       <c r="B1821" t="inlineStr">
         <is>
-          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+          <t>InFo Hämatologie + Onkologie</t>
         </is>
       </c>
       <c r="C1821" t="n">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="D1821" t="inlineStr">
         <is>
-          <t>Sonder- und Festplatzierungen</t>
+          <t>Einhefter-Sonderwerbeformen</t>
         </is>
       </c>
       <c r="E1821" t="inlineStr">
         <is>
-          <t>Insel</t>
+          <t>Flip-Einhefter</t>
         </is>
       </c>
       <c r="H1821" t="inlineStr">
@@ -81250,12 +81330,12 @@
       </c>
       <c r="D1822" t="inlineStr">
         <is>
-          <t>Sonder- und Festplatzierungen</t>
+          <t>Anzeigenformate</t>
         </is>
       </c>
       <c r="E1822" t="inlineStr">
         <is>
-          <t>Insel maxi</t>
+          <t>1/1 Seite</t>
         </is>
       </c>
       <c r="H1822" t="inlineStr">
@@ -81288,12 +81368,12 @@
       </c>
       <c r="D1823" t="inlineStr">
         <is>
-          <t>Sonder- und Festplatzierungen</t>
+          <t>Anzeigenformate</t>
         </is>
       </c>
       <c r="E1823" t="inlineStr">
         <is>
-          <t>Tunnel klein</t>
+          <t>A4 Seite hoch</t>
         </is>
       </c>
       <c r="H1823" t="inlineStr">
@@ -81326,12 +81406,12 @@
       </c>
       <c r="D1824" t="inlineStr">
         <is>
-          <t>Sonder- und Festplatzierungen</t>
+          <t>Anzeigenformate</t>
         </is>
       </c>
       <c r="E1824" t="inlineStr">
         <is>
-          <t>Tunnel groß</t>
+          <t>A5 Seite hoch</t>
         </is>
       </c>
       <c r="H1824" t="inlineStr">
@@ -81364,12 +81444,12 @@
       </c>
       <c r="D1825" t="inlineStr">
         <is>
-          <t>Sonder- und Festplatzierungen</t>
+          <t>Anzeigenformate</t>
         </is>
       </c>
       <c r="E1825" t="inlineStr">
         <is>
-          <t>Seite 3, 1/1 Seite</t>
+          <t>3/4 Seite quer</t>
         </is>
       </c>
       <c r="H1825" t="inlineStr">
@@ -81402,12 +81482,12 @@
       </c>
       <c r="D1826" t="inlineStr">
         <is>
-          <t>Sonder- und Festplatzierungen</t>
+          <t>Anzeigenformate</t>
         </is>
       </c>
       <c r="E1826" t="inlineStr">
         <is>
-          <t>Seite 5, 1/1 Seite</t>
+          <t>1/2 Seite quer</t>
         </is>
       </c>
       <c r="H1826" t="inlineStr">
@@ -81440,12 +81520,12 @@
       </c>
       <c r="D1827" t="inlineStr">
         <is>
-          <t>Sonder- und Festplatzierungen</t>
+          <t>Anzeigenformate</t>
         </is>
       </c>
       <c r="E1827" t="inlineStr">
         <is>
-          <t>Seite 7, 1/1 Seite</t>
+          <t>1/3 Seite quer</t>
         </is>
       </c>
       <c r="H1827" t="inlineStr">
@@ -81478,12 +81558,12 @@
       </c>
       <c r="D1828" t="inlineStr">
         <is>
-          <t>Sonder- und Festplatzierungen</t>
+          <t>Anzeigenformate</t>
         </is>
       </c>
       <c r="E1828" t="inlineStr">
         <is>
-          <t>Seite 9, 1/1 Seite</t>
+          <t>1/4 Seite quer</t>
         </is>
       </c>
       <c r="H1828" t="inlineStr">
@@ -81516,12 +81596,12 @@
       </c>
       <c r="D1829" t="inlineStr">
         <is>
-          <t>Sonder- und Festplatzierungen</t>
+          <t>Anzeigenformate</t>
         </is>
       </c>
       <c r="E1829" t="inlineStr">
         <is>
-          <t>Seite 11, 1/1 Seite</t>
+          <t>Advertorial (A4 hoch)</t>
         </is>
       </c>
       <c r="H1829" t="inlineStr">
@@ -81559,7 +81639,7 @@
       </c>
       <c r="E1830" t="inlineStr">
         <is>
-          <t>Seite 3, A4 hoch</t>
+          <t>Titelseitenfuß</t>
         </is>
       </c>
       <c r="H1830" t="inlineStr">
@@ -81597,7 +81677,7 @@
       </c>
       <c r="E1831" t="inlineStr">
         <is>
-          <t>Seite 5, A4 hoch</t>
+          <t>Insel</t>
         </is>
       </c>
       <c r="H1831" t="inlineStr">
@@ -81635,7 +81715,7 @@
       </c>
       <c r="E1832" t="inlineStr">
         <is>
-          <t>Seite 7, A4 hoch</t>
+          <t>Insel maxi</t>
         </is>
       </c>
       <c r="H1832" t="inlineStr">
@@ -81673,7 +81753,7 @@
       </c>
       <c r="E1833" t="inlineStr">
         <is>
-          <t>Seite 9, A4 hoch</t>
+          <t>Tunnel klein</t>
         </is>
       </c>
       <c r="H1833" t="inlineStr">
@@ -81711,7 +81791,7 @@
       </c>
       <c r="E1834" t="inlineStr">
         <is>
-          <t>Seite 11, A4 hoch</t>
+          <t>Tunnel groß</t>
         </is>
       </c>
       <c r="H1834" t="inlineStr">
@@ -81744,12 +81824,12 @@
       </c>
       <c r="D1835" t="inlineStr">
         <is>
-          <t>Ein- und Durchhefter</t>
+          <t>Sonder- und Festplatzierungen</t>
         </is>
       </c>
       <c r="E1835" t="inlineStr">
         <is>
-          <t>Flex-Tarif – 1/1 Seite 4c</t>
+          <t>Seite 3, 1/1 Seite</t>
         </is>
       </c>
       <c r="H1835" t="inlineStr">
@@ -81782,12 +81862,12 @@
       </c>
       <c r="D1836" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Sonder- und Festplatzierungen</t>
         </is>
       </c>
       <c r="E1836" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (pro 1.000)</t>
+          <t>Seite 5, 1/1 Seite</t>
         </is>
       </c>
       <c r="H1836" t="inlineStr">
@@ -81820,12 +81900,12 @@
       </c>
       <c r="D1837" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Sonder- und Festplatzierungen</t>
         </is>
       </c>
       <c r="E1837" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 25g (gesamt)</t>
+          <t>Seite 7, 1/1 Seite</t>
         </is>
       </c>
       <c r="H1837" t="inlineStr">
@@ -81858,12 +81938,12 @@
       </c>
       <c r="D1838" t="inlineStr">
         <is>
-          <t>Beilagen</t>
+          <t>Sonder- und Festplatzierungen</t>
         </is>
       </c>
       <c r="E1838" t="inlineStr">
         <is>
-          <t>Werbebeilage bis 50g (gesamt)</t>
+          <t>Seite 9, 1/1 Seite</t>
         </is>
       </c>
       <c r="H1838" t="inlineStr">
@@ -81896,12 +81976,12 @@
       </c>
       <c r="D1839" t="inlineStr">
         <is>
-          <t>AdSpecials</t>
+          <t>Sonder- und Festplatzierungen</t>
         </is>
       </c>
       <c r="E1839" t="inlineStr">
         <is>
-          <t>Großumleger 4-seitig</t>
+          <t>Seite 11, 1/1 Seite</t>
         </is>
       </c>
       <c r="H1839" t="inlineStr">
@@ -81934,12 +82014,12 @@
       </c>
       <c r="D1840" t="inlineStr">
         <is>
-          <t>AdSpecials</t>
+          <t>Sonder- und Festplatzierungen</t>
         </is>
       </c>
       <c r="E1840" t="inlineStr">
         <is>
-          <t>Titelseite + 2. Seite</t>
+          <t>Seite 3, A4 hoch</t>
         </is>
       </c>
       <c r="H1840" t="inlineStr">
@@ -81972,12 +82052,12 @@
       </c>
       <c r="D1841" t="inlineStr">
         <is>
-          <t>AdSpecials</t>
+          <t>Sonder- und Festplatzierungen</t>
         </is>
       </c>
       <c r="E1841" t="inlineStr">
         <is>
-          <t>Transparenzumleger 4-seitig</t>
+          <t>Seite 5, A4 hoch</t>
         </is>
       </c>
       <c r="H1841" t="inlineStr">
@@ -82010,12 +82090,12 @@
       </c>
       <c r="D1842" t="inlineStr">
         <is>
-          <t>AdSpecials</t>
+          <t>Sonder- und Festplatzierungen</t>
         </is>
       </c>
       <c r="E1842" t="inlineStr">
         <is>
-          <t>HalfCover TSK (voll)</t>
+          <t>Seite 7, A4 hoch</t>
         </is>
       </c>
       <c r="H1842" t="inlineStr">
@@ -82048,12 +82128,12 @@
       </c>
       <c r="D1843" t="inlineStr">
         <is>
-          <t>AdSpecials</t>
+          <t>Sonder- und Festplatzierungen</t>
         </is>
       </c>
       <c r="E1843" t="inlineStr">
         <is>
-          <t>HalfCover TSK (1/2 Vorder-/Rückseite)</t>
+          <t>Seite 9, A4 hoch</t>
         </is>
       </c>
       <c r="H1843" t="inlineStr">
@@ -82086,12 +82166,12 @@
       </c>
       <c r="D1844" t="inlineStr">
         <is>
-          <t>AdSpecials</t>
+          <t>Sonder- und Festplatzierungen</t>
         </is>
       </c>
       <c r="E1844" t="inlineStr">
         <is>
-          <t>Banderole</t>
+          <t>Seite 11, A4 hoch</t>
         </is>
       </c>
       <c r="H1844" t="inlineStr">
@@ -82124,12 +82204,12 @@
       </c>
       <c r="D1845" t="inlineStr">
         <is>
-          <t>AdSpecials</t>
+          <t>Ein- und Durchhefter</t>
         </is>
       </c>
       <c r="E1845" t="inlineStr">
         <is>
-          <t>Transparent-Flieger</t>
+          <t>Flex-Tarif – 1/1 Seite 4c</t>
         </is>
       </c>
       <c r="H1845" t="inlineStr">
@@ -82162,37 +82242,417 @@
       </c>
       <c r="D1846" t="inlineStr">
         <is>
+          <t>Beilagen</t>
+        </is>
+      </c>
+      <c r="E1846" t="inlineStr">
+        <is>
+          <t>Werbebeilage bis 25g (pro 1.000)</t>
+        </is>
+      </c>
+      <c r="H1846" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="I1846" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="K1846" t="inlineStr">
+        <is>
+          <t>Onkologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B1847" t="inlineStr">
+        <is>
+          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+        </is>
+      </c>
+      <c r="C1847" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D1847" t="inlineStr">
+        <is>
+          <t>Beilagen</t>
+        </is>
+      </c>
+      <c r="E1847" t="inlineStr">
+        <is>
+          <t>Werbebeilage bis 25g (gesamt)</t>
+        </is>
+      </c>
+      <c r="H1847" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="I1847" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="K1847" t="inlineStr">
+        <is>
+          <t>Onkologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B1848" t="inlineStr">
+        <is>
+          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+        </is>
+      </c>
+      <c r="C1848" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D1848" t="inlineStr">
+        <is>
+          <t>Beilagen</t>
+        </is>
+      </c>
+      <c r="E1848" t="inlineStr">
+        <is>
+          <t>Werbebeilage bis 50g (gesamt)</t>
+        </is>
+      </c>
+      <c r="H1848" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="I1848" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="K1848" t="inlineStr">
+        <is>
+          <t>Onkologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B1849" t="inlineStr">
+        <is>
+          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+        </is>
+      </c>
+      <c r="C1849" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D1849" t="inlineStr">
+        <is>
           <t>AdSpecials</t>
         </is>
       </c>
-      <c r="E1846" t="inlineStr">
+      <c r="E1849" t="inlineStr">
+        <is>
+          <t>Großumleger 4-seitig</t>
+        </is>
+      </c>
+      <c r="H1849" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="I1849" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="K1849" t="inlineStr">
+        <is>
+          <t>Onkologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B1850" t="inlineStr">
+        <is>
+          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+        </is>
+      </c>
+      <c r="C1850" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D1850" t="inlineStr">
+        <is>
+          <t>AdSpecials</t>
+        </is>
+      </c>
+      <c r="E1850" t="inlineStr">
+        <is>
+          <t>Titelseite + 2. Seite</t>
+        </is>
+      </c>
+      <c r="H1850" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="I1850" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="K1850" t="inlineStr">
+        <is>
+          <t>Onkologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B1851" t="inlineStr">
+        <is>
+          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+        </is>
+      </c>
+      <c r="C1851" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D1851" t="inlineStr">
+        <is>
+          <t>AdSpecials</t>
+        </is>
+      </c>
+      <c r="E1851" t="inlineStr">
+        <is>
+          <t>Transparenzumleger 4-seitig</t>
+        </is>
+      </c>
+      <c r="H1851" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="I1851" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="K1851" t="inlineStr">
+        <is>
+          <t>Onkologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B1852" t="inlineStr">
+        <is>
+          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+        </is>
+      </c>
+      <c r="C1852" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D1852" t="inlineStr">
+        <is>
+          <t>AdSpecials</t>
+        </is>
+      </c>
+      <c r="E1852" t="inlineStr">
+        <is>
+          <t>HalfCover TSK (voll)</t>
+        </is>
+      </c>
+      <c r="H1852" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="I1852" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="K1852" t="inlineStr">
+        <is>
+          <t>Onkologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B1853" t="inlineStr">
+        <is>
+          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+        </is>
+      </c>
+      <c r="C1853" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D1853" t="inlineStr">
+        <is>
+          <t>AdSpecials</t>
+        </is>
+      </c>
+      <c r="E1853" t="inlineStr">
+        <is>
+          <t>HalfCover TSK (1/2 Vorder-/Rückseite)</t>
+        </is>
+      </c>
+      <c r="H1853" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="I1853" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="K1853" t="inlineStr">
+        <is>
+          <t>Onkologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B1854" t="inlineStr">
+        <is>
+          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+        </is>
+      </c>
+      <c r="C1854" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D1854" t="inlineStr">
+        <is>
+          <t>AdSpecials</t>
+        </is>
+      </c>
+      <c r="E1854" t="inlineStr">
+        <is>
+          <t>Banderole</t>
+        </is>
+      </c>
+      <c r="H1854" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="I1854" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="K1854" t="inlineStr">
+        <is>
+          <t>Onkologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B1855" t="inlineStr">
+        <is>
+          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+        </is>
+      </c>
+      <c r="C1855" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D1855" t="inlineStr">
+        <is>
+          <t>AdSpecials</t>
+        </is>
+      </c>
+      <c r="E1855" t="inlineStr">
+        <is>
+          <t>Transparent-Flieger</t>
+        </is>
+      </c>
+      <c r="H1855" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="I1855" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="K1855" t="inlineStr">
+        <is>
+          <t>Onkologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B1856" t="inlineStr">
+        <is>
+          <t>Ärzte Zeitung ONKOLOGIE UND HÄMATOLOGIE</t>
+        </is>
+      </c>
+      <c r="C1856" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D1856" t="inlineStr">
+        <is>
+          <t>AdSpecials</t>
+        </is>
+      </c>
+      <c r="E1856" t="inlineStr">
         <is>
           <t>Aufkleber maschinell</t>
         </is>
       </c>
-      <c r="H1846" t="inlineStr">
-        <is>
-          <t>nein</t>
-        </is>
-      </c>
-      <c r="I1846" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="K1846" t="inlineStr">
+      <c r="H1856" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="I1856" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="K1856" t="inlineStr">
         <is>
           <t>Onkologie</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1846"/>
+  <autoFilter ref="A1:L1856"/>
   <dataValidations count="2">
-    <dataValidation sqref="H2:I1846" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:I1856" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J1846" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J1856" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"DU,EH"</formula1>
     </dataValidation>
   </dataValidations>
@@ -89143,8 +89603,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Wirbelsäule und Gelenke
-CME: Gelenke</t>
+          <t>Wirbelsäule und Gelenke</t>
         </is>
       </c>
     </row>
@@ -89189,8 +89648,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Palliativmedizin
-CME: Einsatz von PAMORAs/Opiate inkl. Diskussion verschiedener Leitlinien</t>
+          <t>Palliativmedizin</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -89244,8 +89702,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Polyneuropathie/Neuropathie aus drei dimensionaler Sicht
-CME: Nervenschmerzen – von der Anamnese zur Therapie: Konservative/klassische Medikation</t>
+          <t>Polyneuropathie/Neuropathie aus drei dimensionaler Sicht</t>
         </is>
       </c>
     </row>
@@ -89290,8 +89747,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Chronic Pelvic Pain
-CME: Chronic Pelvic Pain, konservative Therapie</t>
+          <t>Chronic Pelvic Pain</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -89346,8 +89802,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Cannabinoidtherapie
-CME: Cannabistherapie von den Ursprüngen bis heute</t>
+          <t>Cannabinoidtherapie</t>
         </is>
       </c>
     </row>
@@ -89392,8 +89847,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Gesundheitspolitik / Versorgung auf Bundes- und Landesebene
-CME: PsychosomatischeGrundversorgung</t>
+          <t>Gesundheitspolitik / Versorgung auf Bundes- und Landesebene</t>
         </is>
       </c>
     </row>
